--- a/hamlet/tables.xlsx
+++ b/hamlet/tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ge23nur\GitKraken\HAMLET\hamlet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ge23nur\Documents\Python Scripts\HAMLET\hamlet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5170B058-2F71-43FB-BC57-4E9E9A0D502F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B5BED9E-25DD-48AD-8748-2684FC98E2F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2" autoFilterDateGrouping="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-14505" yWindow="0" windowWidth="14610" windowHeight="17385" activeTab="2" autoFilterDateGrouping="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Explanation" sheetId="13" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="299">
   <si>
     <t>column</t>
   </si>
@@ -583,9 +583,6 @@
     <t>type_plants</t>
   </si>
   <si>
-    <t>none</t>
-  </si>
-  <si>
     <t>types of plants (per agent)</t>
   </si>
   <si>
@@ -899,6 +896,45 @@
   </si>
   <si>
     <t>meter_readings_delta</t>
+  </si>
+  <si>
+    <t>energy_type</t>
+  </si>
+  <si>
+    <t>type of energy (electr., heat, etc.)</t>
+  </si>
+  <si>
+    <t>timetable</t>
+  </si>
+  <si>
+    <t>contains the timetable with the actions to be conducted in the market</t>
+  </si>
+  <si>
+    <t>action</t>
+  </si>
+  <si>
+    <t>action to be undertaken for market</t>
+  </si>
+  <si>
+    <t>method</t>
+  </si>
+  <si>
+    <t>clearing method (pda, etc.)</t>
+  </si>
+  <si>
+    <t>clearing type (ex-ante, ex-post)</t>
+  </si>
+  <si>
+    <t>pricing</t>
+  </si>
+  <si>
+    <t>pricing method (uniform, etc.)</t>
+  </si>
+  <si>
+    <t>coupling</t>
+  </si>
+  <si>
+    <t>coupling method (above, below)</t>
   </si>
 </sst>
 </file>
@@ -986,7 +1022,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1023,6 +1059,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1344,7 +1381,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -2684,15 +2721,15 @@
     <row r="125" spans="1:6" s="4" customFormat="1" ht="15.75" collapsed="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="126" spans="1:6" s="4" customFormat="1" ht="15.75" collapsed="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B128" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="129" spans="1:29" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -2700,7 +2737,7 @@
         <v>60</v>
       </c>
       <c r="B129" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="130" spans="1:29" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -2782,31 +2819,31 @@
         <v>72</v>
       </c>
       <c r="C133" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D133" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E133" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F133" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G133" t="s">
         <v>72</v>
       </c>
       <c r="H133" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I133" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J133" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K133" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="134" spans="1:29" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -2817,15 +2854,15 @@
     <row r="135" spans="1:29" s="4" customFormat="1" ht="15.75" collapsed="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="137" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B137" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="138" spans="1:29" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="V138" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="139" spans="1:29" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -2839,28 +2876,28 @@
         <v>29</v>
       </c>
       <c r="D139" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E139" t="s">
         <v>31</v>
       </c>
       <c r="F139" t="s">
+        <v>189</v>
+      </c>
+      <c r="G139" t="s">
         <v>190</v>
       </c>
-      <c r="G139" t="s">
+      <c r="H139" t="s">
         <v>191</v>
-      </c>
-      <c r="H139" t="s">
-        <v>192</v>
       </c>
       <c r="I139" t="s">
         <v>30</v>
       </c>
       <c r="J139" t="s">
+        <v>192</v>
+      </c>
+      <c r="K139" t="s">
         <v>193</v>
-      </c>
-      <c r="K139" t="s">
-        <v>194</v>
       </c>
       <c r="L139" t="s">
         <v>26</v>
@@ -2869,28 +2906,28 @@
         <v>32</v>
       </c>
       <c r="N139" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O139" t="s">
         <v>34</v>
       </c>
       <c r="P139" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q139" t="s">
         <v>196</v>
       </c>
-      <c r="Q139" t="s">
+      <c r="R139" t="s">
         <v>197</v>
-      </c>
-      <c r="R139" t="s">
-        <v>198</v>
       </c>
       <c r="S139" t="s">
         <v>33</v>
       </c>
       <c r="T139" t="s">
+        <v>198</v>
+      </c>
+      <c r="U139" t="s">
         <v>199</v>
-      </c>
-      <c r="U139" t="s">
-        <v>200</v>
       </c>
       <c r="V139" t="s">
         <v>38</v>
@@ -2899,7 +2936,7 @@
         <v>35</v>
       </c>
       <c r="X139" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Y139" t="s">
         <v>77</v>
@@ -3011,88 +3048,88 @@
         <v>28</v>
       </c>
       <c r="B141" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C141" t="s">
         <v>72</v>
       </c>
       <c r="D141" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E141" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F141" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G141" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H141" t="s">
         <v>72</v>
       </c>
       <c r="I141" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J141" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K141" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L141" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="M141" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="N141" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O141" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="P141" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q141" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="R141" t="s">
         <v>72</v>
       </c>
       <c r="S141" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="T141" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="U141" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="V141" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="W141" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="X141" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Y141" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Z141" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AA141" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AB141" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AC141" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="142" spans="1:29" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -3103,15 +3140,15 @@
     <row r="143" spans="1:29" s="4" customFormat="1" ht="15.75" collapsed="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="144" spans="1:29" s="4" customFormat="1" ht="15.75" collapsed="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B146" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="147" spans="1:6" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -3119,7 +3156,7 @@
         <v>60</v>
       </c>
       <c r="B147" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="148" spans="1:6" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -3140,7 +3177,7 @@
         <v>15</v>
       </c>
       <c r="F149" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="150" spans="1:6" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -3168,19 +3205,19 @@
         <v>28</v>
       </c>
       <c r="B151" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C151" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D151" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E151" t="s">
         <v>72</v>
       </c>
       <c r="F151" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="152" spans="1:6" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -3191,10 +3228,10 @@
     <row r="153" spans="1:6" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B155" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="156" spans="1:6" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -3202,7 +3239,7 @@
         <v>60</v>
       </c>
       <c r="B156" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="157" spans="1:6" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -3214,7 +3251,7 @@
         <v>114</v>
       </c>
       <c r="C158" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="159" spans="1:6" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -3233,7 +3270,7 @@
         <v>28</v>
       </c>
       <c r="B160" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="161" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -3244,10 +3281,10 @@
     <row r="162" spans="1:3" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B164" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="165" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -3255,7 +3292,7 @@
         <v>60</v>
       </c>
       <c r="B165" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="166" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -3267,7 +3304,7 @@
         <v>114</v>
       </c>
       <c r="C167" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="168" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -3286,7 +3323,7 @@
         <v>28</v>
       </c>
       <c r="B169" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="170" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -3297,10 +3334,10 @@
     <row r="171" spans="1:3" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B173" t="s">
         <v>234</v>
-      </c>
-      <c r="B173" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="174" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -3308,7 +3345,7 @@
         <v>60</v>
       </c>
       <c r="B174" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="175" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -3320,7 +3357,7 @@
         <v>114</v>
       </c>
       <c r="C176" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="177" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -3339,7 +3376,7 @@
         <v>28</v>
       </c>
       <c r="B178" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="179" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -3350,10 +3387,10 @@
     <row r="180" spans="1:8" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B182" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="183" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -3361,7 +3398,7 @@
         <v>60</v>
       </c>
       <c r="B183" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="184" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -3373,10 +3410,10 @@
         <v>114</v>
       </c>
       <c r="C185" t="s">
+        <v>239</v>
+      </c>
+      <c r="D185" t="s">
         <v>240</v>
-      </c>
-      <c r="D185" t="s">
-        <v>241</v>
       </c>
       <c r="E185" t="s">
         <v>49</v>
@@ -3422,25 +3459,25 @@
         <v>28</v>
       </c>
       <c r="B187" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C187" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D187" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E187" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F187" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G187" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H187" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="188" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -3451,10 +3488,10 @@
     <row r="189" spans="1:8" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B191" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="192" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -3462,7 +3499,7 @@
         <v>60</v>
       </c>
       <c r="B192" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="193" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -3474,7 +3511,7 @@
         <v>114</v>
       </c>
       <c r="C194" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="195" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -3493,7 +3530,7 @@
         <v>28</v>
       </c>
       <c r="B196" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="197" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -3515,7 +3552,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{845B957E-FD5F-4D07-9D0A-3E5DB720F61E}">
-  <dimension ref="A1:AE204"/>
+  <dimension ref="A1:AK214"/>
   <sheetFormatPr defaultColWidth="25.7109375" defaultRowHeight="15" outlineLevelRow="4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.7109375" style="3"/>
@@ -3523,27 +3560,27 @@
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B1" t="s">
         <v>283</v>
-      </c>
-      <c r="B1" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C3" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D3" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="D3" s="15" t="s">
-        <v>256</v>
-      </c>
       <c r="E3" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -3551,13 +3588,13 @@
         <v>97</v>
       </c>
       <c r="B4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C4" t="s">
         <v>148</v>
       </c>
       <c r="D4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -3565,16 +3602,16 @@
     </row>
     <row r="5" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>136</v>
+        <v>288</v>
       </c>
       <c r="B5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C5" t="s">
-        <v>137</v>
+        <v>289</v>
       </c>
       <c r="D5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -3582,16 +3619,16 @@
     </row>
     <row r="6" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B6" t="s">
         <v>281</v>
       </c>
       <c r="C6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -3599,16 +3636,16 @@
     </row>
     <row r="7" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>286</v>
+        <v>140</v>
       </c>
       <c r="B7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
@@ -3616,16 +3653,16 @@
     </row>
     <row r="8" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>138</v>
+        <v>285</v>
       </c>
       <c r="B8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
@@ -3633,16 +3670,16 @@
     </row>
     <row r="9" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="B9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C9" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="D9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
@@ -3650,16 +3687,16 @@
     </row>
     <row r="10" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C10" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E10" t="b">
         <v>1</v>
@@ -3667,16 +3704,16 @@
     </row>
     <row r="11" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D11" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
@@ -3684,33 +3721,33 @@
     </row>
     <row r="12" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>204</v>
+        <v>174</v>
       </c>
       <c r="B12" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C12" t="s">
-        <v>208</v>
+        <v>175</v>
       </c>
       <c r="D12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B13" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C13" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
@@ -3718,16 +3755,16 @@
     </row>
     <row r="14" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B14" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C14" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D14" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
@@ -3735,16 +3772,16 @@
     </row>
     <row r="15" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>183</v>
+        <v>205</v>
       </c>
       <c r="B15" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C15" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D15" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
@@ -3752,116 +3789,132 @@
     </row>
     <row r="16" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>207</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C16" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D16" t="s">
+        <v>256</v>
+      </c>
+      <c r="E16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:37" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="B17" t="s">
+        <v>281</v>
+      </c>
+      <c r="C17" t="s">
+        <v>211</v>
+      </c>
+      <c r="D17" t="s">
+        <v>256</v>
+      </c>
+      <c r="E17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:37" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="B18" t="s">
+        <v>281</v>
+      </c>
+      <c r="C18" t="s">
+        <v>262</v>
+      </c>
+      <c r="D18" t="s">
         <v>257</v>
-      </c>
-      <c r="E16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:31" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="B17" t="s">
-        <v>282</v>
-      </c>
-      <c r="C17" t="s">
-        <v>263</v>
-      </c>
-      <c r="D17" t="s">
-        <v>258</v>
-      </c>
-      <c r="E17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:31" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="B18" t="s">
-        <v>282</v>
-      </c>
-      <c r="C18" t="s">
-        <v>264</v>
-      </c>
-      <c r="D18" t="s">
-        <v>258</v>
       </c>
       <c r="E18" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:31" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:37" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B19" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C19" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="D19" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E19" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:31" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:37" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B20" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C20" t="s">
         <v>265</v>
       </c>
       <c r="D20" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:31" outlineLevel="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:37" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B21" t="s">
+        <v>281</v>
+      </c>
+      <c r="C21" t="s">
+        <v>264</v>
+      </c>
+      <c r="D21" t="s">
+        <v>257</v>
+      </c>
+      <c r="E21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:37" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="B22" t="s">
+        <v>281</v>
+      </c>
+      <c r="C22" t="s">
         <v>267</v>
       </c>
-      <c r="B21" t="s">
-        <v>282</v>
-      </c>
-      <c r="C21" t="s">
-        <v>268</v>
-      </c>
-      <c r="D21" t="s">
-        <v>258</v>
-      </c>
-      <c r="E21" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:31" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:31" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D22" t="s">
+        <v>257</v>
+      </c>
+      <c r="E22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:37" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8"/>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="26" spans="1:31" s="9" customFormat="1" outlineLevel="4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:37" s="9" customFormat="1" outlineLevel="4" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>112</v>
       </c>
@@ -3881,82 +3934,100 @@
         <v>151</v>
       </c>
       <c r="G26" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="H26" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="H26" s="9" t="s">
+      <c r="I26" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="I26" s="9" t="s">
+      <c r="J26" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="K26" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="J26" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="K26" s="9" t="s">
+      <c r="L26" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="L26" s="9" t="s">
-        <v>213</v>
-      </c>
       <c r="M26" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="N26" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="N26" s="9" t="s">
+      <c r="O26" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="O26" s="9" t="s">
+      <c r="P26" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="P26" s="9" t="s">
+      <c r="Q26" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="R26" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="S26" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="T26" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="Q26" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="R26" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="S26" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="T26" s="9" t="s">
+      <c r="U26" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="U26" s="9" t="s">
+      <c r="V26" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="V26" s="9" t="s">
+      <c r="W26" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="X26" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="W26" s="9" t="s">
+      <c r="Y26" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="X26" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="Y26" s="9" t="s">
+      <c r="Z26" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="Z26" s="9" t="s">
+      <c r="AA26" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="AA26" s="9" t="s">
+      <c r="AB26" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="AB26" s="9" t="s">
+      <c r="AC26" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="AC26" s="9" t="s">
+      <c r="AD26" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="AD26" s="9" t="s">
-        <v>246</v>
-      </c>
       <c r="AE26" s="9" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="27" spans="1:31" s="9" customFormat="1" outlineLevel="4" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+      <c r="AF26" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="AG26" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="AH26" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="AI26" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="AJ26" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="AK26" s="9" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="27" spans="1:37" s="9" customFormat="1" outlineLevel="4" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>28</v>
       </c>
@@ -3988,13 +4059,13 @@
         <v>98</v>
       </c>
       <c r="K27" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="L27" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="L27" s="9" t="s">
+      <c r="M27" s="9" t="s">
         <v>93</v>
-      </c>
-      <c r="M27" s="9" t="s">
-        <v>128</v>
       </c>
       <c r="N27" s="9" t="s">
         <v>128</v>
@@ -4003,7 +4074,7 @@
         <v>128</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>92</v>
+        <v>128</v>
       </c>
       <c r="Q27" s="9" t="s">
         <v>92</v>
@@ -4012,7 +4083,7 @@
         <v>92</v>
       </c>
       <c r="S27" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T27" s="9" t="s">
         <v>93</v>
@@ -4021,34 +4092,52 @@
         <v>93</v>
       </c>
       <c r="V27" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="W27" s="9" t="s">
         <v>92</v>
-      </c>
-      <c r="W27" s="9" t="s">
-        <v>127</v>
       </c>
       <c r="X27" s="9" t="s">
         <v>127</v>
       </c>
       <c r="Y27" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z27" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="Z27" s="9" t="s">
+      <c r="AA27" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="AA27" s="9" t="s">
+      <c r="AB27" s="9" t="s">
         <v>91</v>
-      </c>
-      <c r="AB27" s="9" t="s">
-        <v>98</v>
       </c>
       <c r="AC27" s="9" t="s">
         <v>98</v>
       </c>
       <c r="AD27" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="AE27" s="9" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="28" spans="1:31" s="9" customFormat="1" outlineLevel="4" x14ac:dyDescent="0.25">
+      <c r="AG27" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH27" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI27" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="AJ27" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK27" s="9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:37" s="9" customFormat="1" outlineLevel="4" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
         <v>111</v>
       </c>
@@ -4083,7 +4172,7 @@
         <v>155</v>
       </c>
       <c r="L28" s="9" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="M28" s="9" t="s">
         <v>135</v>
@@ -4095,52 +4184,70 @@
         <v>135</v>
       </c>
       <c r="P28" s="9" t="s">
-        <v>250</v>
+        <v>135</v>
       </c>
       <c r="Q28" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="R28" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="S28" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="T28" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="U28" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="V28" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="W28" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="X28" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="Y28" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="Z28" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="AA28" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="AB28" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="AC28" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="AD28" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="AE28" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="T28" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="U28" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="V28" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="W28" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="X28" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="Y28" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="Z28" s="9" t="s">
+      <c r="AG28" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="AA28" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="AB28" s="9" t="s">
+      <c r="AH28" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="AC28" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="AD28" s="9" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="29" spans="1:31" s="9" customFormat="1" outlineLevel="4" x14ac:dyDescent="0.25">
+      <c r="AI28" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="AJ28" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="AK28" s="9" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="29" spans="1:37" s="9" customFormat="1" outlineLevel="4" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>1</v>
       </c>
@@ -4160,85 +4267,103 @@
         <v>154</v>
       </c>
       <c r="G29" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="H29" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="H29" s="9" t="s">
+      <c r="I29" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="I29" s="9" t="s">
+      <c r="J29" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="K29" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="J29" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="K29" s="9" t="s">
+      <c r="L29" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="L29" s="9" t="s">
-        <v>214</v>
-      </c>
       <c r="M29" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="N29" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="N29" s="9" t="s">
+      <c r="O29" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="O29" s="9" t="s">
+      <c r="P29" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="P29" s="9" t="s">
-        <v>218</v>
-      </c>
       <c r="Q29" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="R29" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="R29" s="9" t="s">
+      <c r="S29" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="S29" s="9" t="s">
-        <v>217</v>
-      </c>
       <c r="T29" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="U29" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="U29" s="9" t="s">
+      <c r="V29" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="V29" s="9" t="s">
+      <c r="W29" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="X29" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="W29" s="9" t="s">
+      <c r="Y29" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="X29" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="Y29" s="9" t="s">
+      <c r="Z29" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="Z29" s="9" t="s">
+      <c r="AA29" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="AA29" s="9" t="s">
+      <c r="AB29" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="AB29" s="9" t="s">
+      <c r="AC29" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="AC29" s="9" t="s">
-        <v>182</v>
-      </c>
       <c r="AD29" s="9" t="s">
-        <v>247</v>
+        <v>181</v>
       </c>
       <c r="AE29" s="9" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="30" spans="1:31" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>246</v>
+      </c>
+      <c r="AF29" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="AG29" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="AH29" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="AI29" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="AJ29" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="AK29" s="9" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="30" spans="1:37" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8"/>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>170</v>
       </c>
@@ -4322,10 +4447,10 @@
         <v>-9.2233720368547697E+18</v>
       </c>
       <c r="J34" s="14" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K34" s="14" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O34">
         <v>0</v>
@@ -4360,10 +4485,10 @@
         <v>9.2233720368547697E+18</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K35" s="14" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O35">
         <v>1</v>
@@ -4425,19 +4550,19 @@
         <v>balancing_energy</v>
       </c>
       <c r="B44" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A44,$A$4:$A$21,$B$4:$B$21)</f>
+        <f>_xlfn.XLOOKUP(A44,$A$4:$A$22,$B$4:$B$22)</f>
         <v>Analyzer</v>
       </c>
       <c r="C44" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A44,$A$4:$A$21,$C$4:$C$21)</f>
+        <f>_xlfn.XLOOKUP(A44,$A$4:$A$22,$C$4:$C$22)</f>
         <v>who required how much balancing energy and what it cost (can be extracted from market transactions)</v>
       </c>
       <c r="D44" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A44,$A$4:$A$21,$D$4:$D$21)</f>
+        <f>_xlfn.XLOOKUP(A44,$A$4:$A$22,$D$4:$D$22)</f>
         <v>Markets</v>
       </c>
       <c r="E44" s="5" t="b">
-        <f>_xlfn.XLOOKUP(A44,$A$4:$A$21,$E$4:$E$21)</f>
+        <f>_xlfn.XLOOKUP(A44,$A$4:$A$22,$E$4:$E$22)</f>
         <v>1</v>
       </c>
     </row>
@@ -4465,31 +4590,31 @@
         <v>name</v>
       </c>
       <c r="F46" t="str">
-        <f>H26</f>
+        <f>I26</f>
         <v>id_agent</v>
       </c>
       <c r="G46" s="9" t="str">
-        <f>M26</f>
+        <f>N26</f>
         <v>energy_in</v>
       </c>
       <c r="H46" s="9" t="str">
-        <f>N26</f>
+        <f>O26</f>
         <v>energy_out</v>
       </c>
       <c r="I46" s="9" t="str">
-        <f>Q26</f>
+        <f>R26</f>
         <v>price_pu_in</v>
       </c>
       <c r="J46" s="9" t="str">
-        <f>R26</f>
+        <f>S26</f>
         <v>price_pu_out</v>
       </c>
       <c r="K46" s="9" t="str">
-        <f>T26</f>
+        <f>U26</f>
         <v>price_in</v>
       </c>
       <c r="L46" s="9" t="str">
-        <f>U26</f>
+        <f>V26</f>
         <v>price_out</v>
       </c>
     </row>
@@ -4646,10 +4771,7 @@
     <row r="50" spans="1:15" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="8"/>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B51" s="5"/>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="15" t="str">
         <f>$A$3</f>
         <v>Table</v>
@@ -4671,3155 +4793,3287 @@
         <v>Saved</v>
       </c>
     </row>
-    <row r="53" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="16" t="str">
         <f>A5</f>
-        <v>market_transactions</v>
+        <v>timetable</v>
       </c>
       <c r="B53" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A53,$A$4:$A$21,$B$4:$B$21)</f>
+        <f>_xlfn.XLOOKUP(A207,$A$4:$A$22,$B$4:$B$22)</f>
         <v>Executor</v>
       </c>
       <c r="C53" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A53,$A$4:$A$21,$C$4:$C$21)</f>
-        <v>contains all trades done in the markets</v>
+        <f>_xlfn.XLOOKUP(A53,$A$4:$A$22,$C$4:$C$22)</f>
+        <v>contains the timetable with the actions to be conducted in the market</v>
       </c>
       <c r="D53" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A53,$A$4:$A$21,$D$4:$D$21)</f>
+        <f>_xlfn.XLOOKUP(A53,$A$4:$A$22,$D$4:$D$22)</f>
         <v>Markets</v>
       </c>
       <c r="E53" s="5" t="b">
-        <f>_xlfn.XLOOKUP(A53,$A$4:$A$21,$E$4:$E$21)</f>
+        <f>_xlfn.XLOOKUP(A53,$A$4:$A$22,$E$4:$E$22)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A54"/>
-    </row>
+    <row r="54" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
     <row r="55" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>0</v>
-      </c>
-      <c r="B55" s="9" t="str">
-        <f t="shared" ref="B55:F55" si="10">B26</f>
+      <c r="A55"/>
+      <c r="D55" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B56" s="18" t="str">
+        <f>B26</f>
         <v>timestamp</v>
       </c>
-      <c r="C55" s="9" t="str">
+      <c r="C56" s="18" t="str">
+        <f>C26</f>
+        <v>timestep</v>
+      </c>
+      <c r="D56" s="18" t="str">
+        <f>D26</f>
+        <v>region</v>
+      </c>
+      <c r="E56" s="18" t="str">
+        <f>E26</f>
+        <v>market</v>
+      </c>
+      <c r="F56" s="18" t="str">
+        <f>F26</f>
+        <v>name</v>
+      </c>
+      <c r="G56" s="18" t="str">
+        <f>G26</f>
+        <v>energy_type</v>
+      </c>
+      <c r="H56" s="9" t="str">
+        <f>AG26</f>
+        <v>action</v>
+      </c>
+      <c r="I56" s="9" t="str">
+        <f t="shared" ref="I56:K56" si="10">AH26</f>
+        <v>type</v>
+      </c>
+      <c r="J56" s="9" t="str">
         <f t="shared" si="10"/>
-        <v>timestep</v>
-      </c>
-      <c r="D55" s="9" t="str">
+        <v>method</v>
+      </c>
+      <c r="K56" s="9" t="str">
         <f t="shared" si="10"/>
-        <v>region</v>
-      </c>
-      <c r="E55" s="9" t="str">
-        <f t="shared" si="10"/>
-        <v>market</v>
-      </c>
-      <c r="F55" s="9" t="str">
-        <f t="shared" si="10"/>
-        <v>name</v>
-      </c>
-      <c r="G55" s="9" t="str">
-        <f>G26</f>
-        <v>type_transaction</v>
-      </c>
-      <c r="H55" s="9" t="str">
-        <f>H26</f>
-        <v>id_agent</v>
-      </c>
-      <c r="I55" s="9" t="str">
-        <f>M26</f>
-        <v>energy_in</v>
-      </c>
-      <c r="J55" s="9" t="str">
-        <f>N26</f>
-        <v>energy_out</v>
-      </c>
-      <c r="K55" s="9" t="str">
-        <f>Q26</f>
-        <v>price_pu_in</v>
-      </c>
-      <c r="L55" s="9" t="str">
-        <f>R26</f>
-        <v>price_pu_out</v>
-      </c>
-      <c r="M55" s="9" t="str">
-        <f>T26</f>
-        <v>price_in</v>
-      </c>
-      <c r="N55" s="9" t="str">
-        <f>U26</f>
-        <v>price_out</v>
-      </c>
-      <c r="O55" s="9" t="str">
-        <f>AA26</f>
-        <v>share_quality_XXX</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="9" t="str">
+        <v>pricing</v>
+      </c>
+      <c r="L56" s="9" t="str">
+        <f>AK26</f>
+        <v>coupling</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="9" t="str">
         <f>$A$27</f>
         <v>dtype</v>
       </c>
-      <c r="B56" s="3" t="str">
-        <f>_xlfn.XLOOKUP(B55,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="B57" s="3" t="str">
+        <f>_xlfn.XLOOKUP(B56,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>datetime</v>
       </c>
-      <c r="C56" s="3" t="str">
-        <f t="shared" ref="C56:F56" si="11">_xlfn.XLOOKUP(C55,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="C57" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C56,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>datetime</v>
       </c>
-      <c r="D56" s="3" t="str">
+      <c r="D57" s="3" t="str">
+        <f>_xlfn.XLOOKUP(D56,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <v>categorical</v>
+      </c>
+      <c r="E57" s="3" t="str">
+        <f t="shared" ref="E57:G57" si="11">_xlfn.XLOOKUP(E56,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <v>categorical</v>
+      </c>
+      <c r="F57" s="3" t="str">
         <f t="shared" si="11"/>
         <v>categorical</v>
       </c>
-      <c r="E56" s="3" t="str">
+      <c r="G57" s="3" t="str">
         <f t="shared" si="11"/>
         <v>categorical</v>
       </c>
-      <c r="F56" s="3" t="str">
-        <f t="shared" si="11"/>
+      <c r="H57" s="3" t="str">
+        <f t="shared" ref="H57" si="12">_xlfn.XLOOKUP(H56,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
-      <c r="G56" s="3" t="str">
-        <f>_xlfn.XLOOKUP(G55,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="I57" s="3" t="str">
+        <f t="shared" ref="I57" si="13">_xlfn.XLOOKUP(I56,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
-      <c r="H56" s="3" t="str">
-        <f>_xlfn.XLOOKUP(H55,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="J57" s="3" t="str">
+        <f t="shared" ref="J57" si="14">_xlfn.XLOOKUP(J56,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
-      <c r="I56" s="3" t="str">
-        <f t="shared" ref="I56:O56" si="12">_xlfn.XLOOKUP(I55,$B$26:$XFD$26,$B$27:$XFD$27)</f>
-        <v>uint64</v>
-      </c>
-      <c r="J56" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>uint64</v>
-      </c>
-      <c r="K56" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>int32</v>
-      </c>
-      <c r="L56" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>int32</v>
-      </c>
-      <c r="M56" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>int64</v>
-      </c>
-      <c r="N56" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>int64</v>
-      </c>
-      <c r="O56" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>int8</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="9" t="str">
+      <c r="K57" s="3" t="str">
+        <f t="shared" ref="K57" si="15">_xlfn.XLOOKUP(K56,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <v>categorical</v>
+      </c>
+      <c r="L57" s="3" t="str">
+        <f t="shared" ref="L57" si="16">_xlfn.XLOOKUP(L56,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <v>categorical</v>
+      </c>
+      <c r="M57" s="3"/>
+      <c r="N57" s="3"/>
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="9" t="str">
         <f>$A$28</f>
         <v>unit</v>
       </c>
-      <c r="B57" s="3" t="str">
-        <f>_xlfn.XLOOKUP(B55,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="B58" s="3" t="str">
+        <f>_xlfn.XLOOKUP(B56,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>s</v>
       </c>
-      <c r="C57" s="3" t="str">
-        <f t="shared" ref="C57:F57" si="13">_xlfn.XLOOKUP(C55,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="C58" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C56,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>s</v>
       </c>
-      <c r="D57" s="3" t="str">
-        <f t="shared" si="13"/>
+      <c r="D58" s="3" t="str">
+        <f>_xlfn.XLOOKUP(D56,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>None</v>
       </c>
-      <c r="E57" s="3" t="str">
-        <f t="shared" si="13"/>
+      <c r="E58" s="3" t="str">
+        <f t="shared" ref="E58:G58" si="17">_xlfn.XLOOKUP(E56,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>None</v>
       </c>
-      <c r="F57" s="3" t="str">
-        <f t="shared" si="13"/>
+      <c r="F58" s="3" t="str">
+        <f t="shared" si="17"/>
         <v>None</v>
       </c>
-      <c r="G57" s="3" t="str">
-        <f t="shared" ref="G57" si="14">_xlfn.XLOOKUP(G55,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="G58" s="3" t="str">
+        <f t="shared" si="17"/>
         <v>None</v>
       </c>
-      <c r="H57" s="3" t="str">
-        <f>_xlfn.XLOOKUP(H55,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="H58" s="3" t="str">
+        <f t="shared" ref="H58:L58" si="18">_xlfn.XLOOKUP(H56,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>None</v>
       </c>
-      <c r="I57" s="3" t="str">
-        <f t="shared" ref="I57:O57" si="15">_xlfn.XLOOKUP(I55,$B$26:$XFD$26,$B$28:$XFD$28)</f>
-        <v>Wh</v>
-      </c>
-      <c r="J57" s="3" t="str">
-        <f t="shared" si="15"/>
-        <v>Wh</v>
-      </c>
-      <c r="K57" s="3" t="str">
-        <f t="shared" si="15"/>
-        <v>€e7/Wh</v>
-      </c>
-      <c r="L57" s="3" t="str">
-        <f t="shared" si="15"/>
-        <v>€e7/Wh</v>
-      </c>
-      <c r="M57" s="3" t="str">
-        <f t="shared" si="15"/>
-        <v>€e7</v>
-      </c>
-      <c r="N57" s="3" t="str">
-        <f t="shared" si="15"/>
-        <v>€e7</v>
-      </c>
-      <c r="O57" s="3" t="str">
-        <f t="shared" si="15"/>
-        <v>0-100</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="9" t="str">
+      <c r="I58" s="3" t="str">
+        <f t="shared" si="18"/>
+        <v>None</v>
+      </c>
+      <c r="J58" s="3" t="str">
+        <f t="shared" si="18"/>
+        <v>None</v>
+      </c>
+      <c r="K58" s="3" t="str">
+        <f t="shared" si="18"/>
+        <v>None</v>
+      </c>
+      <c r="L58" s="3" t="str">
+        <f t="shared" si="18"/>
+        <v>None</v>
+      </c>
+      <c r="M58" s="3"/>
+      <c r="N58" s="3"/>
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="9" t="str">
         <f>$A$29</f>
         <v>description</v>
       </c>
-      <c r="B58" t="str">
-        <f>_xlfn.XLOOKUP(B55,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+      <c r="B59" t="str">
+        <f>_xlfn.XLOOKUP(B56,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>current timestamp</v>
       </c>
-      <c r="C58" t="str">
-        <f t="shared" ref="C58:F58" si="16">_xlfn.XLOOKUP(C55,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+      <c r="C59" t="str">
+        <f>_xlfn.XLOOKUP(C56,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>timestep (can be in future)</v>
       </c>
-      <c r="D58" t="str">
-        <f t="shared" si="16"/>
+      <c r="D59" t="str">
+        <f>_xlfn.XLOOKUP(D56,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>region in which the market is</v>
       </c>
-      <c r="E58" t="str">
-        <f t="shared" si="16"/>
+      <c r="E59" t="str">
+        <f t="shared" ref="E59:G59" si="19">_xlfn.XLOOKUP(E56,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>type of market</v>
       </c>
-      <c r="F58" t="str">
-        <f t="shared" si="16"/>
+      <c r="F59" t="str">
+        <f t="shared" si="19"/>
         <v>name of the market</v>
       </c>
-      <c r="G58" t="str">
-        <f t="shared" ref="G58" si="17">_xlfn.XLOOKUP(G55,$B$26:$XFD$26,$B$29:$XFD$29)</f>
-        <v>source of the costs/profits (e.g. Market, levies, balancing)</v>
-      </c>
-      <c r="H58" t="str">
-        <f>_xlfn.XLOOKUP(H55,$B$26:$XFD$26,$B$29:$XFD$29)</f>
-        <v>agent id (also serves as main meter)</v>
-      </c>
-      <c r="I58" t="str">
-        <f t="shared" ref="I58:O58" si="18">_xlfn.XLOOKUP(I55,$B$26:$XFD$26,$B$29:$XFD$29)</f>
-        <v>energy going into the meter</v>
-      </c>
-      <c r="J58" t="str">
-        <f t="shared" si="18"/>
-        <v>energy going out of the meter</v>
-      </c>
-      <c r="K58" t="str">
-        <f t="shared" si="18"/>
-        <v>spec. price for incoming energy</v>
-      </c>
-      <c r="L58" t="str">
-        <f t="shared" si="18"/>
-        <v>spec. price for outflowing energy</v>
-      </c>
-      <c r="M58" t="str">
-        <f t="shared" si="18"/>
-        <v>total price for incoming energy</v>
-      </c>
-      <c r="N58" t="str">
-        <f t="shared" si="18"/>
-        <v>total price for outflowing energy</v>
-      </c>
-      <c r="O58" t="str">
-        <f t="shared" si="18"/>
-        <v>quality share of energy (one column per type)</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="8"/>
+      <c r="G59" t="str">
+        <f t="shared" si="19"/>
+        <v>type of energy (electr., heat, etc.)</v>
+      </c>
+      <c r="H59" t="str">
+        <f t="shared" ref="H59:L59" si="20">_xlfn.XLOOKUP(H56,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <v>action to be undertaken for market</v>
+      </c>
+      <c r="I59" t="str">
+        <f t="shared" si="20"/>
+        <v>clearing type (ex-ante, ex-post)</v>
+      </c>
+      <c r="J59" t="str">
+        <f t="shared" si="20"/>
+        <v>clearing method (pda, etc.)</v>
+      </c>
+      <c r="K59" t="str">
+        <f t="shared" si="20"/>
+        <v>pricing method (uniform, etc.)</v>
+      </c>
+      <c r="L59" t="str">
+        <f t="shared" si="20"/>
+        <v>coupling method (above, below)</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="8"/>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A61" s="15" t="str">
+      <c r="B61" s="5"/>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A62" s="15" t="str">
         <f>$A$3</f>
         <v>Table</v>
       </c>
-      <c r="B61" s="15" t="str">
+      <c r="B62" s="15" t="str">
         <f>$B$3</f>
         <v>Section</v>
       </c>
-      <c r="C61" s="15" t="str">
+      <c r="C62" s="15" t="str">
         <f>$C$3</f>
         <v>Description</v>
       </c>
-      <c r="D61" s="15" t="str">
+      <c r="D62" s="15" t="str">
         <f>$D$3</f>
         <v>Class</v>
       </c>
-      <c r="E61" s="15" t="str">
+      <c r="E62" s="15" t="str">
         <f>$E$3</f>
         <v>Saved</v>
       </c>
     </row>
-    <row r="62" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="16" t="str">
+    <row r="63" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="16" t="str">
         <f>A6</f>
-        <v>meter_readings_cum</v>
-      </c>
-      <c r="B62" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A62,$A$4:$A$21,$B$4:$B$21)</f>
-        <v>Analyzer</v>
-      </c>
-      <c r="C62" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A62,$A$4:$A$21,$C$4:$C$21)</f>
-        <v>contains the meter readings at each timestamp</v>
-      </c>
-      <c r="D62" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A62,$A$4:$A$21,$D$4:$D$21)</f>
+        <v>market_transactions</v>
+      </c>
+      <c r="B63" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A63,$A$4:$A$22,$B$4:$B$22)</f>
+        <v>Executor</v>
+      </c>
+      <c r="C63" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A63,$A$4:$A$22,$C$4:$C$22)</f>
+        <v>contains all trades done in the markets</v>
+      </c>
+      <c r="D63" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A63,$A$4:$A$22,$D$4:$D$22)</f>
         <v>Markets</v>
       </c>
-      <c r="E62" s="5" t="b">
-        <f>_xlfn.XLOOKUP(A62,$A$4:$A$21,$E$4:$E$21)</f>
+      <c r="E63" s="5" t="b">
+        <f>_xlfn.XLOOKUP(A63,$A$4:$A$22,$E$4:$E$22)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A63"/>
-    </row>
     <row r="64" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>0</v>
-      </c>
-      <c r="B64" s="9" t="str">
+      <c r="A64"/>
+    </row>
+    <row r="65" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>0</v>
+      </c>
+      <c r="B65" s="9" t="str">
         <f>B26</f>
         <v>timestamp</v>
       </c>
-      <c r="C64" s="9" t="str">
+      <c r="C65" s="9" t="str">
+        <f>C26</f>
+        <v>timestep</v>
+      </c>
+      <c r="D65" s="9" t="str">
         <f>D26</f>
         <v>region</v>
       </c>
-      <c r="D64" s="9" t="str">
+      <c r="E65" s="9" t="str">
         <f>E26</f>
         <v>market</v>
       </c>
-      <c r="E64" s="9" t="str">
+      <c r="F65" s="9" t="str">
         <f>F26</f>
         <v>name</v>
       </c>
-      <c r="F64" s="9" t="str">
+      <c r="G65" s="9" t="str">
+        <f>G26</f>
+        <v>energy_type</v>
+      </c>
+      <c r="H65" s="9" t="str">
         <f>H26</f>
+        <v>type_transaction</v>
+      </c>
+      <c r="I65" s="9" t="str">
+        <f>I26</f>
         <v>id_agent</v>
       </c>
-      <c r="G64" s="9" t="str">
-        <f>K26</f>
-        <v>id_meter</v>
-      </c>
-      <c r="H64" s="9" t="str">
-        <f>M26</f>
+      <c r="J65" s="9" t="str">
+        <f>N26</f>
         <v>energy_in</v>
       </c>
-      <c r="I64" s="9" t="str">
-        <f>N26</f>
+      <c r="K65" s="9" t="str">
+        <f>O26</f>
         <v>energy_out</v>
       </c>
-    </row>
-    <row r="65" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="9" t="str">
+      <c r="L65" s="9" t="str">
+        <f>R26</f>
+        <v>price_pu_in</v>
+      </c>
+      <c r="M65" s="9" t="str">
+        <f>S26</f>
+        <v>price_pu_out</v>
+      </c>
+      <c r="N65" s="9" t="str">
+        <f>U26</f>
+        <v>price_in</v>
+      </c>
+      <c r="O65" s="9" t="str">
+        <f>V26</f>
+        <v>price_out</v>
+      </c>
+      <c r="P65" s="9" t="str">
+        <f>AB26</f>
+        <v>share_quality_XXX</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="9" t="str">
         <f>$A$27</f>
         <v>dtype</v>
       </c>
-      <c r="B65" s="3" t="str">
-        <f>_xlfn.XLOOKUP(B64,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="B66" s="3" t="str">
+        <f>_xlfn.XLOOKUP(B65,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>datetime</v>
       </c>
-      <c r="C65" s="3" t="str">
-        <f t="shared" ref="C65:E65" si="19">_xlfn.XLOOKUP(C64,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="C66" s="3" t="str">
+        <f t="shared" ref="C66:F66" si="21">_xlfn.XLOOKUP(C65,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <v>datetime</v>
+      </c>
+      <c r="D66" s="3" t="str">
+        <f t="shared" si="21"/>
         <v>categorical</v>
       </c>
-      <c r="D65" s="3" t="str">
-        <f t="shared" si="19"/>
+      <c r="E66" s="3" t="str">
+        <f t="shared" si="21"/>
         <v>categorical</v>
       </c>
-      <c r="E65" s="3" t="str">
-        <f t="shared" si="19"/>
+      <c r="F66" s="3" t="str">
+        <f t="shared" si="21"/>
         <v>categorical</v>
       </c>
-      <c r="F65" s="3" t="str">
-        <f t="shared" ref="F65:I65" si="20">_xlfn.XLOOKUP(F64,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="G66" s="3" t="str">
+        <f t="shared" ref="G66" si="22">_xlfn.XLOOKUP(G65,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
-      <c r="G65" s="3" t="str">
-        <f t="shared" si="20"/>
-        <v>str</v>
-      </c>
-      <c r="H65" s="3" t="str">
-        <f t="shared" si="20"/>
+      <c r="H66" s="3" t="str">
+        <f>_xlfn.XLOOKUP(H65,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <v>categorical</v>
+      </c>
+      <c r="I66" s="3" t="str">
+        <f>_xlfn.XLOOKUP(I65,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <v>categorical</v>
+      </c>
+      <c r="J66" s="3" t="str">
+        <f t="shared" ref="J66:P66" si="23">_xlfn.XLOOKUP(J65,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>uint64</v>
       </c>
-      <c r="I65" s="3" t="str">
-        <f t="shared" si="20"/>
+      <c r="K66" s="3" t="str">
+        <f t="shared" si="23"/>
         <v>uint64</v>
       </c>
-    </row>
-    <row r="66" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="9" t="str">
+      <c r="L66" s="3" t="str">
+        <f t="shared" si="23"/>
+        <v>int32</v>
+      </c>
+      <c r="M66" s="3" t="str">
+        <f t="shared" si="23"/>
+        <v>int32</v>
+      </c>
+      <c r="N66" s="3" t="str">
+        <f t="shared" si="23"/>
+        <v>int64</v>
+      </c>
+      <c r="O66" s="3" t="str">
+        <f t="shared" si="23"/>
+        <v>int64</v>
+      </c>
+      <c r="P66" s="3" t="str">
+        <f t="shared" si="23"/>
+        <v>int8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="9" t="str">
         <f>$A$28</f>
         <v>unit</v>
       </c>
-      <c r="B66" s="3" t="str">
-        <f>_xlfn.XLOOKUP(B64,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="B67" s="3" t="str">
+        <f>_xlfn.XLOOKUP(B65,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>s</v>
       </c>
-      <c r="C66" s="3" t="str">
-        <f t="shared" ref="C66:E66" si="21">_xlfn.XLOOKUP(C64,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="C67" s="3" t="str">
+        <f t="shared" ref="C67:F67" si="24">_xlfn.XLOOKUP(C65,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <v>s</v>
+      </c>
+      <c r="D67" s="3" t="str">
+        <f t="shared" si="24"/>
         <v>None</v>
       </c>
-      <c r="D66" s="3" t="str">
-        <f t="shared" si="21"/>
+      <c r="E67" s="3" t="str">
+        <f t="shared" si="24"/>
         <v>None</v>
       </c>
-      <c r="E66" s="3" t="str">
-        <f t="shared" si="21"/>
+      <c r="F67" s="3" t="str">
+        <f t="shared" si="24"/>
         <v>None</v>
       </c>
-      <c r="F66" s="3" t="str">
-        <f t="shared" ref="F66:I66" si="22">_xlfn.XLOOKUP(F64,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="G67" s="3" t="str">
+        <f t="shared" ref="G67" si="25">_xlfn.XLOOKUP(G65,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>None</v>
       </c>
-      <c r="G66" s="3" t="str">
-        <f t="shared" si="22"/>
+      <c r="H67" s="3" t="str">
+        <f t="shared" ref="H67" si="26">_xlfn.XLOOKUP(H65,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>None</v>
       </c>
-      <c r="H66" s="3" t="str">
-        <f t="shared" si="22"/>
+      <c r="I67" s="3" t="str">
+        <f>_xlfn.XLOOKUP(I65,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <v>None</v>
+      </c>
+      <c r="J67" s="3" t="str">
+        <f t="shared" ref="J67:P67" si="27">_xlfn.XLOOKUP(J65,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>Wh</v>
       </c>
-      <c r="I66" s="3" t="str">
-        <f t="shared" si="22"/>
+      <c r="K67" s="3" t="str">
+        <f t="shared" si="27"/>
         <v>Wh</v>
       </c>
-    </row>
-    <row r="67" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="9" t="str">
+      <c r="L67" s="3" t="str">
+        <f t="shared" si="27"/>
+        <v>€e7/Wh</v>
+      </c>
+      <c r="M67" s="3" t="str">
+        <f t="shared" si="27"/>
+        <v>€e7/Wh</v>
+      </c>
+      <c r="N67" s="3" t="str">
+        <f t="shared" si="27"/>
+        <v>€e7</v>
+      </c>
+      <c r="O67" s="3" t="str">
+        <f t="shared" si="27"/>
+        <v>€e7</v>
+      </c>
+      <c r="P67" s="3" t="str">
+        <f t="shared" si="27"/>
+        <v>0-100</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="9" t="str">
         <f>$A$29</f>
         <v>description</v>
       </c>
-      <c r="B67" t="str">
-        <f>_xlfn.XLOOKUP(B64,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+      <c r="B68" t="str">
+        <f>_xlfn.XLOOKUP(B65,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>current timestamp</v>
       </c>
-      <c r="C67" t="str">
-        <f t="shared" ref="C67:E67" si="23">_xlfn.XLOOKUP(C64,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+      <c r="C68" t="str">
+        <f t="shared" ref="C68:F68" si="28">_xlfn.XLOOKUP(C65,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <v>timestep (can be in future)</v>
+      </c>
+      <c r="D68" t="str">
+        <f t="shared" si="28"/>
         <v>region in which the market is</v>
       </c>
-      <c r="D67" t="str">
-        <f t="shared" si="23"/>
+      <c r="E68" t="str">
+        <f t="shared" si="28"/>
         <v>type of market</v>
       </c>
-      <c r="E67" t="str">
-        <f t="shared" si="23"/>
+      <c r="F68" t="str">
+        <f t="shared" si="28"/>
         <v>name of the market</v>
       </c>
-      <c r="F67" t="str">
-        <f t="shared" ref="F67:I67" si="24">_xlfn.XLOOKUP(F64,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+      <c r="G68" t="str">
+        <f t="shared" ref="G68" si="29">_xlfn.XLOOKUP(G65,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <v>type of energy (electr., heat, etc.)</v>
+      </c>
+      <c r="H68" t="str">
+        <f t="shared" ref="H68" si="30">_xlfn.XLOOKUP(H65,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <v>source of the costs/profits (e.g. Market, levies, balancing)</v>
+      </c>
+      <c r="I68" t="str">
+        <f>_xlfn.XLOOKUP(I65,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>agent id (also serves as main meter)</v>
       </c>
-      <c r="G67" t="str">
-        <f t="shared" si="24"/>
-        <v>id of the (sub-)meter</v>
-      </c>
-      <c r="H67" t="str">
-        <f t="shared" si="24"/>
+      <c r="J68" t="str">
+        <f t="shared" ref="J68:P68" si="31">_xlfn.XLOOKUP(J65,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>energy going into the meter</v>
       </c>
-      <c r="I67" t="str">
-        <f t="shared" si="24"/>
+      <c r="K68" t="str">
+        <f t="shared" si="31"/>
         <v>energy going out of the meter</v>
       </c>
-    </row>
-    <row r="68" spans="1:9" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="8"/>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="15" t="str">
+      <c r="L68" t="str">
+        <f t="shared" si="31"/>
+        <v>spec. price for incoming energy</v>
+      </c>
+      <c r="M68" t="str">
+        <f t="shared" si="31"/>
+        <v>spec. price for outflowing energy</v>
+      </c>
+      <c r="N68" t="str">
+        <f t="shared" si="31"/>
+        <v>total price for incoming energy</v>
+      </c>
+      <c r="O68" t="str">
+        <f t="shared" si="31"/>
+        <v>total price for outflowing energy</v>
+      </c>
+      <c r="P68" t="str">
+        <f t="shared" si="31"/>
+        <v>quality share of energy (one column per type)</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="8"/>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A71" s="15" t="str">
         <f>$A$3</f>
         <v>Table</v>
       </c>
-      <c r="B70" s="15" t="str">
+      <c r="B71" s="15" t="str">
         <f>$B$3</f>
         <v>Section</v>
       </c>
-      <c r="C70" s="15" t="str">
+      <c r="C71" s="15" t="str">
         <f>$C$3</f>
         <v>Description</v>
       </c>
-      <c r="D70" s="15" t="str">
+      <c r="D71" s="15" t="str">
         <f>$D$3</f>
         <v>Class</v>
       </c>
-      <c r="E70" s="15" t="str">
+      <c r="E71" s="15" t="str">
         <f>$E$3</f>
         <v>Saved</v>
       </c>
     </row>
-    <row r="71" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="16" t="str">
+    <row r="72" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="16" t="str">
         <f>A7</f>
-        <v>meter_readings_delta</v>
-      </c>
-      <c r="B71" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A71,$A$4:$A$21,$B$4:$B$21)</f>
+        <v>meter_readings_cum</v>
+      </c>
+      <c r="B72" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A72,$A$4:$A$22,$B$4:$B$22)</f>
         <v>Analyzer</v>
       </c>
-      <c r="C71" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A71,$A$4:$A$21,$C$4:$C$21)</f>
-        <v>contains the meter delta readings at each timestamp</v>
-      </c>
-      <c r="D71" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A71,$A$4:$A$21,$D$4:$D$21)</f>
+      <c r="C72" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A72,$A$4:$A$22,$C$4:$C$22)</f>
+        <v>contains the meter readings at each timestamp</v>
+      </c>
+      <c r="D72" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A72,$A$4:$A$22,$D$4:$D$22)</f>
         <v>Markets</v>
       </c>
-      <c r="E71" s="5" t="b">
-        <f>_xlfn.XLOOKUP(A71,$A$4:$A$21,$E$4:$E$21)</f>
+      <c r="E72" s="5" t="b">
+        <f>_xlfn.XLOOKUP(A72,$A$4:$A$22,$E$4:$E$22)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A72"/>
-    </row>
-    <row r="73" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>0</v>
-      </c>
-      <c r="B73" s="9" t="str">
+    <row r="73" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A73"/>
+    </row>
+    <row r="74" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>0</v>
+      </c>
+      <c r="B74" s="9" t="str">
         <f>B26</f>
         <v>timestamp</v>
       </c>
-      <c r="C73" s="9" t="str">
+      <c r="C74" s="9" t="str">
         <f>D26</f>
         <v>region</v>
       </c>
-      <c r="D73" s="9" t="str">
+      <c r="D74" s="9" t="str">
         <f>E26</f>
         <v>market</v>
       </c>
-      <c r="E73" s="9" t="str">
+      <c r="E74" s="9" t="str">
         <f>F26</f>
         <v>name</v>
       </c>
-      <c r="F73" s="9" t="str">
-        <f>H26</f>
+      <c r="F74" s="9" t="str">
+        <f>I26</f>
         <v>id_agent</v>
       </c>
-      <c r="G73" s="9" t="str">
-        <f>K26</f>
+      <c r="G74" s="9" t="str">
+        <f>L26</f>
         <v>id_meter</v>
       </c>
-      <c r="H73" s="9" t="str">
-        <f>M26</f>
+      <c r="H74" s="9" t="str">
+        <f>N26</f>
         <v>energy_in</v>
       </c>
-      <c r="I73" s="9" t="str">
-        <f>N26</f>
+      <c r="I74" s="9" t="str">
+        <f>O26</f>
         <v>energy_out</v>
       </c>
     </row>
-    <row r="74" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="9" t="str">
+    <row r="75" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="9" t="str">
         <f>$A$27</f>
         <v>dtype</v>
       </c>
-      <c r="B74" s="3" t="str">
-        <f>_xlfn.XLOOKUP(B73,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="B75" s="3" t="str">
+        <f>_xlfn.XLOOKUP(B74,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>datetime</v>
       </c>
-      <c r="C74" s="3" t="str">
-        <f t="shared" ref="C74:I74" si="25">_xlfn.XLOOKUP(C73,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="C75" s="3" t="str">
+        <f t="shared" ref="C75:E75" si="32">_xlfn.XLOOKUP(C74,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
-      <c r="D74" s="3" t="str">
-        <f t="shared" si="25"/>
+      <c r="D75" s="3" t="str">
+        <f t="shared" si="32"/>
         <v>categorical</v>
       </c>
-      <c r="E74" s="3" t="str">
-        <f t="shared" si="25"/>
+      <c r="E75" s="3" t="str">
+        <f t="shared" si="32"/>
         <v>categorical</v>
       </c>
-      <c r="F74" s="3" t="str">
-        <f t="shared" si="25"/>
+      <c r="F75" s="3" t="str">
+        <f t="shared" ref="F75:I75" si="33">_xlfn.XLOOKUP(F74,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
-      <c r="G74" s="3" t="str">
-        <f t="shared" si="25"/>
+      <c r="G75" s="3" t="str">
+        <f t="shared" si="33"/>
         <v>str</v>
       </c>
-      <c r="H74" s="3" t="str">
-        <f t="shared" si="25"/>
+      <c r="H75" s="3" t="str">
+        <f t="shared" si="33"/>
         <v>uint64</v>
       </c>
-      <c r="I74" s="3" t="str">
-        <f t="shared" si="25"/>
+      <c r="I75" s="3" t="str">
+        <f t="shared" si="33"/>
         <v>uint64</v>
       </c>
     </row>
-    <row r="75" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="9" t="str">
+    <row r="76" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="9" t="str">
         <f>$A$28</f>
         <v>unit</v>
       </c>
-      <c r="B75" s="3" t="str">
-        <f>_xlfn.XLOOKUP(B73,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="B76" s="3" t="str">
+        <f>_xlfn.XLOOKUP(B74,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>s</v>
       </c>
-      <c r="C75" s="3" t="str">
-        <f t="shared" ref="C75:I75" si="26">_xlfn.XLOOKUP(C73,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="C76" s="3" t="str">
+        <f t="shared" ref="C76:E76" si="34">_xlfn.XLOOKUP(C74,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>None</v>
       </c>
-      <c r="D75" s="3" t="str">
-        <f t="shared" si="26"/>
+      <c r="D76" s="3" t="str">
+        <f t="shared" si="34"/>
         <v>None</v>
       </c>
-      <c r="E75" s="3" t="str">
-        <f t="shared" si="26"/>
+      <c r="E76" s="3" t="str">
+        <f t="shared" si="34"/>
         <v>None</v>
       </c>
-      <c r="F75" s="3" t="str">
-        <f t="shared" si="26"/>
+      <c r="F76" s="3" t="str">
+        <f t="shared" ref="F76:I76" si="35">_xlfn.XLOOKUP(F74,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>None</v>
       </c>
-      <c r="G75" s="3" t="str">
-        <f t="shared" si="26"/>
+      <c r="G76" s="3" t="str">
+        <f t="shared" si="35"/>
         <v>None</v>
       </c>
-      <c r="H75" s="3" t="str">
-        <f t="shared" si="26"/>
+      <c r="H76" s="3" t="str">
+        <f t="shared" si="35"/>
         <v>Wh</v>
       </c>
-      <c r="I75" s="3" t="str">
-        <f t="shared" si="26"/>
+      <c r="I76" s="3" t="str">
+        <f t="shared" si="35"/>
         <v>Wh</v>
       </c>
     </row>
-    <row r="76" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="9" t="str">
+    <row r="77" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="9" t="str">
         <f>$A$29</f>
         <v>description</v>
       </c>
-      <c r="B76" t="str">
-        <f>_xlfn.XLOOKUP(B73,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+      <c r="B77" t="str">
+        <f>_xlfn.XLOOKUP(B74,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>current timestamp</v>
       </c>
-      <c r="C76" t="str">
-        <f t="shared" ref="C76:I76" si="27">_xlfn.XLOOKUP(C73,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+      <c r="C77" t="str">
+        <f t="shared" ref="C77:E77" si="36">_xlfn.XLOOKUP(C74,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>region in which the market is</v>
       </c>
-      <c r="D76" t="str">
-        <f t="shared" si="27"/>
+      <c r="D77" t="str">
+        <f t="shared" si="36"/>
         <v>type of market</v>
       </c>
-      <c r="E76" t="str">
-        <f t="shared" si="27"/>
+      <c r="E77" t="str">
+        <f t="shared" si="36"/>
         <v>name of the market</v>
       </c>
-      <c r="F76" t="str">
-        <f t="shared" si="27"/>
+      <c r="F77" t="str">
+        <f t="shared" ref="F77:I77" si="37">_xlfn.XLOOKUP(F74,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>agent id (also serves as main meter)</v>
       </c>
-      <c r="G76" t="str">
-        <f t="shared" si="27"/>
+      <c r="G77" t="str">
+        <f t="shared" si="37"/>
         <v>id of the (sub-)meter</v>
       </c>
-      <c r="H76" t="str">
-        <f t="shared" si="27"/>
+      <c r="H77" t="str">
+        <f t="shared" si="37"/>
         <v>energy going into the meter</v>
       </c>
-      <c r="I76" t="str">
-        <f t="shared" si="27"/>
+      <c r="I77" t="str">
+        <f t="shared" si="37"/>
         <v>energy going out of the meter</v>
       </c>
     </row>
-    <row r="77" spans="1:9" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="8"/>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" s="15" t="str">
+    <row r="78" spans="1:16" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="8"/>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A80" s="15" t="str">
         <f>$A$3</f>
         <v>Table</v>
       </c>
-      <c r="B79" s="15" t="str">
+      <c r="B80" s="15" t="str">
         <f>$B$3</f>
         <v>Section</v>
       </c>
-      <c r="C79" s="15" t="str">
+      <c r="C80" s="15" t="str">
         <f>$C$3</f>
         <v>Description</v>
       </c>
-      <c r="D79" s="15" t="str">
+      <c r="D80" s="15" t="str">
         <f>$D$3</f>
         <v>Class</v>
       </c>
-      <c r="E79" s="15" t="str">
+      <c r="E80" s="15" t="str">
         <f>$E$3</f>
         <v>Saved</v>
       </c>
     </row>
-    <row r="80" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="B80" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A80,$A$4:$A$21,$B$4:$B$21)</f>
+    <row r="81" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="16" t="str">
+        <f>A8</f>
+        <v>meter_readings_delta</v>
+      </c>
+      <c r="B81" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A81,$A$4:$A$22,$B$4:$B$22)</f>
         <v>Analyzer</v>
       </c>
-      <c r="C80" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A80,$A$4:$A$21,$C$4:$C$21)</f>
-        <v>contains the prices and quantities sold by the retailer (can be extracted from market transactions)</v>
-      </c>
-      <c r="D80" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A80,$A$4:$A$21,$D$4:$D$21)</f>
+      <c r="C81" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A81,$A$4:$A$22,$C$4:$C$22)</f>
+        <v>contains the meter delta readings at each timestamp</v>
+      </c>
+      <c r="D81" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A81,$A$4:$A$22,$D$4:$D$22)</f>
         <v>Markets</v>
       </c>
-      <c r="E80" s="5" t="b">
-        <f>_xlfn.XLOOKUP(A80,$A$4:$A$21,$E$4:$E$21)</f>
+      <c r="E81" s="5" t="b">
+        <f>_xlfn.XLOOKUP(A81,$A$4:$A$22,$E$4:$E$22)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A81"/>
-    </row>
-    <row r="82" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>0</v>
-      </c>
-      <c r="B82" t="str">
-        <f t="shared" ref="B82:G82" si="28">B26</f>
+    <row r="82" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A82"/>
+    </row>
+    <row r="83" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>0</v>
+      </c>
+      <c r="B83" s="9" t="str">
+        <f>B26</f>
         <v>timestamp</v>
       </c>
-      <c r="C82" t="str">
-        <f t="shared" si="28"/>
-        <v>timestep</v>
-      </c>
-      <c r="D82" t="str">
-        <f t="shared" si="28"/>
+      <c r="C83" s="9" t="str">
+        <f>D26</f>
         <v>region</v>
       </c>
-      <c r="E82" t="str">
-        <f t="shared" si="28"/>
+      <c r="D83" s="9" t="str">
+        <f>E26</f>
         <v>market</v>
       </c>
-      <c r="F82" t="str">
-        <f t="shared" si="28"/>
+      <c r="E83" s="9" t="str">
+        <f>F26</f>
         <v>name</v>
       </c>
-      <c r="G82" s="9" t="str">
-        <f t="shared" si="28"/>
-        <v>type_transaction</v>
-      </c>
-      <c r="H82" s="9" t="str">
-        <f>M26</f>
+      <c r="F83" s="9" t="str">
+        <f>I26</f>
+        <v>id_agent</v>
+      </c>
+      <c r="G83" s="9" t="str">
+        <f>L26</f>
+        <v>id_meter</v>
+      </c>
+      <c r="H83" s="9" t="str">
+        <f>N26</f>
         <v>energy_in</v>
       </c>
-      <c r="I82" s="9" t="str">
-        <f>N26</f>
+      <c r="I83" s="9" t="str">
+        <f>O26</f>
         <v>energy_out</v>
       </c>
-      <c r="J82" s="9" t="str">
-        <f>Q26</f>
-        <v>price_pu_in</v>
-      </c>
-      <c r="K82" s="9" t="str">
-        <f>R26</f>
-        <v>price_pu_out</v>
-      </c>
-      <c r="L82" s="9" t="str">
-        <f>T26</f>
-        <v>price_in</v>
-      </c>
-      <c r="M82" s="9" t="str">
-        <f>U26</f>
-        <v>price_out</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="9" t="str">
+    </row>
+    <row r="84" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="9" t="str">
         <f>$A$27</f>
         <v>dtype</v>
       </c>
-      <c r="B83" s="3" t="str">
-        <f>_xlfn.XLOOKUP(B82,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="B84" s="3" t="str">
+        <f>_xlfn.XLOOKUP(B83,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>datetime</v>
       </c>
-      <c r="C83" s="3" t="str">
-        <f t="shared" ref="C83" si="29">_xlfn.XLOOKUP(C82,$B$26:$XFD$26,$B$27:$XFD$27)</f>
-        <v>datetime</v>
-      </c>
-      <c r="D83" s="3" t="str">
-        <f t="shared" ref="D83" si="30">_xlfn.XLOOKUP(D82,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="C84" s="3" t="str">
+        <f t="shared" ref="C84:I84" si="38">_xlfn.XLOOKUP(C83,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
-      <c r="E83" s="3" t="str">
-        <f t="shared" ref="E83" si="31">_xlfn.XLOOKUP(E82,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="D84" s="3" t="str">
+        <f t="shared" si="38"/>
         <v>categorical</v>
       </c>
-      <c r="F83" s="3" t="str">
-        <f t="shared" ref="F83" si="32">_xlfn.XLOOKUP(F82,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="E84" s="3" t="str">
+        <f t="shared" si="38"/>
         <v>categorical</v>
       </c>
-      <c r="G83" s="3" t="str">
-        <f t="shared" ref="G83" si="33">_xlfn.XLOOKUP(G82,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="F84" s="3" t="str">
+        <f t="shared" si="38"/>
         <v>categorical</v>
       </c>
-      <c r="H83" s="3" t="str">
-        <f t="shared" ref="H83" si="34">_xlfn.XLOOKUP(H82,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="G84" s="3" t="str">
+        <f t="shared" si="38"/>
+        <v>str</v>
+      </c>
+      <c r="H84" s="3" t="str">
+        <f t="shared" si="38"/>
         <v>uint64</v>
       </c>
-      <c r="I83" s="3" t="str">
-        <f t="shared" ref="I83" si="35">_xlfn.XLOOKUP(I82,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="I84" s="3" t="str">
+        <f t="shared" si="38"/>
         <v>uint64</v>
       </c>
-      <c r="J83" s="3" t="str">
-        <f t="shared" ref="J83" si="36">_xlfn.XLOOKUP(J82,$B$26:$XFD$26,$B$27:$XFD$27)</f>
-        <v>int32</v>
-      </c>
-      <c r="K83" s="3" t="str">
-        <f t="shared" ref="K83" si="37">_xlfn.XLOOKUP(K82,$B$26:$XFD$26,$B$27:$XFD$27)</f>
-        <v>int32</v>
-      </c>
-      <c r="L83" s="3" t="str">
-        <f t="shared" ref="L83" si="38">_xlfn.XLOOKUP(L82,$B$26:$XFD$26,$B$27:$XFD$27)</f>
-        <v>int64</v>
-      </c>
-      <c r="M83" s="3" t="str">
-        <f t="shared" ref="M83" si="39">_xlfn.XLOOKUP(M82,$B$26:$XFD$26,$B$27:$XFD$27)</f>
-        <v>int64</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="9" t="str">
+    </row>
+    <row r="85" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="9" t="str">
         <f>$A$28</f>
         <v>unit</v>
       </c>
-      <c r="B84" s="3" t="str">
-        <f>_xlfn.XLOOKUP(B82,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="B85" s="3" t="str">
+        <f>_xlfn.XLOOKUP(B83,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>s</v>
       </c>
-      <c r="C84" s="3" t="str">
-        <f t="shared" ref="C84:I84" si="40">_xlfn.XLOOKUP(C82,$B$26:$XFD$26,$B$28:$XFD$28)</f>
-        <v>s</v>
-      </c>
-      <c r="D84" s="3" t="str">
-        <f t="shared" si="40"/>
+      <c r="C85" s="3" t="str">
+        <f t="shared" ref="C85:I85" si="39">_xlfn.XLOOKUP(C83,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>None</v>
       </c>
-      <c r="E84" s="3" t="str">
-        <f t="shared" si="40"/>
+      <c r="D85" s="3" t="str">
+        <f t="shared" si="39"/>
         <v>None</v>
       </c>
-      <c r="F84" s="3" t="str">
-        <f t="shared" si="40"/>
+      <c r="E85" s="3" t="str">
+        <f t="shared" si="39"/>
         <v>None</v>
       </c>
-      <c r="G84" s="3" t="str">
-        <f t="shared" si="40"/>
+      <c r="F85" s="3" t="str">
+        <f t="shared" si="39"/>
         <v>None</v>
       </c>
-      <c r="H84" s="3" t="str">
-        <f t="shared" si="40"/>
+      <c r="G85" s="3" t="str">
+        <f t="shared" si="39"/>
+        <v>None</v>
+      </c>
+      <c r="H85" s="3" t="str">
+        <f t="shared" si="39"/>
         <v>Wh</v>
       </c>
-      <c r="I84" s="3" t="str">
-        <f t="shared" si="40"/>
+      <c r="I85" s="3" t="str">
+        <f t="shared" si="39"/>
         <v>Wh</v>
       </c>
-      <c r="J84" s="3" t="str">
-        <f t="shared" ref="J84:M84" si="41">_xlfn.XLOOKUP(J82,$B$26:$XFD$26,$B$28:$XFD$28)</f>
-        <v>€e7/Wh</v>
-      </c>
-      <c r="K84" s="3" t="str">
-        <f t="shared" si="41"/>
-        <v>€e7/Wh</v>
-      </c>
-      <c r="L84" s="3" t="str">
-        <f t="shared" si="41"/>
-        <v>€e7</v>
-      </c>
-      <c r="M84" s="3" t="str">
-        <f t="shared" si="41"/>
-        <v>€e7</v>
-      </c>
-    </row>
-    <row r="85" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="9" t="str">
+    </row>
+    <row r="86" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="9" t="str">
         <f>$A$29</f>
         <v>description</v>
       </c>
-      <c r="B85" t="str">
-        <f>_xlfn.XLOOKUP(B82,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+      <c r="B86" t="str">
+        <f>_xlfn.XLOOKUP(B83,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>current timestamp</v>
       </c>
-      <c r="C85" t="str">
-        <f t="shared" ref="C85:I85" si="42">_xlfn.XLOOKUP(C82,$B$26:$XFD$26,$B$29:$XFD$29)</f>
-        <v>timestep (can be in future)</v>
-      </c>
-      <c r="D85" t="str">
-        <f t="shared" si="42"/>
+      <c r="C86" t="str">
+        <f t="shared" ref="C86:I86" si="40">_xlfn.XLOOKUP(C83,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>region in which the market is</v>
       </c>
-      <c r="E85" t="str">
-        <f t="shared" si="42"/>
+      <c r="D86" t="str">
+        <f t="shared" si="40"/>
         <v>type of market</v>
       </c>
-      <c r="F85" t="str">
-        <f t="shared" si="42"/>
+      <c r="E86" t="str">
+        <f t="shared" si="40"/>
         <v>name of the market</v>
       </c>
-      <c r="G85" t="str">
-        <f t="shared" si="42"/>
-        <v>source of the costs/profits (e.g. Market, levies, balancing)</v>
-      </c>
-      <c r="H85" t="str">
-        <f t="shared" si="42"/>
+      <c r="F86" t="str">
+        <f t="shared" si="40"/>
+        <v>agent id (also serves as main meter)</v>
+      </c>
+      <c r="G86" t="str">
+        <f t="shared" si="40"/>
+        <v>id of the (sub-)meter</v>
+      </c>
+      <c r="H86" t="str">
+        <f t="shared" si="40"/>
         <v>energy going into the meter</v>
       </c>
-      <c r="I85" t="str">
-        <f t="shared" si="42"/>
+      <c r="I86" t="str">
+        <f t="shared" si="40"/>
         <v>energy going out of the meter</v>
       </c>
-      <c r="J85" t="str">
-        <f t="shared" ref="J85:M85" si="43">_xlfn.XLOOKUP(J82,$B$26:$XFD$26,$B$29:$XFD$29)</f>
-        <v>spec. price for incoming energy</v>
-      </c>
-      <c r="K85" t="str">
-        <f t="shared" si="43"/>
-        <v>spec. price for outflowing energy</v>
-      </c>
-      <c r="L85" t="str">
-        <f t="shared" si="43"/>
-        <v>total price for incoming energy</v>
-      </c>
-      <c r="M85" t="str">
-        <f t="shared" si="43"/>
-        <v>total price for outflowing energy</v>
-      </c>
-    </row>
-    <row r="86" spans="1:14" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="8"/>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A88" s="15" t="str">
+    </row>
+    <row r="87" spans="1:13" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="8"/>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" s="15" t="str">
         <f>$A$3</f>
         <v>Table</v>
       </c>
-      <c r="B88" s="15" t="str">
+      <c r="B89" s="15" t="str">
         <f>$B$3</f>
         <v>Section</v>
       </c>
-      <c r="C88" s="15" t="str">
+      <c r="C89" s="15" t="str">
         <f>$C$3</f>
         <v>Description</v>
       </c>
-      <c r="D88" s="15" t="str">
+      <c r="D89" s="15" t="str">
         <f>$D$3</f>
         <v>Class</v>
       </c>
-      <c r="E88" s="15" t="str">
+      <c r="E89" s="15" t="str">
         <f>$E$3</f>
         <v>Saved</v>
       </c>
     </row>
-    <row r="89" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="B89" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A89,$A$4:$A$21,$B$4:$B$21)</f>
+    <row r="90" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B90" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A90,$A$4:$A$22,$B$4:$B$22)</f>
         <v>Analyzer</v>
       </c>
-      <c r="C89" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A89,$A$4:$A$21,$C$4:$C$21)</f>
-        <v>contains summary of each timestamp</v>
-      </c>
-      <c r="D89" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A89,$A$4:$A$21,$D$4:$D$21)</f>
+      <c r="C90" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A90,$A$4:$A$22,$C$4:$C$22)</f>
+        <v>contains the prices and quantities sold by the retailer (can be extracted from market transactions)</v>
+      </c>
+      <c r="D90" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A90,$A$4:$A$22,$D$4:$D$22)</f>
         <v>Markets</v>
       </c>
-      <c r="E89" s="5" t="b">
-        <f>_xlfn.XLOOKUP(A89,$A$4:$A$21,$E$4:$E$21)</f>
+      <c r="E90" s="5" t="b">
+        <f>_xlfn.XLOOKUP(A90,$A$4:$A$22,$E$4:$E$22)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A90"/>
-    </row>
-    <row r="91" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>0</v>
-      </c>
-      <c r="B91" t="str">
+    <row r="91" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A91"/>
+    </row>
+    <row r="92" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>0</v>
+      </c>
+      <c r="B92" t="str">
         <f>B26</f>
         <v>timestamp</v>
       </c>
-      <c r="C91" t="str">
+      <c r="C92" t="str">
+        <f>C26</f>
+        <v>timestep</v>
+      </c>
+      <c r="D92" t="str">
         <f>D26</f>
         <v>region</v>
       </c>
-      <c r="D91" t="str">
-        <f t="shared" ref="D91:E91" si="44">E26</f>
+      <c r="E92" t="str">
+        <f>E26</f>
         <v>market</v>
       </c>
-      <c r="E91" t="str">
-        <f t="shared" si="44"/>
+      <c r="F92" t="str">
+        <f>F26</f>
         <v>name</v>
       </c>
-      <c r="F91" s="9" t="str">
-        <f>G26</f>
+      <c r="G92" s="9" t="str">
+        <f>H26</f>
         <v>type_transaction</v>
       </c>
-      <c r="G91" t="str">
-        <f>H26</f>
-        <v>id_agent</v>
-      </c>
-      <c r="H91" s="9" t="str">
-        <f>M26</f>
+      <c r="H92" s="9" t="str">
+        <f>N26</f>
         <v>energy_in</v>
       </c>
-      <c r="I91" s="9" t="str">
-        <f>N26</f>
+      <c r="I92" s="9" t="str">
+        <f>O26</f>
         <v>energy_out</v>
       </c>
-      <c r="J91" s="9" t="str">
-        <f>Q26</f>
+      <c r="J92" s="9" t="str">
+        <f>R26</f>
         <v>price_pu_in</v>
       </c>
-      <c r="K91" s="9" t="str">
-        <f>R26</f>
+      <c r="K92" s="9" t="str">
+        <f>S26</f>
         <v>price_pu_out</v>
       </c>
-      <c r="L91" s="9" t="str">
-        <f>T26</f>
+      <c r="L92" s="9" t="str">
+        <f>U26</f>
         <v>price_in</v>
       </c>
-      <c r="M91" s="9" t="str">
-        <f>U26</f>
+      <c r="M92" s="9" t="str">
+        <f>V26</f>
         <v>price_out</v>
       </c>
-      <c r="N91" s="9" t="str">
-        <f>AA26</f>
-        <v>share_quality_XXX</v>
-      </c>
-    </row>
-    <row r="92" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="9" t="str">
+    </row>
+    <row r="93" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="9" t="str">
         <f>$A$27</f>
         <v>dtype</v>
       </c>
-      <c r="B92" s="3" t="str">
-        <f>_xlfn.XLOOKUP(B91,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="B93" s="3" t="str">
+        <f>_xlfn.XLOOKUP(B92,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>datetime</v>
       </c>
-      <c r="C92" s="3" t="str">
-        <f t="shared" ref="C92" si="45">_xlfn.XLOOKUP(C91,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="C93" s="3" t="str">
+        <f t="shared" ref="C93" si="41">_xlfn.XLOOKUP(C92,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <v>datetime</v>
+      </c>
+      <c r="D93" s="3" t="str">
+        <f t="shared" ref="D93" si="42">_xlfn.XLOOKUP(D92,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
-      <c r="D92" s="3" t="str">
-        <f t="shared" ref="D92" si="46">_xlfn.XLOOKUP(D91,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="E93" s="3" t="str">
+        <f t="shared" ref="E93" si="43">_xlfn.XLOOKUP(E92,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
-      <c r="E92" s="3" t="str">
-        <f t="shared" ref="E92" si="47">_xlfn.XLOOKUP(E91,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="F93" s="3" t="str">
+        <f t="shared" ref="F93" si="44">_xlfn.XLOOKUP(F92,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
-      <c r="F92" s="3" t="str">
-        <f t="shared" ref="F92" si="48">_xlfn.XLOOKUP(F91,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="G93" s="3" t="str">
+        <f t="shared" ref="G93" si="45">_xlfn.XLOOKUP(G92,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
-      <c r="G92" s="3" t="str">
-        <f t="shared" ref="G92" si="49">_xlfn.XLOOKUP(G91,$B$26:$XFD$26,$B$27:$XFD$27)</f>
-        <v>categorical</v>
-      </c>
-      <c r="H92" s="3" t="str">
-        <f t="shared" ref="H92" si="50">_xlfn.XLOOKUP(H91,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="H93" s="3" t="str">
+        <f t="shared" ref="H93" si="46">_xlfn.XLOOKUP(H92,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>uint64</v>
       </c>
-      <c r="I92" s="3" t="str">
-        <f t="shared" ref="I92" si="51">_xlfn.XLOOKUP(I91,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="I93" s="3" t="str">
+        <f t="shared" ref="I93" si="47">_xlfn.XLOOKUP(I92,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>uint64</v>
       </c>
-      <c r="J92" s="3" t="str">
-        <f t="shared" ref="J92" si="52">_xlfn.XLOOKUP(J91,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="J93" s="3" t="str">
+        <f t="shared" ref="J93" si="48">_xlfn.XLOOKUP(J92,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>int32</v>
       </c>
-      <c r="K92" s="3" t="str">
-        <f t="shared" ref="K92" si="53">_xlfn.XLOOKUP(K91,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="K93" s="3" t="str">
+        <f t="shared" ref="K93" si="49">_xlfn.XLOOKUP(K92,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>int32</v>
       </c>
-      <c r="L92" s="3" t="str">
-        <f t="shared" ref="L92" si="54">_xlfn.XLOOKUP(L91,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="L93" s="3" t="str">
+        <f t="shared" ref="L93" si="50">_xlfn.XLOOKUP(L92,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>int64</v>
       </c>
-      <c r="M92" s="3" t="str">
-        <f t="shared" ref="M92:N92" si="55">_xlfn.XLOOKUP(M91,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="M93" s="3" t="str">
+        <f t="shared" ref="M93" si="51">_xlfn.XLOOKUP(M92,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>int64</v>
       </c>
-      <c r="N92" s="3" t="str">
-        <f t="shared" si="55"/>
-        <v>int8</v>
-      </c>
-    </row>
-    <row r="93" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="9" t="str">
+    </row>
+    <row r="94" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="9" t="str">
         <f>$A$28</f>
         <v>unit</v>
       </c>
-      <c r="B93" s="3" t="str">
-        <f>_xlfn.XLOOKUP(B91,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="B94" s="3" t="str">
+        <f>_xlfn.XLOOKUP(B92,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>s</v>
       </c>
-      <c r="C93" s="3" t="str">
-        <f t="shared" ref="C93:E93" si="56">_xlfn.XLOOKUP(C91,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="C94" s="3" t="str">
+        <f t="shared" ref="C94:I94" si="52">_xlfn.XLOOKUP(C92,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <v>s</v>
+      </c>
+      <c r="D94" s="3" t="str">
+        <f t="shared" si="52"/>
         <v>None</v>
       </c>
-      <c r="D93" s="3" t="str">
-        <f t="shared" si="56"/>
+      <c r="E94" s="3" t="str">
+        <f t="shared" si="52"/>
         <v>None</v>
       </c>
-      <c r="E93" s="3" t="str">
-        <f t="shared" si="56"/>
+      <c r="F94" s="3" t="str">
+        <f t="shared" si="52"/>
         <v>None</v>
       </c>
-      <c r="F93" s="3" t="str">
-        <f t="shared" ref="F93:M93" si="57">_xlfn.XLOOKUP(F91,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="G94" s="3" t="str">
+        <f t="shared" si="52"/>
         <v>None</v>
       </c>
-      <c r="G93" s="3" t="str">
-        <f t="shared" si="57"/>
-        <v>None</v>
-      </c>
-      <c r="H93" s="3" t="str">
-        <f t="shared" si="57"/>
+      <c r="H94" s="3" t="str">
+        <f t="shared" si="52"/>
         <v>Wh</v>
       </c>
-      <c r="I93" s="3" t="str">
-        <f t="shared" si="57"/>
+      <c r="I94" s="3" t="str">
+        <f t="shared" si="52"/>
         <v>Wh</v>
       </c>
-      <c r="J93" s="3" t="str">
-        <f t="shared" si="57"/>
+      <c r="J94" s="3" t="str">
+        <f t="shared" ref="J94:M94" si="53">_xlfn.XLOOKUP(J92,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>€e7/Wh</v>
       </c>
-      <c r="K93" s="3" t="str">
-        <f t="shared" si="57"/>
+      <c r="K94" s="3" t="str">
+        <f t="shared" si="53"/>
         <v>€e7/Wh</v>
       </c>
-      <c r="L93" s="3" t="str">
-        <f t="shared" si="57"/>
+      <c r="L94" s="3" t="str">
+        <f t="shared" si="53"/>
         <v>€e7</v>
       </c>
-      <c r="M93" s="3" t="str">
-        <f t="shared" si="57"/>
+      <c r="M94" s="3" t="str">
+        <f t="shared" si="53"/>
         <v>€e7</v>
       </c>
-      <c r="N93" s="3" t="str">
-        <f t="shared" ref="N93" si="58">_xlfn.XLOOKUP(N91,$B$26:$XFD$26,$B$28:$XFD$28)</f>
-        <v>0-100</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="9" t="str">
+    </row>
+    <row r="95" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="9" t="str">
         <f>$A$29</f>
         <v>description</v>
       </c>
-      <c r="B94" t="str">
-        <f>_xlfn.XLOOKUP(B91,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+      <c r="B95" t="str">
+        <f>_xlfn.XLOOKUP(B92,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>current timestamp</v>
       </c>
-      <c r="C94" t="str">
-        <f t="shared" ref="C94:E94" si="59">_xlfn.XLOOKUP(C91,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+      <c r="C95" t="str">
+        <f t="shared" ref="C95:I95" si="54">_xlfn.XLOOKUP(C92,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <v>timestep (can be in future)</v>
+      </c>
+      <c r="D95" t="str">
+        <f t="shared" si="54"/>
         <v>region in which the market is</v>
       </c>
-      <c r="D94" t="str">
-        <f t="shared" si="59"/>
+      <c r="E95" t="str">
+        <f t="shared" si="54"/>
         <v>type of market</v>
       </c>
-      <c r="E94" t="str">
-        <f t="shared" si="59"/>
+      <c r="F95" t="str">
+        <f t="shared" si="54"/>
         <v>name of the market</v>
       </c>
-      <c r="F94" t="str">
-        <f t="shared" ref="F94:M94" si="60">_xlfn.XLOOKUP(F91,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+      <c r="G95" t="str">
+        <f t="shared" si="54"/>
         <v>source of the costs/profits (e.g. Market, levies, balancing)</v>
       </c>
-      <c r="G94" t="str">
-        <f t="shared" si="60"/>
-        <v>agent id (also serves as main meter)</v>
-      </c>
-      <c r="H94" t="str">
-        <f t="shared" si="60"/>
+      <c r="H95" t="str">
+        <f t="shared" si="54"/>
         <v>energy going into the meter</v>
       </c>
-      <c r="I94" t="str">
-        <f t="shared" si="60"/>
+      <c r="I95" t="str">
+        <f t="shared" si="54"/>
         <v>energy going out of the meter</v>
       </c>
-      <c r="J94" t="str">
-        <f t="shared" si="60"/>
+      <c r="J95" t="str">
+        <f t="shared" ref="J95:M95" si="55">_xlfn.XLOOKUP(J92,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>spec. price for incoming energy</v>
       </c>
-      <c r="K94" t="str">
-        <f t="shared" si="60"/>
+      <c r="K95" t="str">
+        <f t="shared" si="55"/>
         <v>spec. price for outflowing energy</v>
       </c>
-      <c r="L94" t="str">
-        <f t="shared" si="60"/>
+      <c r="L95" t="str">
+        <f t="shared" si="55"/>
         <v>total price for incoming energy</v>
       </c>
-      <c r="M94" t="str">
-        <f t="shared" si="60"/>
+      <c r="M95" t="str">
+        <f t="shared" si="55"/>
         <v>total price for outflowing energy</v>
       </c>
-      <c r="N94" t="str">
-        <f t="shared" ref="N94" si="61">_xlfn.XLOOKUP(N91,$B$26:$XFD$26,$B$29:$XFD$29)</f>
-        <v>quality share of energy (one column per type)</v>
-      </c>
-    </row>
-    <row r="95" spans="1:14" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="8"/>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A97" s="15" t="str">
+    </row>
+    <row r="96" spans="1:13" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="8"/>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A98" s="15" t="str">
         <f>$A$3</f>
         <v>Table</v>
       </c>
-      <c r="B97" s="15" t="str">
+      <c r="B98" s="15" t="str">
         <f>$B$3</f>
         <v>Section</v>
       </c>
-      <c r="C97" s="15" t="str">
+      <c r="C98" s="15" t="str">
         <f>$C$3</f>
         <v>Description</v>
       </c>
-      <c r="D97" s="15" t="str">
+      <c r="D98" s="15" t="str">
         <f>$D$3</f>
         <v>Class</v>
       </c>
-      <c r="E97" s="15" t="str">
+      <c r="E98" s="15" t="str">
         <f>$E$3</f>
         <v>Saved</v>
       </c>
     </row>
-    <row r="98" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="B98" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A98,$A$4:$A$21,$B$4:$B$21)</f>
+    <row r="99" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="B99" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A99,$A$4:$A$22,$B$4:$B$22)</f>
         <v>Analyzer</v>
       </c>
-      <c r="C98" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A98,$A$4:$A$21,$C$4:$C$21)</f>
-        <v>contains info about agents</v>
-      </c>
-      <c r="D98" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A98,$A$4:$A$21,$D$4:$D$21)</f>
+      <c r="C99" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A99,$A$4:$A$22,$C$4:$C$22)</f>
+        <v>contains summary of each timestamp</v>
+      </c>
+      <c r="D99" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A99,$A$4:$A$22,$D$4:$D$22)</f>
         <v>Markets</v>
       </c>
-      <c r="E98" s="5" t="b">
-        <f>_xlfn.XLOOKUP(A98,$A$4:$A$21,$E$4:$E$21)</f>
+      <c r="E99" s="5" t="b">
+        <f>_xlfn.XLOOKUP(A99,$A$4:$A$22,$E$4:$E$22)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A99"/>
-    </row>
     <row r="100" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>0</v>
-      </c>
-      <c r="B100" t="str">
+      <c r="A100"/>
+    </row>
+    <row r="101" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B101" t="str">
+        <f>B26</f>
+        <v>timestamp</v>
+      </c>
+      <c r="C101" t="str">
         <f>D26</f>
         <v>region</v>
       </c>
-      <c r="C100" t="str">
-        <f t="shared" ref="C100:D100" si="62">E26</f>
+      <c r="D101" t="str">
+        <f>E26</f>
         <v>market</v>
       </c>
-      <c r="D100" t="str">
-        <f t="shared" si="62"/>
+      <c r="E101" t="str">
+        <f>F26</f>
         <v>name</v>
       </c>
-      <c r="E100" t="str">
+      <c r="F101" s="9" t="str">
         <f>H26</f>
+        <v>type_transaction</v>
+      </c>
+      <c r="G101" t="str">
+        <f>I26</f>
         <v>id_agent</v>
       </c>
-      <c r="F100" t="str">
-        <f>M26</f>
+      <c r="H101" s="9" t="str">
+        <f>N26</f>
         <v>energy_in</v>
       </c>
-      <c r="G100" t="str">
-        <f>N26</f>
+      <c r="I101" s="9" t="str">
+        <f>O26</f>
         <v>energy_out</v>
       </c>
-      <c r="H100" t="str">
-        <f>O26</f>
-        <v>energy_used</v>
-      </c>
-      <c r="I100" s="9" t="str">
-        <f>T26</f>
+      <c r="J101" s="9" t="str">
+        <f>R26</f>
+        <v>price_pu_in</v>
+      </c>
+      <c r="K101" s="9" t="str">
+        <f>S26</f>
+        <v>price_pu_out</v>
+      </c>
+      <c r="L101" s="9" t="str">
+        <f>U26</f>
         <v>price_in</v>
       </c>
-      <c r="J100" s="9" t="str">
-        <f>U26</f>
+      <c r="M101" s="9" t="str">
+        <f>V26</f>
         <v>price_out</v>
       </c>
-      <c r="K100" s="9" t="str">
-        <f>Y26</f>
-        <v>balance_account</v>
-      </c>
-      <c r="L100" s="9" t="str">
-        <f>AA26</f>
+      <c r="N101" s="9" t="str">
+        <f>AB26</f>
         <v>share_quality_XXX</v>
       </c>
-      <c r="M100" s="9" t="str">
-        <f>AC26</f>
-        <v>type_plants</v>
-      </c>
-    </row>
-    <row r="101" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="9" t="str">
+    </row>
+    <row r="102" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="9" t="str">
         <f>$A$27</f>
         <v>dtype</v>
       </c>
-      <c r="B101" s="3" t="str">
-        <f>_xlfn.XLOOKUP(B100,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="B102" s="3" t="str">
+        <f>_xlfn.XLOOKUP(B101,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <v>datetime</v>
+      </c>
+      <c r="C102" s="3" t="str">
+        <f t="shared" ref="C102" si="56">_xlfn.XLOOKUP(C101,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
-      <c r="C101" s="3" t="str">
-        <f t="shared" ref="C101" si="63">_xlfn.XLOOKUP(C100,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="D102" s="3" t="str">
+        <f t="shared" ref="D102" si="57">_xlfn.XLOOKUP(D101,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
-      <c r="D101" s="3" t="str">
-        <f t="shared" ref="D101" si="64">_xlfn.XLOOKUP(D100,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="E102" s="3" t="str">
+        <f t="shared" ref="E102" si="58">_xlfn.XLOOKUP(E101,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
-      <c r="E101" s="3" t="str">
-        <f t="shared" ref="E101" si="65">_xlfn.XLOOKUP(E100,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="F102" s="3" t="str">
+        <f t="shared" ref="F102" si="59">_xlfn.XLOOKUP(F101,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
-      <c r="F101" s="3" t="str">
-        <f t="shared" ref="F101" si="66">_xlfn.XLOOKUP(F100,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="G102" s="3" t="str">
+        <f t="shared" ref="G102" si="60">_xlfn.XLOOKUP(G101,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <v>categorical</v>
+      </c>
+      <c r="H102" s="3" t="str">
+        <f t="shared" ref="H102" si="61">_xlfn.XLOOKUP(H101,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>uint64</v>
       </c>
-      <c r="G101" s="3" t="str">
-        <f t="shared" ref="G101" si="67">_xlfn.XLOOKUP(G100,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="I102" s="3" t="str">
+        <f t="shared" ref="I102" si="62">_xlfn.XLOOKUP(I101,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>uint64</v>
       </c>
-      <c r="H101" s="3" t="str">
-        <f>_xlfn.XLOOKUP(H100,$B$26:$XFD$26,$B$27:$XFD$27)</f>
-        <v>uint64</v>
-      </c>
-      <c r="I101" s="3" t="str">
-        <f t="shared" ref="I101" si="68">_xlfn.XLOOKUP(I100,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="J102" s="3" t="str">
+        <f t="shared" ref="J102" si="63">_xlfn.XLOOKUP(J101,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <v>int32</v>
+      </c>
+      <c r="K102" s="3" t="str">
+        <f t="shared" ref="K102" si="64">_xlfn.XLOOKUP(K101,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <v>int32</v>
+      </c>
+      <c r="L102" s="3" t="str">
+        <f t="shared" ref="L102" si="65">_xlfn.XLOOKUP(L101,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>int64</v>
       </c>
-      <c r="J101" s="3" t="str">
-        <f t="shared" ref="J101" si="69">_xlfn.XLOOKUP(J100,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="M102" s="3" t="str">
+        <f t="shared" ref="M102:N102" si="66">_xlfn.XLOOKUP(M101,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>int64</v>
       </c>
-      <c r="K101" s="3" t="str">
-        <f t="shared" ref="K101" si="70">_xlfn.XLOOKUP(K100,$B$26:$XFD$26,$B$27:$XFD$27)</f>
-        <v>int64</v>
-      </c>
-      <c r="L101" s="3" t="str">
-        <f t="shared" ref="L101:M101" si="71">_xlfn.XLOOKUP(L100,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="N102" s="3" t="str">
+        <f t="shared" si="66"/>
         <v>int8</v>
       </c>
-      <c r="M101" s="3" t="str">
-        <f t="shared" si="71"/>
-        <v>categorical</v>
-      </c>
-    </row>
-    <row r="102" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="9" t="str">
+    </row>
+    <row r="103" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="9" t="str">
         <f>$A$28</f>
         <v>unit</v>
       </c>
-      <c r="B102" s="3" t="str">
-        <f>_xlfn.XLOOKUP(B100,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="B103" s="3" t="str">
+        <f>_xlfn.XLOOKUP(B101,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <v>s</v>
+      </c>
+      <c r="C103" s="3" t="str">
+        <f t="shared" ref="C103:E103" si="67">_xlfn.XLOOKUP(C101,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>None</v>
       </c>
-      <c r="C102" s="3" t="str">
-        <f t="shared" ref="C102:L102" si="72">_xlfn.XLOOKUP(C100,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="D103" s="3" t="str">
+        <f t="shared" si="67"/>
         <v>None</v>
       </c>
-      <c r="D102" s="3" t="str">
-        <f t="shared" si="72"/>
+      <c r="E103" s="3" t="str">
+        <f t="shared" si="67"/>
         <v>None</v>
       </c>
-      <c r="E102" s="3" t="str">
-        <f t="shared" si="72"/>
+      <c r="F103" s="3" t="str">
+        <f t="shared" ref="F103:M103" si="68">_xlfn.XLOOKUP(F101,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>None</v>
       </c>
-      <c r="F102" s="3" t="str">
-        <f t="shared" si="72"/>
+      <c r="G103" s="3" t="str">
+        <f t="shared" si="68"/>
+        <v>None</v>
+      </c>
+      <c r="H103" s="3" t="str">
+        <f t="shared" si="68"/>
         <v>Wh</v>
       </c>
-      <c r="G102" s="3" t="str">
-        <f t="shared" si="72"/>
+      <c r="I103" s="3" t="str">
+        <f t="shared" si="68"/>
         <v>Wh</v>
       </c>
-      <c r="H102" s="3" t="str">
-        <f>_xlfn.XLOOKUP(H100,$B$26:$XFD$26,$B$28:$XFD$28)</f>
-        <v>Wh</v>
-      </c>
-      <c r="I102" s="3" t="str">
-        <f t="shared" si="72"/>
+      <c r="J103" s="3" t="str">
+        <f t="shared" si="68"/>
+        <v>€e7/Wh</v>
+      </c>
+      <c r="K103" s="3" t="str">
+        <f t="shared" si="68"/>
+        <v>€e7/Wh</v>
+      </c>
+      <c r="L103" s="3" t="str">
+        <f t="shared" si="68"/>
         <v>€e7</v>
       </c>
-      <c r="J102" s="3" t="str">
-        <f t="shared" si="72"/>
+      <c r="M103" s="3" t="str">
+        <f t="shared" si="68"/>
         <v>€e7</v>
       </c>
-      <c r="K102" s="3" t="str">
-        <f t="shared" si="72"/>
-        <v>€e7</v>
-      </c>
-      <c r="L102" s="3" t="str">
-        <f t="shared" si="72"/>
+      <c r="N103" s="3" t="str">
+        <f t="shared" ref="N103" si="69">_xlfn.XLOOKUP(N101,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>0-100</v>
       </c>
-      <c r="M102" s="3" t="str">
-        <f t="shared" ref="M102" si="73">_xlfn.XLOOKUP(M100,$B$26:$XFD$26,$B$28:$XFD$28)</f>
-        <v>none</v>
-      </c>
-    </row>
-    <row r="103" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="9" t="str">
+    </row>
+    <row r="104" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="9" t="str">
         <f>$A$29</f>
         <v>description</v>
       </c>
-      <c r="B103" t="str">
-        <f>_xlfn.XLOOKUP(B100,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+      <c r="B104" t="str">
+        <f>_xlfn.XLOOKUP(B101,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <v>current timestamp</v>
+      </c>
+      <c r="C104" t="str">
+        <f t="shared" ref="C104:E104" si="70">_xlfn.XLOOKUP(C101,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>region in which the market is</v>
       </c>
-      <c r="C103" t="str">
-        <f t="shared" ref="C103:L103" si="74">_xlfn.XLOOKUP(C100,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+      <c r="D104" t="str">
+        <f t="shared" si="70"/>
         <v>type of market</v>
       </c>
-      <c r="D103" t="str">
-        <f t="shared" si="74"/>
+      <c r="E104" t="str">
+        <f t="shared" si="70"/>
         <v>name of the market</v>
       </c>
-      <c r="E103" t="str">
-        <f t="shared" si="74"/>
+      <c r="F104" t="str">
+        <f t="shared" ref="F104:M104" si="71">_xlfn.XLOOKUP(F101,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <v>source of the costs/profits (e.g. Market, levies, balancing)</v>
+      </c>
+      <c r="G104" t="str">
+        <f t="shared" si="71"/>
         <v>agent id (also serves as main meter)</v>
       </c>
-      <c r="F103" t="str">
-        <f t="shared" si="74"/>
+      <c r="H104" t="str">
+        <f t="shared" si="71"/>
         <v>energy going into the meter</v>
       </c>
-      <c r="G103" t="str">
-        <f t="shared" si="74"/>
+      <c r="I104" t="str">
+        <f t="shared" si="71"/>
         <v>energy going out of the meter</v>
       </c>
-      <c r="H103" t="str">
-        <f>_xlfn.XLOOKUP(H100,$B$26:$XFD$26,$B$29:$XFD$29)</f>
-        <v>used energy over all timesteps</v>
-      </c>
-      <c r="I103" t="str">
-        <f t="shared" si="74"/>
+      <c r="J104" t="str">
+        <f t="shared" si="71"/>
+        <v>spec. price for incoming energy</v>
+      </c>
+      <c r="K104" t="str">
+        <f t="shared" si="71"/>
+        <v>spec. price for outflowing energy</v>
+      </c>
+      <c r="L104" t="str">
+        <f t="shared" si="71"/>
         <v>total price for incoming energy</v>
       </c>
-      <c r="J103" t="str">
-        <f t="shared" si="74"/>
+      <c r="M104" t="str">
+        <f t="shared" si="71"/>
         <v>total price for outflowing energy</v>
       </c>
-      <c r="K103" t="str">
-        <f t="shared" si="74"/>
-        <v>balance of bank account</v>
-      </c>
-      <c r="L103" t="str">
-        <f t="shared" si="74"/>
+      <c r="N104" t="str">
+        <f t="shared" ref="N104" si="72">_xlfn.XLOOKUP(N101,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>quality share of energy (one column per type)</v>
       </c>
-      <c r="M103" t="str">
-        <f t="shared" ref="M103" si="75">_xlfn.XLOOKUP(M100,$B$26:$XFD$26,$B$29:$XFD$29)</f>
-        <v>types of plants (per agent)</v>
-      </c>
-    </row>
-    <row r="104" spans="1:14" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="8"/>
-    </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A106" s="15" t="str">
+    </row>
+    <row r="105" spans="1:14" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="8"/>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A107" s="15" t="str">
         <f>$A$3</f>
         <v>Table</v>
       </c>
-      <c r="B106" s="15" t="str">
+      <c r="B107" s="15" t="str">
         <f>$B$3</f>
         <v>Section</v>
       </c>
-      <c r="C106" s="15" t="str">
+      <c r="C107" s="15" t="str">
         <f>$C$3</f>
         <v>Description</v>
       </c>
-      <c r="D106" s="15" t="str">
+      <c r="D107" s="15" t="str">
         <f>$D$3</f>
         <v>Class</v>
       </c>
-      <c r="E106" s="15" t="str">
+      <c r="E107" s="15" t="str">
         <f>$E$3</f>
         <v>Saved</v>
       </c>
     </row>
-    <row r="107" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="B107" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A107,$A$4:$A$21,$B$4:$B$21)</f>
+    <row r="108" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="B108" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A108,$A$4:$A$22,$B$4:$B$22)</f>
         <v>Analyzer</v>
       </c>
-      <c r="C107" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A107,$A$4:$A$21,$C$4:$C$21)</f>
-        <v>contains info about meters</v>
-      </c>
-      <c r="D107" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A107,$A$4:$A$21,$D$4:$D$21)</f>
+      <c r="C108" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A108,$A$4:$A$22,$C$4:$C$22)</f>
+        <v>contains info about agents</v>
+      </c>
+      <c r="D108" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A108,$A$4:$A$22,$D$4:$D$22)</f>
         <v>Markets</v>
       </c>
-      <c r="E107" s="5" t="b">
-        <f>_xlfn.XLOOKUP(A107,$A$4:$A$21,$E$4:$E$21)</f>
+      <c r="E108" s="5" t="b">
+        <f>_xlfn.XLOOKUP(A108,$A$4:$A$22,$E$4:$E$22)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A108"/>
-    </row>
     <row r="109" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>0</v>
-      </c>
-      <c r="B109" s="9" t="str">
+      <c r="A109"/>
+    </row>
+    <row r="110" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>0</v>
+      </c>
+      <c r="B110" t="str">
         <f>D26</f>
         <v>region</v>
       </c>
-      <c r="C109" s="9" t="str">
-        <f t="shared" ref="C109:D109" si="76">E26</f>
+      <c r="C110" t="str">
+        <f>E26</f>
         <v>market</v>
       </c>
-      <c r="D109" s="9" t="str">
-        <f t="shared" si="76"/>
+      <c r="D110" t="str">
+        <f>F26</f>
         <v>name</v>
       </c>
-      <c r="E109" s="9" t="str">
-        <f>H26</f>
+      <c r="E110" t="str">
+        <f>I26</f>
         <v>id_agent</v>
       </c>
-      <c r="F109" s="9" t="str">
-        <f>K26</f>
-        <v>id_meter</v>
-      </c>
-      <c r="G109" s="9" t="str">
+      <c r="F110" t="str">
+        <f>N26</f>
+        <v>energy_in</v>
+      </c>
+      <c r="G110" t="str">
+        <f>O26</f>
+        <v>energy_out</v>
+      </c>
+      <c r="H110" t="str">
+        <f>P26</f>
+        <v>energy_used</v>
+      </c>
+      <c r="I110" s="9" t="str">
+        <f>U26</f>
+        <v>price_in</v>
+      </c>
+      <c r="J110" s="9" t="str">
+        <f>V26</f>
+        <v>price_out</v>
+      </c>
+      <c r="K110" s="9" t="str">
+        <f>Z26</f>
+        <v>balance_account</v>
+      </c>
+      <c r="L110" s="9" t="str">
         <f>AB26</f>
-        <v>type_meter</v>
-      </c>
-      <c r="H109" s="9" t="str">
-        <f>Z26</f>
-        <v>quality</v>
-      </c>
-    </row>
-    <row r="110" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="9" t="str">
+        <v>share_quality_XXX</v>
+      </c>
+      <c r="M110" s="9" t="str">
+        <f>AD26</f>
+        <v>type_plants</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="9" t="str">
         <f>$A$27</f>
         <v>dtype</v>
       </c>
-      <c r="B110" s="3" t="str">
-        <f>_xlfn.XLOOKUP(B109,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="B111" s="3" t="str">
+        <f>_xlfn.XLOOKUP(B110,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
-      <c r="C110" s="3" t="str">
-        <f t="shared" ref="C110" si="77">_xlfn.XLOOKUP(C109,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="C111" s="3" t="str">
+        <f t="shared" ref="C111" si="73">_xlfn.XLOOKUP(C110,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
-      <c r="D110" s="3" t="str">
-        <f t="shared" ref="D110" si="78">_xlfn.XLOOKUP(D109,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="D111" s="3" t="str">
+        <f t="shared" ref="D111" si="74">_xlfn.XLOOKUP(D110,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
-      <c r="E110" s="3" t="str">
-        <f t="shared" ref="E110" si="79">_xlfn.XLOOKUP(E109,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="E111" s="3" t="str">
+        <f t="shared" ref="E111" si="75">_xlfn.XLOOKUP(E110,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
-      <c r="F110" s="3" t="str">
-        <f t="shared" ref="F110" si="80">_xlfn.XLOOKUP(F109,$B$26:$XFD$26,$B$27:$XFD$27)</f>
-        <v>str</v>
-      </c>
-      <c r="G110" s="3" t="str">
-        <f t="shared" ref="G110" si="81">_xlfn.XLOOKUP(G109,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="F111" s="3" t="str">
+        <f t="shared" ref="F111" si="76">_xlfn.XLOOKUP(F110,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <v>uint64</v>
+      </c>
+      <c r="G111" s="3" t="str">
+        <f t="shared" ref="G111" si="77">_xlfn.XLOOKUP(G110,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <v>uint64</v>
+      </c>
+      <c r="H111" s="3" t="str">
+        <f>_xlfn.XLOOKUP(H110,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <v>uint64</v>
+      </c>
+      <c r="I111" s="3" t="str">
+        <f t="shared" ref="I111" si="78">_xlfn.XLOOKUP(I110,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <v>int64</v>
+      </c>
+      <c r="J111" s="3" t="str">
+        <f t="shared" ref="J111" si="79">_xlfn.XLOOKUP(J110,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <v>int64</v>
+      </c>
+      <c r="K111" s="3" t="str">
+        <f t="shared" ref="K111" si="80">_xlfn.XLOOKUP(K110,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <v>int64</v>
+      </c>
+      <c r="L111" s="3" t="str">
+        <f t="shared" ref="L111:M111" si="81">_xlfn.XLOOKUP(L110,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <v>int8</v>
+      </c>
+      <c r="M111" s="3" t="str">
+        <f t="shared" si="81"/>
         <v>categorical</v>
       </c>
-      <c r="H110" s="3" t="str">
-        <f t="shared" ref="H110" si="82">_xlfn.XLOOKUP(H109,$B$26:$XFD$26,$B$27:$XFD$27)</f>
-        <v>categorical</v>
-      </c>
-      <c r="I110" s="3"/>
-      <c r="J110" s="3"/>
-      <c r="K110" s="3"/>
-      <c r="L110" s="3"/>
-      <c r="M110" s="3"/>
-      <c r="N110" s="3"/>
-    </row>
-    <row r="111" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="9" t="str">
+    </row>
+    <row r="112" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="9" t="str">
         <f>$A$28</f>
         <v>unit</v>
       </c>
-      <c r="B111" s="3" t="str">
-        <f>_xlfn.XLOOKUP(B109,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="B112" s="3" t="str">
+        <f>_xlfn.XLOOKUP(B110,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>None</v>
       </c>
-      <c r="C111" s="3" t="str">
-        <f t="shared" ref="C111:H111" si="83">_xlfn.XLOOKUP(C109,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="C112" s="3" t="str">
+        <f t="shared" ref="C112:L112" si="82">_xlfn.XLOOKUP(C110,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>None</v>
       </c>
-      <c r="D111" s="3" t="str">
-        <f t="shared" si="83"/>
+      <c r="D112" s="3" t="str">
+        <f t="shared" si="82"/>
         <v>None</v>
       </c>
-      <c r="E111" s="3" t="str">
-        <f t="shared" si="83"/>
+      <c r="E112" s="3" t="str">
+        <f t="shared" si="82"/>
         <v>None</v>
       </c>
-      <c r="F111" s="3" t="str">
-        <f t="shared" si="83"/>
+      <c r="F112" s="3" t="str">
+        <f t="shared" si="82"/>
+        <v>Wh</v>
+      </c>
+      <c r="G112" s="3" t="str">
+        <f t="shared" si="82"/>
+        <v>Wh</v>
+      </c>
+      <c r="H112" s="3" t="str">
+        <f>_xlfn.XLOOKUP(H110,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <v>Wh</v>
+      </c>
+      <c r="I112" s="3" t="str">
+        <f t="shared" si="82"/>
+        <v>€e7</v>
+      </c>
+      <c r="J112" s="3" t="str">
+        <f t="shared" si="82"/>
+        <v>€e7</v>
+      </c>
+      <c r="K112" s="3" t="str">
+        <f t="shared" si="82"/>
+        <v>€e7</v>
+      </c>
+      <c r="L112" s="3" t="str">
+        <f t="shared" si="82"/>
+        <v>0-100</v>
+      </c>
+      <c r="M112" s="3" t="str">
+        <f t="shared" ref="M112" si="83">_xlfn.XLOOKUP(M110,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>None</v>
       </c>
-      <c r="G111" s="3" t="str">
-        <f t="shared" si="83"/>
-        <v>None</v>
-      </c>
-      <c r="H111" s="3" t="str">
-        <f t="shared" si="83"/>
-        <v>None</v>
-      </c>
-      <c r="I111" s="3"/>
-      <c r="J111" s="3"/>
-      <c r="K111" s="3"/>
-      <c r="L111" s="3"/>
-      <c r="M111" s="3"/>
-      <c r="N111" s="3"/>
-    </row>
-    <row r="112" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="9" t="str">
+    </row>
+    <row r="113" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="9" t="str">
         <f>$A$29</f>
         <v>description</v>
       </c>
-      <c r="B112" t="str">
-        <f>_xlfn.XLOOKUP(B109,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+      <c r="B113" t="str">
+        <f>_xlfn.XLOOKUP(B110,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>region in which the market is</v>
       </c>
-      <c r="C112" t="str">
-        <f t="shared" ref="C112:H112" si="84">_xlfn.XLOOKUP(C109,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+      <c r="C113" t="str">
+        <f t="shared" ref="C113:L113" si="84">_xlfn.XLOOKUP(C110,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>type of market</v>
       </c>
-      <c r="D112" t="str">
+      <c r="D113" t="str">
         <f t="shared" si="84"/>
         <v>name of the market</v>
       </c>
-      <c r="E112" t="str">
+      <c r="E113" t="str">
         <f t="shared" si="84"/>
         <v>agent id (also serves as main meter)</v>
       </c>
-      <c r="F112" t="str">
+      <c r="F113" t="str">
         <f t="shared" si="84"/>
-        <v>id of the (sub-)meter</v>
-      </c>
-      <c r="G112" t="str">
+        <v>energy going into the meter</v>
+      </c>
+      <c r="G113" t="str">
         <f t="shared" si="84"/>
-        <v>type of meter</v>
-      </c>
-      <c r="H112" t="str">
+        <v>energy going out of the meter</v>
+      </c>
+      <c r="H113" t="str">
+        <f>_xlfn.XLOOKUP(H110,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <v>used energy over all timesteps</v>
+      </c>
+      <c r="I113" t="str">
         <f t="shared" si="84"/>
-        <v>quality of energy</v>
-      </c>
-    </row>
-    <row r="113" spans="1:15" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="8"/>
-    </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A115" s="15" t="str">
+        <v>total price for incoming energy</v>
+      </c>
+      <c r="J113" t="str">
+        <f t="shared" si="84"/>
+        <v>total price for outflowing energy</v>
+      </c>
+      <c r="K113" t="str">
+        <f t="shared" si="84"/>
+        <v>balance of bank account</v>
+      </c>
+      <c r="L113" t="str">
+        <f t="shared" si="84"/>
+        <v>quality share of energy (one column per type)</v>
+      </c>
+      <c r="M113" t="str">
+        <f t="shared" ref="M113" si="85">_xlfn.XLOOKUP(M110,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <v>types of plants (per agent)</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="8"/>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A116" s="15" t="str">
         <f>$A$3</f>
         <v>Table</v>
       </c>
-      <c r="B115" s="15" t="str">
+      <c r="B116" s="15" t="str">
         <f>$B$3</f>
         <v>Section</v>
       </c>
-      <c r="C115" s="15" t="str">
+      <c r="C116" s="15" t="str">
         <f>$C$3</f>
         <v>Description</v>
       </c>
-      <c r="D115" s="15" t="str">
+      <c r="D116" s="15" t="str">
         <f>$D$3</f>
         <v>Class</v>
       </c>
-      <c r="E115" s="15" t="str">
+      <c r="E116" s="15" t="str">
         <f>$E$3</f>
         <v>Saved</v>
       </c>
     </row>
-    <row r="116" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="B116" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A116,$A$4:$A$21,$B$4:$B$21)</f>
+    <row r="117" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="B117" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A117,$A$4:$A$22,$B$4:$B$22)</f>
+        <v>Analyzer</v>
+      </c>
+      <c r="C117" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A117,$A$4:$A$22,$C$4:$C$22)</f>
+        <v>contains info about meters</v>
+      </c>
+      <c r="D117" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A117,$A$4:$A$22,$D$4:$D$22)</f>
+        <v>Markets</v>
+      </c>
+      <c r="E117" s="5" t="b">
+        <f>_xlfn.XLOOKUP(A117,$A$4:$A$22,$E$4:$E$22)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A118"/>
+    </row>
+    <row r="119" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>0</v>
+      </c>
+      <c r="B119" s="9" t="str">
+        <f>D26</f>
+        <v>region</v>
+      </c>
+      <c r="C119" s="9" t="str">
+        <f>E26</f>
+        <v>market</v>
+      </c>
+      <c r="D119" s="9" t="str">
+        <f>F26</f>
+        <v>name</v>
+      </c>
+      <c r="E119" s="9" t="str">
+        <f>I26</f>
+        <v>id_agent</v>
+      </c>
+      <c r="F119" s="9" t="str">
+        <f>L26</f>
+        <v>id_meter</v>
+      </c>
+      <c r="G119" s="9" t="str">
+        <f>AC26</f>
+        <v>type_meter</v>
+      </c>
+      <c r="H119" s="9" t="str">
+        <f>AA26</f>
+        <v>quality</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="9" t="str">
+        <f>$A$27</f>
+        <v>dtype</v>
+      </c>
+      <c r="B120" s="3" t="str">
+        <f>_xlfn.XLOOKUP(B119,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <v>categorical</v>
+      </c>
+      <c r="C120" s="3" t="str">
+        <f t="shared" ref="C120" si="86">_xlfn.XLOOKUP(C119,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <v>categorical</v>
+      </c>
+      <c r="D120" s="3" t="str">
+        <f t="shared" ref="D120" si="87">_xlfn.XLOOKUP(D119,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <v>categorical</v>
+      </c>
+      <c r="E120" s="3" t="str">
+        <f t="shared" ref="E120" si="88">_xlfn.XLOOKUP(E119,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <v>categorical</v>
+      </c>
+      <c r="F120" s="3" t="str">
+        <f t="shared" ref="F120" si="89">_xlfn.XLOOKUP(F119,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <v>str</v>
+      </c>
+      <c r="G120" s="3" t="str">
+        <f t="shared" ref="G120" si="90">_xlfn.XLOOKUP(G119,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <v>categorical</v>
+      </c>
+      <c r="H120" s="3" t="str">
+        <f t="shared" ref="H120" si="91">_xlfn.XLOOKUP(H119,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <v>categorical</v>
+      </c>
+      <c r="I120" s="3"/>
+      <c r="J120" s="3"/>
+      <c r="K120" s="3"/>
+      <c r="L120" s="3"/>
+      <c r="M120" s="3"/>
+      <c r="N120" s="3"/>
+    </row>
+    <row r="121" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="9" t="str">
+        <f>$A$28</f>
+        <v>unit</v>
+      </c>
+      <c r="B121" s="3" t="str">
+        <f>_xlfn.XLOOKUP(B119,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <v>None</v>
+      </c>
+      <c r="C121" s="3" t="str">
+        <f t="shared" ref="C121:H121" si="92">_xlfn.XLOOKUP(C119,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <v>None</v>
+      </c>
+      <c r="D121" s="3" t="str">
+        <f t="shared" si="92"/>
+        <v>None</v>
+      </c>
+      <c r="E121" s="3" t="str">
+        <f t="shared" si="92"/>
+        <v>None</v>
+      </c>
+      <c r="F121" s="3" t="str">
+        <f t="shared" si="92"/>
+        <v>None</v>
+      </c>
+      <c r="G121" s="3" t="str">
+        <f t="shared" si="92"/>
+        <v>None</v>
+      </c>
+      <c r="H121" s="3" t="str">
+        <f t="shared" si="92"/>
+        <v>None</v>
+      </c>
+      <c r="I121" s="3"/>
+      <c r="J121" s="3"/>
+      <c r="K121" s="3"/>
+      <c r="L121" s="3"/>
+      <c r="M121" s="3"/>
+      <c r="N121" s="3"/>
+    </row>
+    <row r="122" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="9" t="str">
+        <f>$A$29</f>
+        <v>description</v>
+      </c>
+      <c r="B122" t="str">
+        <f>_xlfn.XLOOKUP(B119,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <v>region in which the market is</v>
+      </c>
+      <c r="C122" t="str">
+        <f t="shared" ref="C122:H122" si="93">_xlfn.XLOOKUP(C119,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <v>type of market</v>
+      </c>
+      <c r="D122" t="str">
+        <f t="shared" si="93"/>
+        <v>name of the market</v>
+      </c>
+      <c r="E122" t="str">
+        <f t="shared" si="93"/>
+        <v>agent id (also serves as main meter)</v>
+      </c>
+      <c r="F122" t="str">
+        <f t="shared" si="93"/>
+        <v>id of the (sub-)meter</v>
+      </c>
+      <c r="G122" t="str">
+        <f t="shared" si="93"/>
+        <v>type of meter</v>
+      </c>
+      <c r="H122" t="str">
+        <f t="shared" si="93"/>
+        <v>quality of energy</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="8"/>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A125" s="15" t="str">
+        <f>$A$3</f>
+        <v>Table</v>
+      </c>
+      <c r="B125" s="15" t="str">
+        <f>$B$3</f>
+        <v>Section</v>
+      </c>
+      <c r="C125" s="15" t="str">
+        <f>$C$3</f>
+        <v>Description</v>
+      </c>
+      <c r="D125" s="15" t="str">
+        <f>$D$3</f>
+        <v>Class</v>
+      </c>
+      <c r="E125" s="15" t="str">
+        <f>$E$3</f>
+        <v>Saved</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="B126" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A126,$A$4:$A$22,$B$4:$B$22)</f>
         <v>Executor</v>
       </c>
-      <c r="C116" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A116,$A$4:$A$21,$C$4:$C$21)</f>
+      <c r="C126" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A126,$A$4:$A$22,$C$4:$C$22)</f>
         <v>contains all cleared bids</v>
       </c>
-      <c r="D116" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A116,$A$4:$A$21,$D$4:$D$21)</f>
+      <c r="D126" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A126,$A$4:$A$22,$D$4:$D$22)</f>
         <v>Markets</v>
       </c>
-      <c r="E116" s="5" t="b">
-        <f>_xlfn.XLOOKUP(A116,$A$4:$A$21,$E$4:$E$21)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A117"/>
-    </row>
-    <row r="118" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B118" t="str">
+      <c r="E126" s="5" t="b">
+        <f>_xlfn.XLOOKUP(A126,$A$4:$A$22,$E$4:$E$22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A127"/>
+    </row>
+    <row r="128" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>0</v>
+      </c>
+      <c r="B128" t="str">
         <f>B26</f>
         <v>timestamp</v>
       </c>
-      <c r="C118" t="str">
-        <f t="shared" ref="C118:F118" si="85">C26</f>
+      <c r="C128" t="str">
+        <f>C26</f>
         <v>timestep</v>
       </c>
-      <c r="D118" t="str">
-        <f t="shared" si="85"/>
+      <c r="D128" t="str">
+        <f>D26</f>
         <v>region</v>
       </c>
-      <c r="E118" t="str">
-        <f t="shared" si="85"/>
+      <c r="E128" t="str">
+        <f>E26</f>
         <v>market</v>
       </c>
-      <c r="F118" t="str">
-        <f t="shared" si="85"/>
+      <c r="F128" t="str">
+        <f>F26</f>
         <v>name</v>
       </c>
-      <c r="G118" s="9" t="str">
-        <f>G26</f>
+      <c r="G128" s="9" t="str">
+        <f>H26</f>
         <v>type_transaction</v>
       </c>
-      <c r="H118" t="str">
-        <f>H26</f>
+      <c r="H128" t="str">
+        <f>I26</f>
         <v>id_agent</v>
       </c>
-      <c r="I118" s="9" t="str">
-        <f>M26</f>
+      <c r="I128" s="9" t="str">
+        <f>N26</f>
         <v>energy_in</v>
       </c>
-      <c r="J118" s="9" t="str">
-        <f>Q26</f>
+      <c r="J128" s="9" t="str">
+        <f>R26</f>
         <v>price_pu_in</v>
       </c>
-      <c r="K118" s="9" t="str">
-        <f>T26</f>
+      <c r="K128" s="9" t="str">
+        <f>U26</f>
         <v>price_in</v>
       </c>
-      <c r="N118" s="9"/>
-      <c r="O118" s="9"/>
-    </row>
-    <row r="119" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="9" t="str">
+      <c r="N128" s="9"/>
+      <c r="O128" s="9"/>
+    </row>
+    <row r="129" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="9" t="str">
         <f>$A$27</f>
         <v>dtype</v>
       </c>
-      <c r="B119" s="3" t="str">
-        <f>_xlfn.XLOOKUP(B118,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="B129" s="3" t="str">
+        <f>_xlfn.XLOOKUP(B128,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>datetime</v>
       </c>
-      <c r="C119" s="3" t="str">
-        <f t="shared" ref="C119:F119" si="86">_xlfn.XLOOKUP(C118,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="C129" s="3" t="str">
+        <f t="shared" ref="C129:F129" si="94">_xlfn.XLOOKUP(C128,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>datetime</v>
       </c>
-      <c r="D119" s="3" t="str">
-        <f t="shared" si="86"/>
+      <c r="D129" s="3" t="str">
+        <f t="shared" si="94"/>
         <v>categorical</v>
       </c>
-      <c r="E119" s="3" t="str">
-        <f t="shared" si="86"/>
+      <c r="E129" s="3" t="str">
+        <f t="shared" si="94"/>
         <v>categorical</v>
       </c>
-      <c r="F119" s="3" t="str">
-        <f t="shared" si="86"/>
+      <c r="F129" s="3" t="str">
+        <f t="shared" si="94"/>
         <v>categorical</v>
       </c>
-      <c r="G119" s="3" t="str">
-        <f>_xlfn.XLOOKUP(G118,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="G129" s="3" t="str">
+        <f>_xlfn.XLOOKUP(G128,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
-      <c r="H119" s="3" t="str">
-        <f>_xlfn.XLOOKUP(H118,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="H129" s="3" t="str">
+        <f>_xlfn.XLOOKUP(H128,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
-      <c r="I119" s="3" t="str">
-        <f>_xlfn.XLOOKUP(I118,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="I129" s="3" t="str">
+        <f>_xlfn.XLOOKUP(I128,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>uint64</v>
       </c>
-      <c r="J119" s="3" t="str">
-        <f>_xlfn.XLOOKUP(J118,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="J129" s="3" t="str">
+        <f>_xlfn.XLOOKUP(J128,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>int32</v>
       </c>
-      <c r="K119" s="3" t="str">
-        <f>_xlfn.XLOOKUP(K118,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="K129" s="3" t="str">
+        <f>_xlfn.XLOOKUP(K128,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>int64</v>
       </c>
-      <c r="N119" s="3"/>
-      <c r="O119" s="3"/>
-    </row>
-    <row r="120" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="9" t="str">
+      <c r="N129" s="3"/>
+      <c r="O129" s="3"/>
+    </row>
+    <row r="130" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="9" t="str">
         <f>$A$28</f>
         <v>unit</v>
       </c>
-      <c r="B120" s="3" t="str">
-        <f>_xlfn.XLOOKUP(B118,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="B130" s="3" t="str">
+        <f>_xlfn.XLOOKUP(B128,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>s</v>
       </c>
-      <c r="C120" s="3" t="str">
-        <f t="shared" ref="C120:F120" si="87">_xlfn.XLOOKUP(C118,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="C130" s="3" t="str">
+        <f t="shared" ref="C130:F130" si="95">_xlfn.XLOOKUP(C128,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>s</v>
       </c>
-      <c r="D120" s="3" t="str">
-        <f t="shared" si="87"/>
+      <c r="D130" s="3" t="str">
+        <f t="shared" si="95"/>
         <v>None</v>
       </c>
-      <c r="E120" s="3" t="str">
-        <f t="shared" si="87"/>
+      <c r="E130" s="3" t="str">
+        <f t="shared" si="95"/>
         <v>None</v>
       </c>
-      <c r="F120" s="3" t="str">
-        <f t="shared" si="87"/>
+      <c r="F130" s="3" t="str">
+        <f t="shared" si="95"/>
         <v>None</v>
       </c>
-      <c r="G120" s="3" t="str">
-        <f>_xlfn.XLOOKUP(G118,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="G130" s="3" t="str">
+        <f>_xlfn.XLOOKUP(G128,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>None</v>
       </c>
-      <c r="H120" s="3" t="str">
-        <f>_xlfn.XLOOKUP(H118,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="H130" s="3" t="str">
+        <f>_xlfn.XLOOKUP(H128,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>None</v>
       </c>
-      <c r="I120" s="3" t="str">
-        <f>_xlfn.XLOOKUP(I118,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="I130" s="3" t="str">
+        <f>_xlfn.XLOOKUP(I128,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>Wh</v>
       </c>
-      <c r="J120" s="3" t="str">
-        <f>_xlfn.XLOOKUP(J118,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="J130" s="3" t="str">
+        <f>_xlfn.XLOOKUP(J128,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>€e7/Wh</v>
       </c>
-      <c r="K120" s="3" t="str">
-        <f>_xlfn.XLOOKUP(K118,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="K130" s="3" t="str">
+        <f>_xlfn.XLOOKUP(K128,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>€e7</v>
       </c>
-      <c r="N120" s="3"/>
-      <c r="O120" s="3"/>
-    </row>
-    <row r="121" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="9" t="str">
+      <c r="N130" s="3"/>
+      <c r="O130" s="3"/>
+    </row>
+    <row r="131" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="9" t="str">
         <f>$A$29</f>
         <v>description</v>
       </c>
-      <c r="B121" t="str">
-        <f>_xlfn.XLOOKUP(B118,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+      <c r="B131" t="str">
+        <f>_xlfn.XLOOKUP(B128,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>current timestamp</v>
       </c>
-      <c r="C121" t="str">
-        <f t="shared" ref="C121:F121" si="88">_xlfn.XLOOKUP(C118,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+      <c r="C131" t="str">
+        <f t="shared" ref="C131:F131" si="96">_xlfn.XLOOKUP(C128,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>timestep (can be in future)</v>
       </c>
-      <c r="D121" t="str">
-        <f t="shared" si="88"/>
+      <c r="D131" t="str">
+        <f t="shared" si="96"/>
         <v>region in which the market is</v>
       </c>
-      <c r="E121" t="str">
-        <f t="shared" si="88"/>
+      <c r="E131" t="str">
+        <f t="shared" si="96"/>
         <v>type of market</v>
       </c>
-      <c r="F121" t="str">
-        <f t="shared" si="88"/>
+      <c r="F131" t="str">
+        <f t="shared" si="96"/>
         <v>name of the market</v>
       </c>
-      <c r="G121" t="str">
-        <f>_xlfn.XLOOKUP(G118,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+      <c r="G131" t="str">
+        <f>_xlfn.XLOOKUP(G128,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>source of the costs/profits (e.g. Market, levies, balancing)</v>
       </c>
-      <c r="H121" t="str">
-        <f>_xlfn.XLOOKUP(H118,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+      <c r="H131" t="str">
+        <f>_xlfn.XLOOKUP(H128,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>agent id (also serves as main meter)</v>
       </c>
-      <c r="I121" t="str">
-        <f>_xlfn.XLOOKUP(I118,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+      <c r="I131" t="str">
+        <f>_xlfn.XLOOKUP(I128,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>energy going into the meter</v>
       </c>
-      <c r="J121" t="str">
-        <f>_xlfn.XLOOKUP(J118,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+      <c r="J131" t="str">
+        <f>_xlfn.XLOOKUP(J128,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>spec. price for incoming energy</v>
       </c>
-      <c r="K121" t="str">
-        <f>_xlfn.XLOOKUP(K118,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+      <c r="K131" t="str">
+        <f>_xlfn.XLOOKUP(K128,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>total price for incoming energy</v>
       </c>
     </row>
-    <row r="122" spans="1:15" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="8"/>
-    </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A124" s="15" t="str">
+    <row r="132" spans="1:15" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="8"/>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A134" s="15" t="str">
         <f>$A$3</f>
         <v>Table</v>
       </c>
-      <c r="B124" s="15" t="str">
+      <c r="B134" s="15" t="str">
         <f>$B$3</f>
         <v>Section</v>
       </c>
-      <c r="C124" s="15" t="str">
+      <c r="C134" s="15" t="str">
         <f>$C$3</f>
         <v>Description</v>
       </c>
-      <c r="D124" s="15" t="str">
+      <c r="D134" s="15" t="str">
         <f>$D$3</f>
         <v>Class</v>
       </c>
-      <c r="E124" s="15" t="str">
+      <c r="E134" s="15" t="str">
         <f>$E$3</f>
         <v>Saved</v>
       </c>
     </row>
-    <row r="125" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="16" t="s">
-        <v>205</v>
-      </c>
-      <c r="B125" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A125,$A$4:$A$21,$B$4:$B$21)</f>
+    <row r="135" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="B135" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A135,$A$4:$A$22,$B$4:$B$22)</f>
         <v>Executor</v>
       </c>
-      <c r="C125" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A125,$A$4:$A$21,$C$4:$C$21)</f>
+      <c r="C135" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A135,$A$4:$A$22,$C$4:$C$22)</f>
         <v>contains all uncleared bids</v>
       </c>
-      <c r="D125" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A125,$A$4:$A$21,$D$4:$D$21)</f>
+      <c r="D135" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A135,$A$4:$A$22,$D$4:$D$22)</f>
         <v>Markets</v>
       </c>
-      <c r="E125" s="5" t="b">
-        <f>_xlfn.XLOOKUP(A125,$A$4:$A$21,$E$4:$E$21)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A126"/>
-    </row>
-    <row r="127" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>0</v>
-      </c>
-      <c r="B127" t="str">
-        <f>B118</f>
+      <c r="E135" s="5" t="b">
+        <f>_xlfn.XLOOKUP(A135,$A$4:$A$22,$E$4:$E$22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A136"/>
+    </row>
+    <row r="137" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>0</v>
+      </c>
+      <c r="B137" t="str">
+        <f>B128</f>
         <v>timestamp</v>
       </c>
-      <c r="C127" t="str">
-        <f t="shared" ref="C127:H127" si="89">C118</f>
+      <c r="C137" t="str">
+        <f t="shared" ref="C137:H137" si="97">C128</f>
         <v>timestep</v>
       </c>
-      <c r="D127" t="str">
-        <f t="shared" si="89"/>
+      <c r="D137" t="str">
+        <f t="shared" si="97"/>
         <v>region</v>
       </c>
-      <c r="E127" t="str">
-        <f t="shared" si="89"/>
+      <c r="E137" t="str">
+        <f t="shared" si="97"/>
         <v>market</v>
       </c>
-      <c r="F127" t="str">
-        <f t="shared" si="89"/>
+      <c r="F137" t="str">
+        <f t="shared" si="97"/>
         <v>name</v>
       </c>
-      <c r="G127" t="str">
-        <f t="shared" si="89"/>
+      <c r="G137" t="str">
+        <f t="shared" si="97"/>
         <v>type_transaction</v>
       </c>
-      <c r="H127" t="str">
-        <f t="shared" si="89"/>
+      <c r="H137" t="str">
+        <f t="shared" si="97"/>
         <v>id_agent</v>
       </c>
-      <c r="I127" t="str">
-        <f>I118</f>
+      <c r="I137" t="str">
+        <f>I128</f>
         <v>energy_in</v>
       </c>
-      <c r="J127" t="str">
-        <f>J118</f>
+      <c r="J137" t="str">
+        <f>J128</f>
         <v>price_pu_in</v>
       </c>
-      <c r="K127" t="str">
-        <f>K118</f>
+      <c r="K137" t="str">
+        <f>K128</f>
         <v>price_in</v>
       </c>
     </row>
-    <row r="128" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="9" t="str">
+    <row r="138" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="9" t="str">
         <f>$A$27</f>
         <v>dtype</v>
       </c>
-      <c r="B128" s="3" t="str">
-        <f>_xlfn.XLOOKUP(B127,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="B138" s="3" t="str">
+        <f>_xlfn.XLOOKUP(B137,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>datetime</v>
       </c>
-      <c r="C128" s="3" t="str">
-        <f t="shared" ref="C128:I128" si="90">_xlfn.XLOOKUP(C127,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="C138" s="3" t="str">
+        <f t="shared" ref="C138:I138" si="98">_xlfn.XLOOKUP(C137,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>datetime</v>
       </c>
-      <c r="D128" s="3" t="str">
-        <f t="shared" si="90"/>
+      <c r="D138" s="3" t="str">
+        <f t="shared" si="98"/>
         <v>categorical</v>
       </c>
-      <c r="E128" s="3" t="str">
-        <f t="shared" si="90"/>
+      <c r="E138" s="3" t="str">
+        <f t="shared" si="98"/>
         <v>categorical</v>
       </c>
-      <c r="F128" s="3" t="str">
-        <f t="shared" si="90"/>
+      <c r="F138" s="3" t="str">
+        <f t="shared" si="98"/>
         <v>categorical</v>
       </c>
-      <c r="G128" s="3" t="str">
-        <f t="shared" si="90"/>
+      <c r="G138" s="3" t="str">
+        <f t="shared" si="98"/>
         <v>categorical</v>
       </c>
-      <c r="H128" s="3" t="str">
-        <f t="shared" si="90"/>
+      <c r="H138" s="3" t="str">
+        <f t="shared" si="98"/>
         <v>categorical</v>
       </c>
-      <c r="I128" s="3" t="str">
-        <f t="shared" si="90"/>
+      <c r="I138" s="3" t="str">
+        <f t="shared" si="98"/>
         <v>uint64</v>
       </c>
-      <c r="J128" s="3" t="str">
-        <f>_xlfn.XLOOKUP(J127,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="J138" s="3" t="str">
+        <f>_xlfn.XLOOKUP(J137,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>int32</v>
       </c>
-      <c r="K128" s="3" t="str">
-        <f>_xlfn.XLOOKUP(K127,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="K138" s="3" t="str">
+        <f>_xlfn.XLOOKUP(K137,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>int64</v>
       </c>
-      <c r="L128" s="3"/>
-      <c r="N128" s="3"/>
-      <c r="O128" s="3"/>
-    </row>
-    <row r="129" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="9" t="str">
+      <c r="L138" s="3"/>
+      <c r="N138" s="3"/>
+      <c r="O138" s="3"/>
+    </row>
+    <row r="139" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="9" t="str">
         <f>$A$28</f>
         <v>unit</v>
       </c>
-      <c r="B129" s="3" t="str">
-        <f>_xlfn.XLOOKUP(B127,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="B139" s="3" t="str">
+        <f>_xlfn.XLOOKUP(B137,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>s</v>
       </c>
-      <c r="C129" s="3" t="str">
-        <f t="shared" ref="C129:I129" si="91">_xlfn.XLOOKUP(C127,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="C139" s="3" t="str">
+        <f t="shared" ref="C139:I139" si="99">_xlfn.XLOOKUP(C137,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>s</v>
       </c>
-      <c r="D129" s="3" t="str">
-        <f t="shared" si="91"/>
+      <c r="D139" s="3" t="str">
+        <f t="shared" si="99"/>
         <v>None</v>
       </c>
-      <c r="E129" s="3" t="str">
-        <f t="shared" si="91"/>
+      <c r="E139" s="3" t="str">
+        <f t="shared" si="99"/>
         <v>None</v>
       </c>
-      <c r="F129" s="3" t="str">
-        <f t="shared" si="91"/>
+      <c r="F139" s="3" t="str">
+        <f t="shared" si="99"/>
         <v>None</v>
       </c>
-      <c r="G129" s="3" t="str">
-        <f t="shared" si="91"/>
+      <c r="G139" s="3" t="str">
+        <f t="shared" si="99"/>
         <v>None</v>
       </c>
-      <c r="H129" s="3" t="str">
-        <f t="shared" si="91"/>
+      <c r="H139" s="3" t="str">
+        <f t="shared" si="99"/>
         <v>None</v>
       </c>
-      <c r="I129" s="3" t="str">
-        <f t="shared" si="91"/>
+      <c r="I139" s="3" t="str">
+        <f t="shared" si="99"/>
         <v>Wh</v>
       </c>
-      <c r="J129" s="3" t="str">
-        <f>_xlfn.XLOOKUP(J127,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="J139" s="3" t="str">
+        <f>_xlfn.XLOOKUP(J137,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>€e7/Wh</v>
       </c>
-      <c r="K129" s="3" t="str">
-        <f>_xlfn.XLOOKUP(K127,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="K139" s="3" t="str">
+        <f>_xlfn.XLOOKUP(K137,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>€e7</v>
       </c>
-      <c r="L129" s="3"/>
-      <c r="N129" s="3"/>
-      <c r="O129" s="3"/>
-    </row>
-    <row r="130" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="9" t="str">
+      <c r="L139" s="3"/>
+      <c r="N139" s="3"/>
+      <c r="O139" s="3"/>
+    </row>
+    <row r="140" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="9" t="str">
         <f>$A$29</f>
         <v>description</v>
       </c>
-      <c r="B130" t="str">
-        <f>_xlfn.XLOOKUP(B127,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+      <c r="B140" t="str">
+        <f>_xlfn.XLOOKUP(B137,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>current timestamp</v>
       </c>
-      <c r="C130" t="str">
-        <f t="shared" ref="C130:I130" si="92">_xlfn.XLOOKUP(C127,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+      <c r="C140" t="str">
+        <f t="shared" ref="C140:I140" si="100">_xlfn.XLOOKUP(C137,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>timestep (can be in future)</v>
       </c>
-      <c r="D130" t="str">
-        <f t="shared" si="92"/>
+      <c r="D140" t="str">
+        <f t="shared" si="100"/>
         <v>region in which the market is</v>
       </c>
-      <c r="E130" t="str">
-        <f t="shared" si="92"/>
+      <c r="E140" t="str">
+        <f t="shared" si="100"/>
         <v>type of market</v>
       </c>
-      <c r="F130" t="str">
-        <f t="shared" si="92"/>
+      <c r="F140" t="str">
+        <f t="shared" si="100"/>
         <v>name of the market</v>
       </c>
-      <c r="G130" t="str">
-        <f t="shared" si="92"/>
+      <c r="G140" t="str">
+        <f t="shared" si="100"/>
         <v>source of the costs/profits (e.g. Market, levies, balancing)</v>
       </c>
-      <c r="H130" t="str">
-        <f t="shared" si="92"/>
+      <c r="H140" t="str">
+        <f t="shared" si="100"/>
         <v>agent id (also serves as main meter)</v>
       </c>
-      <c r="I130" t="str">
-        <f t="shared" si="92"/>
+      <c r="I140" t="str">
+        <f t="shared" si="100"/>
         <v>energy going into the meter</v>
       </c>
-      <c r="J130" t="str">
-        <f>_xlfn.XLOOKUP(J127,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+      <c r="J140" t="str">
+        <f>_xlfn.XLOOKUP(J137,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>spec. price for incoming energy</v>
       </c>
-      <c r="K130" t="str">
-        <f>_xlfn.XLOOKUP(K127,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+      <c r="K140" t="str">
+        <f>_xlfn.XLOOKUP(K137,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>total price for incoming energy</v>
       </c>
     </row>
-    <row r="131" spans="1:15" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="8"/>
-    </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A133" s="15" t="str">
+    <row r="141" spans="1:15" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A141" s="8"/>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A143" s="15" t="str">
         <f>$A$3</f>
         <v>Table</v>
       </c>
-      <c r="B133" s="15" t="str">
+      <c r="B143" s="15" t="str">
         <f>$B$3</f>
         <v>Section</v>
       </c>
-      <c r="C133" s="15" t="str">
+      <c r="C143" s="15" t="str">
         <f>$C$3</f>
         <v>Description</v>
       </c>
-      <c r="D133" s="15" t="str">
+      <c r="D143" s="15" t="str">
         <f>$D$3</f>
         <v>Class</v>
       </c>
-      <c r="E133" s="15" t="str">
+      <c r="E143" s="15" t="str">
         <f>$E$3</f>
         <v>Saved</v>
       </c>
     </row>
-    <row r="134" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="16" t="s">
-        <v>206</v>
-      </c>
-      <c r="B134" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A134,$A$4:$A$21,$B$4:$B$21)</f>
+    <row r="144" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="B144" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A144,$A$4:$A$22,$B$4:$B$22)</f>
         <v>Executor</v>
       </c>
-      <c r="C134" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A134,$A$4:$A$21,$C$4:$C$21)</f>
+      <c r="C144" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A144,$A$4:$A$22,$C$4:$C$22)</f>
         <v>contains all cleared offers</v>
       </c>
-      <c r="D134" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A134,$A$4:$A$21,$D$4:$D$21)</f>
+      <c r="D144" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A144,$A$4:$A$22,$D$4:$D$22)</f>
         <v>Markets</v>
       </c>
-      <c r="E134" s="5" t="b">
-        <f>_xlfn.XLOOKUP(A134,$A$4:$A$21,$E$4:$E$21)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A135"/>
-    </row>
-    <row r="136" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>0</v>
-      </c>
-      <c r="B136" s="9" t="str">
+      <c r="E144" s="5" t="b">
+        <f>_xlfn.XLOOKUP(A144,$A$4:$A$22,$E$4:$E$22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A145"/>
+    </row>
+    <row r="146" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>0</v>
+      </c>
+      <c r="B146" s="9" t="str">
         <f>B26</f>
         <v>timestamp</v>
       </c>
-      <c r="C136" s="9" t="str">
-        <f t="shared" ref="C136:F136" si="93">C26</f>
+      <c r="C146" s="9" t="str">
+        <f>C26</f>
         <v>timestep</v>
       </c>
-      <c r="D136" s="9" t="str">
-        <f t="shared" si="93"/>
+      <c r="D146" s="9" t="str">
+        <f>D26</f>
         <v>region</v>
       </c>
-      <c r="E136" s="9" t="str">
-        <f t="shared" si="93"/>
+      <c r="E146" s="9" t="str">
+        <f>E26</f>
         <v>market</v>
       </c>
-      <c r="F136" s="9" t="str">
-        <f t="shared" si="93"/>
+      <c r="F146" s="9" t="str">
+        <f>F26</f>
         <v>name</v>
       </c>
-      <c r="G136" s="9" t="str">
-        <f>G26</f>
+      <c r="G146" s="9" t="str">
+        <f>H26</f>
         <v>type_transaction</v>
       </c>
-      <c r="H136" s="9" t="str">
-        <f>H26</f>
+      <c r="H146" s="9" t="str">
+        <f>I26</f>
         <v>id_agent</v>
       </c>
-      <c r="I136" s="9" t="str">
-        <f>N26</f>
+      <c r="I146" s="9" t="str">
+        <f>O26</f>
         <v>energy_out</v>
       </c>
-      <c r="J136" s="9" t="str">
-        <f>R26</f>
+      <c r="J146" s="9" t="str">
+        <f>S26</f>
         <v>price_pu_out</v>
       </c>
-      <c r="K136" s="9" t="str">
-        <f>U26</f>
+      <c r="K146" s="9" t="str">
+        <f>V26</f>
         <v>price_out</v>
       </c>
-      <c r="L136" s="9" t="str">
-        <f>Z26</f>
+      <c r="L146" s="9" t="str">
+        <f>AA26</f>
         <v>quality</v>
       </c>
     </row>
-    <row r="137" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="9" t="str">
+    <row r="147" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="9" t="str">
         <f>$A$27</f>
         <v>dtype</v>
       </c>
-      <c r="B137" s="3" t="str">
-        <f>_xlfn.XLOOKUP(B136,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="B147" s="3" t="str">
+        <f>_xlfn.XLOOKUP(B146,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>datetime</v>
       </c>
-      <c r="C137" s="3" t="str">
-        <f t="shared" ref="C137:F137" si="94">_xlfn.XLOOKUP(C136,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="C147" s="3" t="str">
+        <f t="shared" ref="C147:F147" si="101">_xlfn.XLOOKUP(C146,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>datetime</v>
       </c>
-      <c r="D137" s="3" t="str">
-        <f t="shared" si="94"/>
+      <c r="D147" s="3" t="str">
+        <f t="shared" si="101"/>
         <v>categorical</v>
       </c>
-      <c r="E137" s="3" t="str">
-        <f t="shared" si="94"/>
+      <c r="E147" s="3" t="str">
+        <f t="shared" si="101"/>
         <v>categorical</v>
       </c>
-      <c r="F137" s="3" t="str">
-        <f t="shared" si="94"/>
+      <c r="F147" s="3" t="str">
+        <f t="shared" si="101"/>
         <v>categorical</v>
       </c>
-      <c r="G137" s="3" t="str">
-        <f t="shared" ref="G137:L137" si="95">_xlfn.XLOOKUP(G136,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="G147" s="3" t="str">
+        <f t="shared" ref="G147:L147" si="102">_xlfn.XLOOKUP(G146,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
-      <c r="H137" s="3" t="str">
-        <f t="shared" si="95"/>
+      <c r="H147" s="3" t="str">
+        <f t="shared" si="102"/>
         <v>categorical</v>
       </c>
-      <c r="I137" s="3" t="str">
-        <f t="shared" si="95"/>
+      <c r="I147" s="3" t="str">
+        <f t="shared" si="102"/>
         <v>uint64</v>
       </c>
-      <c r="J137" s="3" t="str">
-        <f t="shared" si="95"/>
+      <c r="J147" s="3" t="str">
+        <f t="shared" si="102"/>
         <v>int32</v>
       </c>
-      <c r="K137" s="3" t="str">
-        <f t="shared" si="95"/>
+      <c r="K147" s="3" t="str">
+        <f t="shared" si="102"/>
         <v>int64</v>
       </c>
-      <c r="L137" s="3" t="str">
-        <f t="shared" si="95"/>
+      <c r="L147" s="3" t="str">
+        <f t="shared" si="102"/>
         <v>categorical</v>
       </c>
-      <c r="N137" s="3"/>
-      <c r="O137" s="3"/>
-    </row>
-    <row r="138" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="9" t="str">
+      <c r="N147" s="3"/>
+      <c r="O147" s="3"/>
+    </row>
+    <row r="148" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="9" t="str">
         <f>$A$28</f>
         <v>unit</v>
       </c>
-      <c r="B138" s="3" t="str">
-        <f>_xlfn.XLOOKUP(B136,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="B148" s="3" t="str">
+        <f>_xlfn.XLOOKUP(B146,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>s</v>
       </c>
-      <c r="C138" s="3" t="str">
-        <f t="shared" ref="C138:F138" si="96">_xlfn.XLOOKUP(C136,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="C148" s="3" t="str">
+        <f t="shared" ref="C148:F148" si="103">_xlfn.XLOOKUP(C146,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>s</v>
       </c>
-      <c r="D138" s="3" t="str">
-        <f t="shared" si="96"/>
+      <c r="D148" s="3" t="str">
+        <f t="shared" si="103"/>
         <v>None</v>
       </c>
-      <c r="E138" s="3" t="str">
-        <f t="shared" si="96"/>
+      <c r="E148" s="3" t="str">
+        <f t="shared" si="103"/>
         <v>None</v>
       </c>
-      <c r="F138" s="3" t="str">
-        <f t="shared" si="96"/>
+      <c r="F148" s="3" t="str">
+        <f t="shared" si="103"/>
         <v>None</v>
       </c>
-      <c r="G138" s="3" t="str">
-        <f t="shared" ref="G138:L138" si="97">_xlfn.XLOOKUP(G136,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="G148" s="3" t="str">
+        <f t="shared" ref="G148:L148" si="104">_xlfn.XLOOKUP(G146,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>None</v>
       </c>
-      <c r="H138" s="3" t="str">
-        <f t="shared" si="97"/>
+      <c r="H148" s="3" t="str">
+        <f t="shared" si="104"/>
         <v>None</v>
       </c>
-      <c r="I138" s="3" t="str">
-        <f t="shared" si="97"/>
+      <c r="I148" s="3" t="str">
+        <f t="shared" si="104"/>
         <v>Wh</v>
       </c>
-      <c r="J138" s="3" t="str">
-        <f t="shared" si="97"/>
+      <c r="J148" s="3" t="str">
+        <f t="shared" si="104"/>
         <v>€e7/Wh</v>
       </c>
-      <c r="K138" s="3" t="str">
-        <f t="shared" si="97"/>
+      <c r="K148" s="3" t="str">
+        <f t="shared" si="104"/>
         <v>€e7</v>
       </c>
-      <c r="L138" s="3" t="str">
-        <f t="shared" si="97"/>
+      <c r="L148" s="3" t="str">
+        <f t="shared" si="104"/>
         <v>None</v>
       </c>
-      <c r="N138" s="3"/>
-      <c r="O138" s="3"/>
-    </row>
-    <row r="139" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="9" t="str">
+      <c r="N148" s="3"/>
+      <c r="O148" s="3"/>
+    </row>
+    <row r="149" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="9" t="str">
         <f>$A$29</f>
         <v>description</v>
       </c>
-      <c r="B139" t="str">
-        <f>_xlfn.XLOOKUP(B136,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+      <c r="B149" t="str">
+        <f>_xlfn.XLOOKUP(B146,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>current timestamp</v>
       </c>
-      <c r="C139" t="str">
-        <f t="shared" ref="C139:F139" si="98">_xlfn.XLOOKUP(C136,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+      <c r="C149" t="str">
+        <f t="shared" ref="C149:F149" si="105">_xlfn.XLOOKUP(C146,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>timestep (can be in future)</v>
       </c>
-      <c r="D139" t="str">
-        <f t="shared" si="98"/>
+      <c r="D149" t="str">
+        <f t="shared" si="105"/>
         <v>region in which the market is</v>
       </c>
-      <c r="E139" t="str">
-        <f t="shared" si="98"/>
+      <c r="E149" t="str">
+        <f t="shared" si="105"/>
         <v>type of market</v>
       </c>
-      <c r="F139" t="str">
-        <f t="shared" si="98"/>
+      <c r="F149" t="str">
+        <f t="shared" si="105"/>
         <v>name of the market</v>
       </c>
-      <c r="G139" t="str">
-        <f t="shared" ref="G139:L139" si="99">_xlfn.XLOOKUP(G136,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+      <c r="G149" t="str">
+        <f t="shared" ref="G149:L149" si="106">_xlfn.XLOOKUP(G146,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>source of the costs/profits (e.g. Market, levies, balancing)</v>
       </c>
-      <c r="H139" t="str">
-        <f t="shared" si="99"/>
+      <c r="H149" t="str">
+        <f t="shared" si="106"/>
         <v>agent id (also serves as main meter)</v>
       </c>
-      <c r="I139" t="str">
-        <f t="shared" si="99"/>
+      <c r="I149" t="str">
+        <f t="shared" si="106"/>
         <v>energy going out of the meter</v>
       </c>
-      <c r="J139" t="str">
-        <f t="shared" si="99"/>
+      <c r="J149" t="str">
+        <f t="shared" si="106"/>
         <v>spec. price for outflowing energy</v>
       </c>
-      <c r="K139" t="str">
-        <f t="shared" si="99"/>
+      <c r="K149" t="str">
+        <f t="shared" si="106"/>
         <v>total price for outflowing energy</v>
       </c>
-      <c r="L139" t="str">
-        <f t="shared" si="99"/>
+      <c r="L149" t="str">
+        <f t="shared" si="106"/>
         <v>quality of energy</v>
       </c>
     </row>
-    <row r="140" spans="1:15" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="8"/>
-    </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A142" s="15" t="str">
+    <row r="150" spans="1:15" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="8"/>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A152" s="15" t="str">
         <f>$A$3</f>
         <v>Table</v>
       </c>
-      <c r="B142" s="15" t="str">
+      <c r="B152" s="15" t="str">
         <f>$B$3</f>
         <v>Section</v>
       </c>
-      <c r="C142" s="15" t="str">
+      <c r="C152" s="15" t="str">
         <f>$C$3</f>
         <v>Description</v>
       </c>
-      <c r="D142" s="15" t="str">
+      <c r="D152" s="15" t="str">
         <f>$D$3</f>
         <v>Class</v>
       </c>
-      <c r="E142" s="15" t="str">
+      <c r="E152" s="15" t="str">
         <f>$E$3</f>
         <v>Saved</v>
       </c>
     </row>
-    <row r="143" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="B143" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A143,$A$4:$A$21,$B$4:$B$21)</f>
+    <row r="153" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="B153" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A153,$A$4:$A$22,$B$4:$B$22)</f>
         <v>Executor</v>
       </c>
-      <c r="C143" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A143,$A$4:$A$21,$C$4:$C$21)</f>
+      <c r="C153" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A153,$A$4:$A$22,$C$4:$C$22)</f>
         <v>contains all uncleared offers</v>
       </c>
-      <c r="D143" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A143,$A$4:$A$21,$D$4:$D$21)</f>
+      <c r="D153" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A153,$A$4:$A$22,$D$4:$D$22)</f>
         <v>Markets</v>
       </c>
-      <c r="E143" s="5" t="b">
-        <f>_xlfn.XLOOKUP(A143,$A$4:$A$21,$E$4:$E$21)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A144"/>
-    </row>
-    <row r="145" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>0</v>
-      </c>
-      <c r="B145" t="str">
-        <f>B136</f>
+      <c r="E153" s="5" t="b">
+        <f>_xlfn.XLOOKUP(A153,$A$4:$A$22,$E$4:$E$22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A154"/>
+    </row>
+    <row r="155" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>0</v>
+      </c>
+      <c r="B155" t="str">
+        <f>B146</f>
         <v>timestamp</v>
       </c>
-      <c r="C145" t="str">
-        <f t="shared" ref="C145:H145" si="100">C136</f>
+      <c r="C155" t="str">
+        <f t="shared" ref="C155:H155" si="107">C146</f>
         <v>timestep</v>
       </c>
-      <c r="D145" t="str">
-        <f t="shared" si="100"/>
+      <c r="D155" t="str">
+        <f t="shared" si="107"/>
         <v>region</v>
       </c>
-      <c r="E145" t="str">
-        <f t="shared" si="100"/>
+      <c r="E155" t="str">
+        <f t="shared" si="107"/>
         <v>market</v>
       </c>
-      <c r="F145" t="str">
-        <f t="shared" si="100"/>
+      <c r="F155" t="str">
+        <f t="shared" si="107"/>
         <v>name</v>
       </c>
-      <c r="G145" t="str">
-        <f t="shared" si="100"/>
+      <c r="G155" t="str">
+        <f t="shared" si="107"/>
         <v>type_transaction</v>
       </c>
-      <c r="H145" t="str">
-        <f t="shared" si="100"/>
+      <c r="H155" t="str">
+        <f t="shared" si="107"/>
         <v>id_agent</v>
       </c>
-      <c r="I145" t="str">
-        <f>I136</f>
+      <c r="I155" t="str">
+        <f>I146</f>
         <v>energy_out</v>
       </c>
-      <c r="J145" t="str">
-        <f>J136</f>
+      <c r="J155" t="str">
+        <f>J146</f>
         <v>price_pu_out</v>
       </c>
-      <c r="K145" t="str">
-        <f>K136</f>
+      <c r="K155" t="str">
+        <f>K146</f>
         <v>price_out</v>
       </c>
-      <c r="L145" t="str">
-        <f>L136</f>
+      <c r="L155" t="str">
+        <f>L146</f>
         <v>quality</v>
       </c>
     </row>
-    <row r="146" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="9" t="str">
+    <row r="156" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="9" t="str">
         <f>$A$27</f>
         <v>dtype</v>
       </c>
-      <c r="B146" s="3" t="str">
-        <f>_xlfn.XLOOKUP(B145,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="B156" s="3" t="str">
+        <f>_xlfn.XLOOKUP(B155,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>datetime</v>
       </c>
-      <c r="C146" s="3" t="str">
-        <f t="shared" ref="C146:L146" si="101">_xlfn.XLOOKUP(C145,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="C156" s="3" t="str">
+        <f t="shared" ref="C156:L156" si="108">_xlfn.XLOOKUP(C155,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>datetime</v>
       </c>
-      <c r="D146" s="3" t="str">
-        <f t="shared" si="101"/>
+      <c r="D156" s="3" t="str">
+        <f t="shared" si="108"/>
         <v>categorical</v>
       </c>
-      <c r="E146" s="3" t="str">
-        <f t="shared" si="101"/>
+      <c r="E156" s="3" t="str">
+        <f t="shared" si="108"/>
         <v>categorical</v>
       </c>
-      <c r="F146" s="3" t="str">
-        <f t="shared" si="101"/>
+      <c r="F156" s="3" t="str">
+        <f t="shared" si="108"/>
         <v>categorical</v>
       </c>
-      <c r="G146" s="3" t="str">
-        <f t="shared" si="101"/>
+      <c r="G156" s="3" t="str">
+        <f t="shared" si="108"/>
         <v>categorical</v>
       </c>
-      <c r="H146" s="3" t="str">
-        <f t="shared" si="101"/>
+      <c r="H156" s="3" t="str">
+        <f t="shared" si="108"/>
         <v>categorical</v>
       </c>
-      <c r="I146" s="3" t="str">
-        <f t="shared" si="101"/>
+      <c r="I156" s="3" t="str">
+        <f t="shared" si="108"/>
         <v>uint64</v>
       </c>
-      <c r="J146" s="3" t="str">
-        <f t="shared" si="101"/>
+      <c r="J156" s="3" t="str">
+        <f t="shared" si="108"/>
         <v>int32</v>
       </c>
-      <c r="K146" s="3" t="str">
-        <f t="shared" si="101"/>
+      <c r="K156" s="3" t="str">
+        <f t="shared" si="108"/>
         <v>int64</v>
       </c>
-      <c r="L146" s="3" t="str">
-        <f t="shared" si="101"/>
+      <c r="L156" s="3" t="str">
+        <f t="shared" si="108"/>
         <v>categorical</v>
       </c>
-      <c r="M146" s="3"/>
-      <c r="N146" s="3"/>
-      <c r="O146" s="3"/>
-    </row>
-    <row r="147" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="9" t="str">
+      <c r="M156" s="3"/>
+      <c r="N156" s="3"/>
+      <c r="O156" s="3"/>
+    </row>
+    <row r="157" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="9" t="str">
         <f>$A$28</f>
         <v>unit</v>
       </c>
-      <c r="B147" s="3" t="str">
-        <f>_xlfn.XLOOKUP(B145,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="B157" s="3" t="str">
+        <f>_xlfn.XLOOKUP(B155,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>s</v>
       </c>
-      <c r="C147" s="3" t="str">
-        <f t="shared" ref="C147:L147" si="102">_xlfn.XLOOKUP(C145,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="C157" s="3" t="str">
+        <f t="shared" ref="C157:L157" si="109">_xlfn.XLOOKUP(C155,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>s</v>
       </c>
-      <c r="D147" s="3" t="str">
-        <f t="shared" si="102"/>
+      <c r="D157" s="3" t="str">
+        <f t="shared" si="109"/>
         <v>None</v>
       </c>
-      <c r="E147" s="3" t="str">
-        <f t="shared" si="102"/>
+      <c r="E157" s="3" t="str">
+        <f t="shared" si="109"/>
         <v>None</v>
       </c>
-      <c r="F147" s="3" t="str">
-        <f t="shared" si="102"/>
+      <c r="F157" s="3" t="str">
+        <f t="shared" si="109"/>
         <v>None</v>
       </c>
-      <c r="G147" s="3" t="str">
-        <f t="shared" si="102"/>
+      <c r="G157" s="3" t="str">
+        <f t="shared" si="109"/>
         <v>None</v>
       </c>
-      <c r="H147" s="3" t="str">
-        <f t="shared" si="102"/>
+      <c r="H157" s="3" t="str">
+        <f t="shared" si="109"/>
         <v>None</v>
       </c>
-      <c r="I147" s="3" t="str">
-        <f t="shared" si="102"/>
+      <c r="I157" s="3" t="str">
+        <f t="shared" si="109"/>
         <v>Wh</v>
       </c>
-      <c r="J147" s="3" t="str">
-        <f t="shared" si="102"/>
+      <c r="J157" s="3" t="str">
+        <f t="shared" si="109"/>
         <v>€e7/Wh</v>
       </c>
-      <c r="K147" s="3" t="str">
-        <f t="shared" si="102"/>
+      <c r="K157" s="3" t="str">
+        <f t="shared" si="109"/>
         <v>€e7</v>
       </c>
-      <c r="L147" s="3" t="str">
-        <f t="shared" si="102"/>
+      <c r="L157" s="3" t="str">
+        <f t="shared" si="109"/>
         <v>None</v>
       </c>
-      <c r="M147" s="3"/>
-      <c r="N147" s="3"/>
-      <c r="O147" s="3"/>
-    </row>
-    <row r="148" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="9" t="str">
+      <c r="M157" s="3"/>
+      <c r="N157" s="3"/>
+      <c r="O157" s="3"/>
+    </row>
+    <row r="158" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="9" t="str">
         <f>$A$29</f>
         <v>description</v>
       </c>
-      <c r="B148" t="str">
-        <f>_xlfn.XLOOKUP(B145,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+      <c r="B158" t="str">
+        <f>_xlfn.XLOOKUP(B155,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>current timestamp</v>
       </c>
-      <c r="C148" t="str">
-        <f t="shared" ref="C148:L148" si="103">_xlfn.XLOOKUP(C145,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+      <c r="C158" t="str">
+        <f t="shared" ref="C158:L158" si="110">_xlfn.XLOOKUP(C155,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>timestep (can be in future)</v>
       </c>
-      <c r="D148" t="str">
-        <f t="shared" si="103"/>
+      <c r="D158" t="str">
+        <f t="shared" si="110"/>
         <v>region in which the market is</v>
       </c>
-      <c r="E148" t="str">
-        <f t="shared" si="103"/>
+      <c r="E158" t="str">
+        <f t="shared" si="110"/>
         <v>type of market</v>
       </c>
-      <c r="F148" t="str">
-        <f t="shared" si="103"/>
+      <c r="F158" t="str">
+        <f t="shared" si="110"/>
         <v>name of the market</v>
       </c>
-      <c r="G148" t="str">
-        <f t="shared" si="103"/>
+      <c r="G158" t="str">
+        <f t="shared" si="110"/>
         <v>source of the costs/profits (e.g. Market, levies, balancing)</v>
       </c>
-      <c r="H148" t="str">
-        <f t="shared" si="103"/>
+      <c r="H158" t="str">
+        <f t="shared" si="110"/>
         <v>agent id (also serves as main meter)</v>
       </c>
-      <c r="I148" t="str">
-        <f t="shared" si="103"/>
+      <c r="I158" t="str">
+        <f t="shared" si="110"/>
         <v>energy going out of the meter</v>
       </c>
-      <c r="J148" t="str">
-        <f t="shared" si="103"/>
+      <c r="J158" t="str">
+        <f t="shared" si="110"/>
         <v>spec. price for outflowing energy</v>
       </c>
-      <c r="K148" t="str">
-        <f t="shared" si="103"/>
+      <c r="K158" t="str">
+        <f t="shared" si="110"/>
         <v>total price for outflowing energy</v>
       </c>
-      <c r="L148" t="str">
-        <f t="shared" si="103"/>
+      <c r="L158" t="str">
+        <f t="shared" si="110"/>
         <v>quality of energy</v>
       </c>
     </row>
-    <row r="149" spans="1:15" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="8"/>
-    </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A151" s="15" t="str">
+    <row r="159" spans="1:15" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A159" s="8"/>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A161" s="15" t="str">
         <f>$A$3</f>
         <v>Table</v>
       </c>
-      <c r="B151" s="15" t="str">
+      <c r="B161" s="15" t="str">
         <f>$B$3</f>
         <v>Section</v>
       </c>
-      <c r="C151" s="15" t="str">
+      <c r="C161" s="15" t="str">
         <f>$C$3</f>
         <v>Description</v>
       </c>
-      <c r="D151" s="15" t="str">
+      <c r="D161" s="15" t="str">
         <f>$D$3</f>
         <v>Class</v>
       </c>
-      <c r="E151" s="15" t="str">
+      <c r="E161" s="15" t="str">
         <f>$E$3</f>
         <v>Saved</v>
       </c>
     </row>
-    <row r="152" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="16" t="s">
-        <v>207</v>
-      </c>
-      <c r="B152" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A152,$A$4:$A$21,$B$4:$B$21)</f>
+    <row r="162" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="B162" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A162,$A$4:$A$22,$B$4:$B$22)</f>
         <v>Executor</v>
       </c>
-      <c r="C152" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A152,$A$4:$A$21,$C$4:$C$21)</f>
+      <c r="C162" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A162,$A$4:$A$22,$C$4:$C$22)</f>
         <v>contains all matched positions</v>
       </c>
-      <c r="D152" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A152,$A$4:$A$21,$D$4:$D$21)</f>
+      <c r="D162" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A162,$A$4:$A$22,$D$4:$D$22)</f>
         <v>Markets</v>
       </c>
-      <c r="E152" s="5" t="b">
-        <f>_xlfn.XLOOKUP(A152,$A$4:$A$21,$E$4:$E$21)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A153"/>
-    </row>
-    <row r="154" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
-        <v>0</v>
-      </c>
-      <c r="B154" t="str">
+      <c r="E162" s="5" t="b">
+        <f>_xlfn.XLOOKUP(A162,$A$4:$A$22,$E$4:$E$22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A163"/>
+    </row>
+    <row r="164" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>0</v>
+      </c>
+      <c r="B164" t="str">
         <f>B26</f>
         <v>timestamp</v>
       </c>
-      <c r="C154" t="str">
-        <f t="shared" ref="C154:G154" si="104">C26</f>
+      <c r="C164" t="str">
+        <f>C26</f>
         <v>timestep</v>
       </c>
-      <c r="D154" t="str">
-        <f t="shared" si="104"/>
+      <c r="D164" t="str">
+        <f>D26</f>
         <v>region</v>
       </c>
-      <c r="E154" t="str">
-        <f t="shared" si="104"/>
+      <c r="E164" t="str">
+        <f>E26</f>
         <v>market</v>
       </c>
-      <c r="F154" t="str">
-        <f t="shared" si="104"/>
+      <c r="F164" t="str">
+        <f>F26</f>
         <v>name</v>
       </c>
-      <c r="G154" t="str">
-        <f t="shared" si="104"/>
+      <c r="G164" t="str">
+        <f>H26</f>
         <v>type_transaction</v>
       </c>
-      <c r="H154" s="9" t="str">
-        <f>I26</f>
+      <c r="H164" s="9" t="str">
+        <f>J26</f>
         <v>id_agent_in</v>
       </c>
-      <c r="I154" s="9" t="str">
-        <f>J26</f>
+      <c r="I164" s="9" t="str">
+        <f>K26</f>
         <v>id_agent_out</v>
       </c>
-      <c r="J154" s="9" t="str">
-        <f>L26</f>
+      <c r="J164" s="9" t="str">
+        <f>M26</f>
         <v>energy</v>
       </c>
-      <c r="K154" s="9" t="str">
-        <f>P26</f>
+      <c r="K164" s="9" t="str">
+        <f>Q26</f>
         <v>price_pu</v>
       </c>
-      <c r="L154" s="9" t="str">
-        <f>S26</f>
+      <c r="L164" s="9" t="str">
+        <f>T26</f>
         <v>price</v>
       </c>
-      <c r="M154" s="9" t="str">
-        <f>Z26</f>
+      <c r="M164" s="9" t="str">
+        <f>AA26</f>
         <v>quality</v>
       </c>
     </row>
-    <row r="155" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="9" t="str">
+    <row r="165" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="9" t="str">
         <f>$A$27</f>
         <v>dtype</v>
       </c>
-      <c r="B155" s="3" t="str">
-        <f>_xlfn.XLOOKUP(B154,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="B165" s="3" t="str">
+        <f>_xlfn.XLOOKUP(B164,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>datetime</v>
       </c>
-      <c r="C155" s="3" t="str">
-        <f t="shared" ref="C155:H155" si="105">_xlfn.XLOOKUP(C154,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="C165" s="3" t="str">
+        <f t="shared" ref="C165:H165" si="111">_xlfn.XLOOKUP(C164,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>datetime</v>
       </c>
-      <c r="D155" s="3" t="str">
-        <f t="shared" si="105"/>
+      <c r="D165" s="3" t="str">
+        <f t="shared" si="111"/>
         <v>categorical</v>
       </c>
-      <c r="E155" s="3" t="str">
-        <f t="shared" si="105"/>
+      <c r="E165" s="3" t="str">
+        <f t="shared" si="111"/>
         <v>categorical</v>
       </c>
-      <c r="F155" s="3" t="str">
-        <f t="shared" si="105"/>
+      <c r="F165" s="3" t="str">
+        <f t="shared" si="111"/>
         <v>categorical</v>
       </c>
-      <c r="G155" s="3" t="str">
-        <f t="shared" si="105"/>
+      <c r="G165" s="3" t="str">
+        <f t="shared" si="111"/>
         <v>categorical</v>
       </c>
-      <c r="H155" s="3" t="str">
-        <f t="shared" si="105"/>
+      <c r="H165" s="3" t="str">
+        <f t="shared" si="111"/>
         <v>categorical</v>
       </c>
-      <c r="I155" s="3" t="str">
-        <f t="shared" ref="I155:M155" si="106">_xlfn.XLOOKUP(I154,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="I165" s="3" t="str">
+        <f t="shared" ref="I165:M165" si="112">_xlfn.XLOOKUP(I164,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
-      <c r="J155" s="3" t="str">
-        <f t="shared" si="106"/>
+      <c r="J165" s="3" t="str">
+        <f t="shared" si="112"/>
         <v>int64</v>
       </c>
-      <c r="K155" s="3" t="str">
-        <f t="shared" si="106"/>
+      <c r="K165" s="3" t="str">
+        <f t="shared" si="112"/>
         <v>int32</v>
       </c>
-      <c r="L155" s="3" t="str">
-        <f t="shared" si="106"/>
+      <c r="L165" s="3" t="str">
+        <f t="shared" si="112"/>
         <v>int64</v>
       </c>
-      <c r="M155" s="3" t="str">
-        <f t="shared" si="106"/>
+      <c r="M165" s="3" t="str">
+        <f t="shared" si="112"/>
         <v>categorical</v>
       </c>
-      <c r="N155" s="3"/>
-      <c r="O155" s="3"/>
-    </row>
-    <row r="156" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="9" t="str">
+      <c r="N165" s="3"/>
+      <c r="O165" s="3"/>
+    </row>
+    <row r="166" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="9" t="str">
         <f>$A$28</f>
         <v>unit</v>
       </c>
-      <c r="B156" s="3" t="str">
-        <f>_xlfn.XLOOKUP(B154,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="B166" s="3" t="str">
+        <f>_xlfn.XLOOKUP(B164,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>s</v>
       </c>
-      <c r="C156" s="3" t="str">
-        <f t="shared" ref="C156:H156" si="107">_xlfn.XLOOKUP(C154,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="C166" s="3" t="str">
+        <f t="shared" ref="C166:H166" si="113">_xlfn.XLOOKUP(C164,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>s</v>
       </c>
-      <c r="D156" s="3" t="str">
-        <f t="shared" si="107"/>
+      <c r="D166" s="3" t="str">
+        <f t="shared" si="113"/>
         <v>None</v>
       </c>
-      <c r="E156" s="3" t="str">
-        <f t="shared" si="107"/>
+      <c r="E166" s="3" t="str">
+        <f t="shared" si="113"/>
         <v>None</v>
       </c>
-      <c r="F156" s="3" t="str">
-        <f t="shared" si="107"/>
+      <c r="F166" s="3" t="str">
+        <f t="shared" si="113"/>
         <v>None</v>
       </c>
-      <c r="G156" s="3" t="str">
-        <f t="shared" si="107"/>
+      <c r="G166" s="3" t="str">
+        <f t="shared" si="113"/>
         <v>None</v>
       </c>
-      <c r="H156" s="3" t="str">
-        <f t="shared" si="107"/>
+      <c r="H166" s="3" t="str">
+        <f t="shared" si="113"/>
         <v>None</v>
       </c>
-      <c r="I156" s="3" t="str">
-        <f t="shared" ref="I156:M156" si="108">_xlfn.XLOOKUP(I154,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+      <c r="I166" s="3" t="str">
+        <f t="shared" ref="I166:M166" si="114">_xlfn.XLOOKUP(I164,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>None</v>
       </c>
-      <c r="J156" s="3" t="str">
-        <f t="shared" si="108"/>
+      <c r="J166" s="3" t="str">
+        <f t="shared" si="114"/>
         <v>Wh</v>
       </c>
-      <c r="K156" s="3" t="str">
-        <f t="shared" si="108"/>
+      <c r="K166" s="3" t="str">
+        <f t="shared" si="114"/>
         <v>€e7/Wh</v>
       </c>
-      <c r="L156" s="3" t="str">
-        <f t="shared" si="108"/>
+      <c r="L166" s="3" t="str">
+        <f t="shared" si="114"/>
         <v>€e7</v>
       </c>
-      <c r="M156" s="3" t="str">
-        <f t="shared" si="108"/>
+      <c r="M166" s="3" t="str">
+        <f t="shared" si="114"/>
         <v>None</v>
       </c>
-      <c r="N156" s="3"/>
-      <c r="O156" s="3"/>
-    </row>
-    <row r="157" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="9" t="str">
+      <c r="N166" s="3"/>
+      <c r="O166" s="3"/>
+    </row>
+    <row r="167" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="9" t="str">
         <f>$A$29</f>
         <v>description</v>
       </c>
-      <c r="B157" t="str">
-        <f>_xlfn.XLOOKUP(B154,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+      <c r="B167" t="str">
+        <f>_xlfn.XLOOKUP(B164,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>current timestamp</v>
       </c>
-      <c r="C157" t="str">
-        <f t="shared" ref="C157:H157" si="109">_xlfn.XLOOKUP(C154,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+      <c r="C167" t="str">
+        <f t="shared" ref="C167:H167" si="115">_xlfn.XLOOKUP(C164,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>timestep (can be in future)</v>
       </c>
-      <c r="D157" t="str">
-        <f t="shared" si="109"/>
+      <c r="D167" t="str">
+        <f t="shared" si="115"/>
         <v>region in which the market is</v>
       </c>
-      <c r="E157" t="str">
-        <f t="shared" si="109"/>
+      <c r="E167" t="str">
+        <f t="shared" si="115"/>
         <v>type of market</v>
       </c>
-      <c r="F157" t="str">
-        <f t="shared" si="109"/>
+      <c r="F167" t="str">
+        <f t="shared" si="115"/>
         <v>name of the market</v>
       </c>
-      <c r="G157" t="str">
-        <f t="shared" si="109"/>
+      <c r="G167" t="str">
+        <f t="shared" si="115"/>
         <v>source of the costs/profits (e.g. Market, levies, balancing)</v>
       </c>
-      <c r="H157" t="str">
-        <f t="shared" si="109"/>
+      <c r="H167" t="str">
+        <f t="shared" si="115"/>
         <v>agent id of incoming energy</v>
       </c>
-      <c r="I157" t="str">
-        <f t="shared" ref="I157:M157" si="110">_xlfn.XLOOKUP(I154,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+      <c r="I167" t="str">
+        <f t="shared" ref="I167:M167" si="116">_xlfn.XLOOKUP(I164,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>agent id of outgoing energy</v>
       </c>
-      <c r="J157" t="str">
-        <f t="shared" si="110"/>
+      <c r="J167" t="str">
+        <f t="shared" si="116"/>
         <v>undirectional energy</v>
       </c>
-      <c r="K157" t="str">
-        <f t="shared" si="110"/>
+      <c r="K167" t="str">
+        <f t="shared" si="116"/>
         <v>spec. price for energy</v>
       </c>
-      <c r="L157" t="str">
-        <f t="shared" si="110"/>
+      <c r="L167" t="str">
+        <f t="shared" si="116"/>
         <v>total price for energy</v>
       </c>
-      <c r="M157" t="str">
-        <f t="shared" si="110"/>
+      <c r="M167" t="str">
+        <f t="shared" si="116"/>
         <v>quality of energy</v>
       </c>
     </row>
-    <row r="158" spans="1:15" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="8"/>
-    </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A160" s="15" t="str">
+    <row r="168" spans="1:15" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A168" s="8"/>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A170" s="15" t="str">
         <f>$A$3</f>
         <v>Table</v>
       </c>
-      <c r="B160" s="15" t="str">
+      <c r="B170" s="15" t="str">
         <f>$B$3</f>
         <v>Section</v>
       </c>
-      <c r="C160" s="15" t="str">
+      <c r="C170" s="15" t="str">
         <f>$C$3</f>
         <v>Description</v>
       </c>
-      <c r="D160" s="15" t="str">
+      <c r="D170" s="15" t="str">
         <f>$D$3</f>
         <v>Class</v>
       </c>
-      <c r="E160" s="15" t="str">
+      <c r="E170" s="15" t="str">
         <f>$E$3</f>
         <v>Saved</v>
       </c>
     </row>
-    <row r="161" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="B161" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A161,$A$4:$A$21,$B$4:$B$21)</f>
+    <row r="171" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="B171" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A171,$A$4:$A$22,$B$4:$B$22)</f>
         <v>Executor</v>
       </c>
-      <c r="C161" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A161,$A$4:$A$21,$C$4:$C$21)</f>
+      <c r="C171" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A171,$A$4:$A$22,$C$4:$C$22)</f>
         <v>contains current meter value</v>
       </c>
-      <c r="D161" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A161,$A$4:$A$21,$D$4:$D$21)</f>
+      <c r="D171" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A171,$A$4:$A$22,$D$4:$D$22)</f>
         <v>Agents</v>
       </c>
-      <c r="E161" s="5" t="b">
-        <f>_xlfn.XLOOKUP(A161,$A$4:$A$21,$E$4:$E$21)</f>
+      <c r="E171" s="5" t="b">
+        <f>_xlfn.XLOOKUP(A171,$A$4:$A$22,$E$4:$E$22)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A162"/>
-      <c r="B162" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="163" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
-        <v>0</v>
-      </c>
-      <c r="B163" s="9" t="str">
-        <f>O26</f>
+    <row r="172" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A172"/>
+      <c r="B172" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>0</v>
+      </c>
+      <c r="B173" s="9" t="str">
+        <f>P26</f>
         <v>energy_used</v>
       </c>
-      <c r="H163" s="9"/>
-      <c r="I163" s="9"/>
-      <c r="J163" s="9"/>
-      <c r="K163" s="9"/>
-      <c r="L163" s="9"/>
-      <c r="M163" s="9"/>
-    </row>
-    <row r="164" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="9" t="str">
+      <c r="H173" s="9"/>
+      <c r="I173" s="9"/>
+      <c r="J173" s="9"/>
+      <c r="K173" s="9"/>
+      <c r="L173" s="9"/>
+      <c r="M173" s="9"/>
+    </row>
+    <row r="174" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A174" s="9" t="str">
         <f>$A$27</f>
         <v>dtype</v>
       </c>
-      <c r="B164" s="3" t="str">
-        <f>_xlfn.XLOOKUP(B163,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="B174" s="3" t="str">
+        <f>_xlfn.XLOOKUP(B173,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>uint64</v>
-      </c>
-      <c r="C164" s="3"/>
-      <c r="D164" s="3"/>
-      <c r="E164" s="3"/>
-      <c r="F164" s="3"/>
-      <c r="G164" s="3"/>
-      <c r="H164" s="3"/>
-      <c r="I164" s="3"/>
-      <c r="J164" s="3"/>
-      <c r="K164" s="3"/>
-      <c r="L164" s="3"/>
-      <c r="M164" s="3"/>
-      <c r="N164" s="3"/>
-      <c r="O164" s="3"/>
-    </row>
-    <row r="165" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="9" t="str">
-        <f>$A$28</f>
-        <v>unit</v>
-      </c>
-      <c r="B165" s="3" t="str">
-        <f>_xlfn.XLOOKUP(B163,$B$26:$XFD$26,$B$28:$XFD$28)</f>
-        <v>Wh</v>
-      </c>
-      <c r="C165" s="3"/>
-      <c r="D165" s="3"/>
-      <c r="E165" s="3"/>
-      <c r="F165" s="3"/>
-      <c r="G165" s="3"/>
-      <c r="H165" s="3"/>
-      <c r="I165" s="3"/>
-      <c r="J165" s="3"/>
-      <c r="K165" s="3"/>
-      <c r="L165" s="3"/>
-      <c r="M165" s="3"/>
-      <c r="N165" s="3"/>
-      <c r="O165" s="3"/>
-    </row>
-    <row r="166" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="9" t="str">
-        <f>$A$29</f>
-        <v>description</v>
-      </c>
-      <c r="B166" t="str">
-        <f>_xlfn.XLOOKUP(B163,$B$26:$XFD$26,$B$29:$XFD$29)</f>
-        <v>used energy over all timesteps</v>
-      </c>
-    </row>
-    <row r="167" spans="1:15" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="8"/>
-    </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A169" s="15" t="str">
-        <f>$A$3</f>
-        <v>Table</v>
-      </c>
-      <c r="B169" s="15" t="str">
-        <f>$B$3</f>
-        <v>Section</v>
-      </c>
-      <c r="C169" s="15" t="str">
-        <f>$C$3</f>
-        <v>Description</v>
-      </c>
-      <c r="D169" s="15" t="str">
-        <f>$D$3</f>
-        <v>Class</v>
-      </c>
-      <c r="E169" s="15" t="str">
-        <f>$E$3</f>
-        <v>Saved</v>
-      </c>
-    </row>
-    <row r="170" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="B170" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A170,$A$4:$A$21,$B$4:$B$21)</f>
-        <v>Executor</v>
-      </c>
-      <c r="C170" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A170,$A$4:$A$21,$C$4:$C$21)</f>
-        <v>contains current SoC</v>
-      </c>
-      <c r="D170" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A170,$A$4:$A$21,$D$4:$D$21)</f>
-        <v>Agents</v>
-      </c>
-      <c r="E170" s="5" t="b">
-        <f>_xlfn.XLOOKUP(A170,$A$4:$A$21,$E$4:$E$21)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="171" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A171"/>
-      <c r="B171" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="172" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
-        <v>0</v>
-      </c>
-      <c r="B172" s="9" t="str">
-        <f>AD26</f>
-        <v>soc</v>
-      </c>
-      <c r="H172" s="9"/>
-      <c r="I172" s="9"/>
-      <c r="J172" s="9"/>
-      <c r="K172" s="9"/>
-      <c r="L172" s="9"/>
-      <c r="M172" s="9"/>
-    </row>
-    <row r="173" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="9" t="str">
-        <f>$A$27</f>
-        <v>dtype</v>
-      </c>
-      <c r="B173" s="3" t="str">
-        <f>_xlfn.XLOOKUP(B172,$B$26:$XFD$26,$B$27:$XFD$27)</f>
-        <v>uint16</v>
-      </c>
-      <c r="C173" s="3"/>
-      <c r="D173" s="3"/>
-      <c r="E173" s="3"/>
-      <c r="F173" s="3"/>
-      <c r="G173" s="3"/>
-      <c r="H173" s="3"/>
-      <c r="I173" s="3"/>
-      <c r="J173" s="3"/>
-      <c r="K173" s="3"/>
-      <c r="L173" s="3"/>
-      <c r="M173" s="3"/>
-      <c r="N173" s="3"/>
-      <c r="O173" s="3"/>
-    </row>
-    <row r="174" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A174" s="9" t="str">
-        <f>$A$28</f>
-        <v>unit</v>
-      </c>
-      <c r="B174" s="3" t="str">
-        <f>_xlfn.XLOOKUP(B172,$B$26:$XFD$26,$B$28:$XFD$28)</f>
-        <v>1e5</v>
       </c>
       <c r="C174" s="3"/>
       <c r="D174" s="3"/>
@@ -7837,124 +8091,114 @@
     </row>
     <row r="175" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A175" s="9" t="str">
+        <f>$A$28</f>
+        <v>unit</v>
+      </c>
+      <c r="B175" s="3" t="str">
+        <f>_xlfn.XLOOKUP(B173,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <v>Wh</v>
+      </c>
+      <c r="C175" s="3"/>
+      <c r="D175" s="3"/>
+      <c r="E175" s="3"/>
+      <c r="F175" s="3"/>
+      <c r="G175" s="3"/>
+      <c r="H175" s="3"/>
+      <c r="I175" s="3"/>
+      <c r="J175" s="3"/>
+      <c r="K175" s="3"/>
+      <c r="L175" s="3"/>
+      <c r="M175" s="3"/>
+      <c r="N175" s="3"/>
+      <c r="O175" s="3"/>
+    </row>
+    <row r="176" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A176" s="9" t="str">
         <f>$A$29</f>
         <v>description</v>
       </c>
-      <c r="B175" t="str">
-        <f>_xlfn.XLOOKUP(B172,$B$26:$XFD$26,$B$29:$XFD$29)</f>
-        <v>state-of-charge</v>
-      </c>
-    </row>
-    <row r="176" spans="1:15" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="8"/>
-    </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A178" s="15" t="str">
+      <c r="B176" t="str">
+        <f>_xlfn.XLOOKUP(B173,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <v>used energy over all timesteps</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A177" s="8"/>
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A179" s="15" t="str">
         <f>$A$3</f>
         <v>Table</v>
       </c>
-      <c r="B178" s="15" t="str">
+      <c r="B179" s="15" t="str">
         <f>$B$3</f>
         <v>Section</v>
       </c>
-      <c r="C178" s="15" t="str">
+      <c r="C179" s="15" t="str">
         <f>$C$3</f>
         <v>Description</v>
       </c>
-      <c r="D178" s="15" t="str">
+      <c r="D179" s="15" t="str">
         <f>$D$3</f>
         <v>Class</v>
       </c>
-      <c r="E178" s="15" t="str">
+      <c r="E179" s="15" t="str">
         <f>$E$3</f>
         <v>Saved</v>
       </c>
     </row>
-    <row r="179" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="16" t="s">
-        <v>261</v>
-      </c>
-      <c r="B179" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A179,$A$4:$A$21,$B$4:$B$21)</f>
+    <row r="180" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A180" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="B180" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A180,$A$4:$A$22,$B$4:$B$22)</f>
         <v>Executor</v>
       </c>
-      <c r="C179" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A179,$A$4:$A$21,$C$4:$C$21)</f>
-        <v>contains all plants timeseries</v>
-      </c>
-      <c r="D179" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A179,$A$4:$A$21,$D$4:$D$21)</f>
+      <c r="C180" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A180,$A$4:$A$22,$C$4:$C$22)</f>
+        <v>contains current SoC</v>
+      </c>
+      <c r="D180" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A180,$A$4:$A$22,$D$4:$D$22)</f>
         <v>Agents</v>
       </c>
-      <c r="E179" s="5" t="b">
-        <f>_xlfn.XLOOKUP(A179,$A$4:$A$21,$E$4:$E$21)</f>
+      <c r="E180" s="5" t="b">
+        <f>_xlfn.XLOOKUP(A180,$A$4:$A$22,$E$4:$E$22)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A180"/>
-      <c r="C180" t="s">
-        <v>269</v>
-      </c>
-    </row>
     <row r="181" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
-        <v>0</v>
-      </c>
-      <c r="B181" s="9" t="str">
-        <f>B26</f>
-        <v>timestamp</v>
-      </c>
-      <c r="C181" s="9" t="str">
+      <c r="A181"/>
+      <c r="B181" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="182" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>0</v>
+      </c>
+      <c r="B182" s="9" t="str">
         <f>AE26</f>
-        <v>plant_value</v>
-      </c>
-      <c r="H181" s="9"/>
-      <c r="I181" s="9"/>
-      <c r="J181" s="9"/>
-      <c r="K181" s="9"/>
-      <c r="L181" s="9"/>
-      <c r="M181" s="9"/>
-    </row>
-    <row r="182" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="9" t="str">
+        <v>soc</v>
+      </c>
+      <c r="H182" s="9"/>
+      <c r="I182" s="9"/>
+      <c r="J182" s="9"/>
+      <c r="K182" s="9"/>
+      <c r="L182" s="9"/>
+      <c r="M182" s="9"/>
+    </row>
+    <row r="183" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="9" t="str">
         <f>$A$27</f>
         <v>dtype</v>
       </c>
-      <c r="B182" s="3" t="str">
-        <f>_xlfn.XLOOKUP(B181,$B$26:$XFD$26,$B$27:$XFD$27)</f>
-        <v>datetime</v>
-      </c>
-      <c r="C182" s="3">
-        <f>_xlfn.XLOOKUP(C181,$B$26:$XFD$26,$B$27:$XFD$27)</f>
-        <v>0</v>
-      </c>
-      <c r="D182" s="3"/>
-      <c r="E182" s="3"/>
-      <c r="F182" s="3"/>
-      <c r="G182" s="3"/>
-      <c r="H182" s="3"/>
-      <c r="I182" s="3"/>
-      <c r="J182" s="3"/>
-      <c r="K182" s="3"/>
-      <c r="L182" s="3"/>
-      <c r="M182" s="3"/>
-      <c r="N182" s="3"/>
-      <c r="O182" s="3"/>
-    </row>
-    <row r="183" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="9" t="str">
-        <f>$A$28</f>
-        <v>unit</v>
-      </c>
       <c r="B183" s="3" t="str">
-        <f>_xlfn.XLOOKUP(B181,$B$26:$XFD$26,$B$28:$XFD$28)</f>
-        <v>s</v>
-      </c>
-      <c r="C183" s="3">
-        <f>_xlfn.XLOOKUP(C181,$B$26:$XFD$26,$B$28:$XFD$28)</f>
-        <v>0</v>
-      </c>
+        <f>_xlfn.XLOOKUP(B182,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <v>uint16</v>
+      </c>
+      <c r="C183" s="3"/>
       <c r="D183" s="3"/>
       <c r="E183" s="3"/>
       <c r="F183" s="3"/>
@@ -7970,133 +8214,122 @@
     </row>
     <row r="184" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A184" s="9" t="str">
+        <f>$A$28</f>
+        <v>unit</v>
+      </c>
+      <c r="B184" s="3" t="str">
+        <f>_xlfn.XLOOKUP(B182,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <v>1e5</v>
+      </c>
+      <c r="C184" s="3"/>
+      <c r="D184" s="3"/>
+      <c r="E184" s="3"/>
+      <c r="F184" s="3"/>
+      <c r="G184" s="3"/>
+      <c r="H184" s="3"/>
+      <c r="I184" s="3"/>
+      <c r="J184" s="3"/>
+      <c r="K184" s="3"/>
+      <c r="L184" s="3"/>
+      <c r="M184" s="3"/>
+      <c r="N184" s="3"/>
+      <c r="O184" s="3"/>
+    </row>
+    <row r="185" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="9" t="str">
         <f>$A$29</f>
         <v>description</v>
       </c>
-      <c r="B184" t="str">
-        <f>_xlfn.XLOOKUP(B181,$B$26:$XFD$26,$B$29:$XFD$29)</f>
-        <v>current timestamp</v>
-      </c>
-      <c r="C184" t="str">
-        <f>_xlfn.XLOOKUP(C181,$B$26:$XFD$26,$B$29:$XFD$29)</f>
-        <v>value of plant timeseries</v>
-      </c>
-    </row>
-    <row r="185" spans="1:15" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="8"/>
-    </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A187" s="15" t="str">
+      <c r="B185" t="str">
+        <f>_xlfn.XLOOKUP(B182,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <v>state-of-charge</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A186" s="8"/>
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A188" s="15" t="str">
         <f>$A$3</f>
         <v>Table</v>
       </c>
-      <c r="B187" s="15" t="str">
+      <c r="B188" s="15" t="str">
         <f>$B$3</f>
         <v>Section</v>
       </c>
-      <c r="C187" s="15" t="str">
+      <c r="C188" s="15" t="str">
         <f>$C$3</f>
         <v>Description</v>
       </c>
-      <c r="D187" s="15" t="str">
+      <c r="D188" s="15" t="str">
         <f>$D$3</f>
         <v>Class</v>
       </c>
-      <c r="E187" s="15" t="str">
+      <c r="E188" s="15" t="str">
         <f>$E$3</f>
         <v>Saved</v>
       </c>
     </row>
-    <row r="188" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A188" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="B188" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A188,$A$4:$A$21,$B$4:$B$21)</f>
+    <row r="189" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A189" s="16" t="s">
+        <v>260</v>
+      </c>
+      <c r="B189" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A189,$A$4:$A$22,$B$4:$B$22)</f>
         <v>Executor</v>
       </c>
-      <c r="C188" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A188,$A$4:$A$21,$C$4:$C$21)</f>
-        <v>contains plant setpoint for timesteps</v>
-      </c>
-      <c r="D188" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A188,$A$4:$A$21,$D$4:$D$21)</f>
+      <c r="C189" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A189,$A$4:$A$22,$C$4:$C$22)</f>
+        <v>contains all plants timeseries</v>
+      </c>
+      <c r="D189" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A189,$A$4:$A$22,$D$4:$D$22)</f>
         <v>Agents</v>
       </c>
-      <c r="E188" s="5" t="b">
-        <f>_xlfn.XLOOKUP(A188,$A$4:$A$21,$E$4:$E$21)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A189"/>
-      <c r="D189" t="s">
-        <v>269</v>
+      <c r="E189" s="5" t="b">
+        <f>_xlfn.XLOOKUP(A189,$A$4:$A$22,$E$4:$E$22)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="190" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A190" t="s">
-        <v>0</v>
-      </c>
-      <c r="B190" t="str">
+      <c r="A190"/>
+      <c r="C190" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="191" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>0</v>
+      </c>
+      <c r="B191" s="9" t="str">
         <f>B26</f>
         <v>timestamp</v>
       </c>
-      <c r="C190" s="9" t="str">
-        <f>C26</f>
-        <v>timestep</v>
-      </c>
-      <c r="D190" t="str">
-        <f>V26</f>
-        <v>power</v>
-      </c>
-    </row>
-    <row r="191" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="9" t="str">
+      <c r="C191" s="9" t="str">
+        <f>AF26</f>
+        <v>plant_value</v>
+      </c>
+      <c r="H191" s="9"/>
+      <c r="I191" s="9"/>
+      <c r="J191" s="9"/>
+      <c r="K191" s="9"/>
+      <c r="L191" s="9"/>
+      <c r="M191" s="9"/>
+    </row>
+    <row r="192" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A192" s="9" t="str">
         <f>$A$27</f>
         <v>dtype</v>
       </c>
-      <c r="B191" s="3" t="str">
-        <f>_xlfn.XLOOKUP(B190,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+      <c r="B192" s="3" t="str">
+        <f>_xlfn.XLOOKUP(B191,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>datetime</v>
       </c>
-      <c r="C191" s="3" t="str">
-        <f>_xlfn.XLOOKUP(C190,$B$26:$XFD$26,$B$27:$XFD$27)</f>
-        <v>datetime</v>
-      </c>
-      <c r="D191" s="3" t="str">
-        <f>_xlfn.XLOOKUP(D190,$B$26:$XFD$26,$B$27:$XFD$27)</f>
-        <v>int32</v>
-      </c>
-      <c r="E191" s="3"/>
-      <c r="F191" s="3"/>
-      <c r="G191" s="3"/>
-      <c r="H191" s="3"/>
-      <c r="I191" s="3"/>
-      <c r="J191" s="3"/>
-      <c r="K191" s="3"/>
-      <c r="L191" s="3"/>
-      <c r="M191" s="3"/>
-      <c r="N191" s="3"/>
-      <c r="O191" s="3"/>
-    </row>
-    <row r="192" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="9" t="str">
-        <f>$A$28</f>
-        <v>unit</v>
-      </c>
-      <c r="B192" s="3" t="str">
-        <f>_xlfn.XLOOKUP(B190,$B$26:$XFD$26,$B$28:$XFD$28)</f>
-        <v>s</v>
-      </c>
-      <c r="C192" s="3" t="str">
-        <f>_xlfn.XLOOKUP(C190,$B$26:$XFD$26,$B$28:$XFD$28)</f>
-        <v>s</v>
-      </c>
-      <c r="D192" s="3" t="str">
-        <f>_xlfn.XLOOKUP(D190,$B$26:$XFD$26,$B$28:$XFD$28)</f>
-        <v>W</v>
-      </c>
+      <c r="C192" s="3">
+        <f>_xlfn.XLOOKUP(C191,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <v>0</v>
+      </c>
+      <c r="D192" s="3"/>
       <c r="E192" s="3"/>
       <c r="F192" s="3"/>
       <c r="G192" s="3"/>
@@ -8111,81 +8344,101 @@
     </row>
     <row r="193" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A193" s="9" t="str">
+        <f>$A$28</f>
+        <v>unit</v>
+      </c>
+      <c r="B193" s="3" t="str">
+        <f>_xlfn.XLOOKUP(B191,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <v>s</v>
+      </c>
+      <c r="C193" s="3">
+        <f>_xlfn.XLOOKUP(C191,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <v>0</v>
+      </c>
+      <c r="D193" s="3"/>
+      <c r="E193" s="3"/>
+      <c r="F193" s="3"/>
+      <c r="G193" s="3"/>
+      <c r="H193" s="3"/>
+      <c r="I193" s="3"/>
+      <c r="J193" s="3"/>
+      <c r="K193" s="3"/>
+      <c r="L193" s="3"/>
+      <c r="M193" s="3"/>
+      <c r="N193" s="3"/>
+      <c r="O193" s="3"/>
+    </row>
+    <row r="194" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A194" s="9" t="str">
         <f>$A$29</f>
         <v>description</v>
       </c>
-      <c r="B193" t="str">
-        <f>_xlfn.XLOOKUP(B190,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+      <c r="B194" t="str">
+        <f>_xlfn.XLOOKUP(B191,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>current timestamp</v>
       </c>
-      <c r="C193" t="str">
-        <f>_xlfn.XLOOKUP(C190,$B$26:$XFD$26,$B$29:$XFD$29)</f>
-        <v>timestep (can be in future)</v>
-      </c>
-      <c r="D193" t="str">
-        <f>_xlfn.XLOOKUP(D190,$B$26:$XFD$26,$B$29:$XFD$29)</f>
-        <v>undirectional power</v>
-      </c>
-    </row>
-    <row r="194" spans="1:15" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="8"/>
-    </row>
-    <row r="196" spans="1:15" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="15" t="str">
+      <c r="C194" t="str">
+        <f>_xlfn.XLOOKUP(C191,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <v>value of plant timeseries</v>
+      </c>
+    </row>
+    <row r="195" spans="1:15" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A195" s="8"/>
+    </row>
+    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A197" s="15" t="str">
         <f>$A$3</f>
         <v>Table</v>
       </c>
-      <c r="B196" s="15" t="str">
+      <c r="B197" s="15" t="str">
         <f>$B$3</f>
         <v>Section</v>
       </c>
-      <c r="C196" s="15" t="str">
+      <c r="C197" s="15" t="str">
         <f>$C$3</f>
         <v>Description</v>
       </c>
-      <c r="D196" s="15" t="str">
+      <c r="D197" s="15" t="str">
         <f>$D$3</f>
         <v>Class</v>
       </c>
-      <c r="E196" s="15" t="str">
+      <c r="E197" s="15" t="str">
         <f>$E$3</f>
         <v>Saved</v>
       </c>
     </row>
-    <row r="197" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A197" s="16" t="str">
-        <f>A21</f>
-        <v>forecasts</v>
-      </c>
-      <c r="B197" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A197,$A$4:$A$21,$B$4:$B$21)</f>
+    <row r="198" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A198" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="B198" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A198,$A$4:$A$22,$B$4:$B$22)</f>
         <v>Executor</v>
       </c>
-      <c r="C197" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A197,$A$4:$A$21,$C$4:$C$21)</f>
-        <v>contains all forecasts (except weather)</v>
-      </c>
-      <c r="D197" s="5" t="str">
-        <f>_xlfn.XLOOKUP(A197,$A$4:$A$21,$D$4:$D$21)</f>
+      <c r="C198" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A198,$A$4:$A$22,$C$4:$C$22)</f>
+        <v>contains plant setpoint for timesteps</v>
+      </c>
+      <c r="D198" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A198,$A$4:$A$22,$D$4:$D$22)</f>
         <v>Agents</v>
       </c>
-      <c r="E197" s="5" t="b">
-        <f>_xlfn.XLOOKUP(A197,$A$4:$A$21,$E$4:$E$21)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="198" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
+      <c r="E198" s="5" t="b">
+        <f>_xlfn.XLOOKUP(A198,$A$4:$A$22,$E$4:$E$22)</f>
+        <v>0</v>
+      </c>
+    </row>
     <row r="199" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A199"/>
       <c r="D199" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="200" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>0</v>
       </c>
-      <c r="B200" s="9" t="str">
+      <c r="B200" t="str">
         <f>B26</f>
         <v>timestamp</v>
       </c>
@@ -8193,16 +8446,10 @@
         <f>C26</f>
         <v>timestep</v>
       </c>
-      <c r="D200" s="9" t="str">
-        <f>AE26</f>
-        <v>plant_value</v>
-      </c>
-      <c r="H200" s="9"/>
-      <c r="I200" s="9"/>
-      <c r="J200" s="9"/>
-      <c r="K200" s="9"/>
-      <c r="L200" s="9"/>
-      <c r="M200" s="9"/>
+      <c r="D200" t="str">
+        <f>W26</f>
+        <v>power</v>
+      </c>
     </row>
     <row r="201" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A201" s="9" t="str">
@@ -8217,9 +8464,9 @@
         <f>_xlfn.XLOOKUP(C200,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>datetime</v>
       </c>
-      <c r="D201" s="3">
+      <c r="D201" s="3" t="str">
         <f>_xlfn.XLOOKUP(D200,$B$26:$XFD$26,$B$27:$XFD$27)</f>
-        <v>0</v>
+        <v>int32</v>
       </c>
       <c r="E201" s="3"/>
       <c r="F201" s="3"/>
@@ -8246,9 +8493,9 @@
         <f>_xlfn.XLOOKUP(C200,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>s</v>
       </c>
-      <c r="D202" s="3">
+      <c r="D202" s="3" t="str">
         <f>_xlfn.XLOOKUP(D200,$B$26:$XFD$26,$B$28:$XFD$28)</f>
-        <v>0</v>
+        <v>W</v>
       </c>
       <c r="E202" s="3"/>
       <c r="F202" s="3"/>
@@ -8277,16 +8524,169 @@
       </c>
       <c r="D203" t="str">
         <f>_xlfn.XLOOKUP(D200,$B$26:$XFD$26,$B$29:$XFD$29)</f>
-        <v>value of plant timeseries</v>
+        <v>undirectional power</v>
       </c>
     </row>
     <row r="204" spans="1:15" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="8"/>
+    </row>
+    <row r="206" spans="1:15" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A206" s="15" t="str">
+        <f>$A$3</f>
+        <v>Table</v>
+      </c>
+      <c r="B206" s="15" t="str">
+        <f>$B$3</f>
+        <v>Section</v>
+      </c>
+      <c r="C206" s="15" t="str">
+        <f>$C$3</f>
+        <v>Description</v>
+      </c>
+      <c r="D206" s="15" t="str">
+        <f>$D$3</f>
+        <v>Class</v>
+      </c>
+      <c r="E206" s="15" t="str">
+        <f>$E$3</f>
+        <v>Saved</v>
+      </c>
+    </row>
+    <row r="207" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A207" s="16" t="str">
+        <f>A22</f>
+        <v>forecasts</v>
+      </c>
+      <c r="B207" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A207,$A$4:$A$22,$B$4:$B$22)</f>
+        <v>Executor</v>
+      </c>
+      <c r="C207" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A207,$A$4:$A$22,$C$4:$C$22)</f>
+        <v>contains all forecasts (except weather)</v>
+      </c>
+      <c r="D207" s="5" t="str">
+        <f>_xlfn.XLOOKUP(A207,$A$4:$A$22,$D$4:$D$22)</f>
+        <v>Agents</v>
+      </c>
+      <c r="E207" s="5" t="b">
+        <f>_xlfn.XLOOKUP(A207,$A$4:$A$22,$E$4:$E$22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="209" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A209"/>
+      <c r="D209" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="210" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>0</v>
+      </c>
+      <c r="B210" s="9" t="str">
+        <f>B26</f>
+        <v>timestamp</v>
+      </c>
+      <c r="C210" s="9" t="str">
+        <f>C26</f>
+        <v>timestep</v>
+      </c>
+      <c r="D210" s="9" t="str">
+        <f>AF26</f>
+        <v>plant_value</v>
+      </c>
+      <c r="H210" s="9"/>
+      <c r="I210" s="9"/>
+      <c r="J210" s="9"/>
+      <c r="K210" s="9"/>
+      <c r="L210" s="9"/>
+      <c r="M210" s="9"/>
+    </row>
+    <row r="211" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A211" s="9" t="str">
+        <f>$A$27</f>
+        <v>dtype</v>
+      </c>
+      <c r="B211" s="3" t="str">
+        <f>_xlfn.XLOOKUP(B210,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <v>datetime</v>
+      </c>
+      <c r="C211" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C210,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <v>datetime</v>
+      </c>
+      <c r="D211" s="3">
+        <f>_xlfn.XLOOKUP(D210,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <v>0</v>
+      </c>
+      <c r="E211" s="3"/>
+      <c r="F211" s="3"/>
+      <c r="G211" s="3"/>
+      <c r="H211" s="3"/>
+      <c r="I211" s="3"/>
+      <c r="J211" s="3"/>
+      <c r="K211" s="3"/>
+      <c r="L211" s="3"/>
+      <c r="M211" s="3"/>
+      <c r="N211" s="3"/>
+      <c r="O211" s="3"/>
+    </row>
+    <row r="212" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A212" s="9" t="str">
+        <f>$A$28</f>
+        <v>unit</v>
+      </c>
+      <c r="B212" s="3" t="str">
+        <f>_xlfn.XLOOKUP(B210,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <v>s</v>
+      </c>
+      <c r="C212" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C210,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <v>s</v>
+      </c>
+      <c r="D212" s="3">
+        <f>_xlfn.XLOOKUP(D210,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <v>0</v>
+      </c>
+      <c r="E212" s="3"/>
+      <c r="F212" s="3"/>
+      <c r="G212" s="3"/>
+      <c r="H212" s="3"/>
+      <c r="I212" s="3"/>
+      <c r="J212" s="3"/>
+      <c r="K212" s="3"/>
+      <c r="L212" s="3"/>
+      <c r="M212" s="3"/>
+      <c r="N212" s="3"/>
+      <c r="O212" s="3"/>
+    </row>
+    <row r="213" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A213" s="9" t="str">
+        <f>$A$29</f>
+        <v>description</v>
+      </c>
+      <c r="B213" t="str">
+        <f>_xlfn.XLOOKUP(B210,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <v>current timestamp</v>
+      </c>
+      <c r="C213" t="str">
+        <f>_xlfn.XLOOKUP(C210,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <v>timestep (can be in future)</v>
+      </c>
+      <c r="D213" t="str">
+        <f>_xlfn.XLOOKUP(D210,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <v>value of plant timeseries</v>
+      </c>
+    </row>
+    <row r="214" spans="1:15" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A214" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q27:R27 M27:O27 T27:U27 Y27:XFD27 B27:K27" xr:uid="{39721BCA-305E-49BF-AD44-90D58CB02102}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R27:S27 Z27:XFD27 B27:F27 H27:L27 U27:V27 N27:P27" xr:uid="{39721BCA-305E-49BF-AD44-90D58CB02102}">
       <formula1>$B$33:$XFD$33</formula1>
     </dataValidation>
   </dataValidations>

--- a/hamlet/tables.xlsx
+++ b/hamlet/tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ge23nur\Documents\Python Scripts\HAMLET\hamlet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B5BED9E-25DD-48AD-8748-2684FC98E2F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91527C64-33C2-4BF7-B4B9-B04F38276B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14505" yWindow="0" windowWidth="14610" windowHeight="17385" activeTab="2" autoFilterDateGrouping="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" autoFilterDateGrouping="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Explanation" sheetId="13" r:id="rId1"/>
@@ -1022,7 +1022,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1059,7 +1059,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -4822,32 +4821,32 @@
         <v>268</v>
       </c>
     </row>
-    <row r="56" spans="1:15" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B56" s="18" t="str">
-        <f>B26</f>
+    <row r="56" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>0</v>
+      </c>
+      <c r="B56" t="str">
+        <f t="shared" ref="B56:G56" si="10">B26</f>
         <v>timestamp</v>
       </c>
-      <c r="C56" s="18" t="str">
-        <f>C26</f>
+      <c r="C56" t="str">
+        <f t="shared" si="10"/>
         <v>timestep</v>
       </c>
-      <c r="D56" s="18" t="str">
-        <f>D26</f>
+      <c r="D56" t="str">
+        <f t="shared" si="10"/>
         <v>region</v>
       </c>
-      <c r="E56" s="18" t="str">
-        <f>E26</f>
+      <c r="E56" t="str">
+        <f t="shared" si="10"/>
         <v>market</v>
       </c>
-      <c r="F56" s="18" t="str">
-        <f>F26</f>
+      <c r="F56" t="str">
+        <f t="shared" si="10"/>
         <v>name</v>
       </c>
-      <c r="G56" s="18" t="str">
-        <f>G26</f>
+      <c r="G56" t="str">
+        <f t="shared" si="10"/>
         <v>energy_type</v>
       </c>
       <c r="H56" s="9" t="str">
@@ -4855,15 +4854,15 @@
         <v>action</v>
       </c>
       <c r="I56" s="9" t="str">
-        <f t="shared" ref="I56:K56" si="10">AH26</f>
+        <f t="shared" ref="I56:K56" si="11">AH26</f>
         <v>type</v>
       </c>
       <c r="J56" s="9" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>method</v>
       </c>
       <c r="K56" s="9" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>pricing</v>
       </c>
       <c r="L56" s="9" t="str">
@@ -4889,35 +4888,35 @@
         <v>categorical</v>
       </c>
       <c r="E57" s="3" t="str">
-        <f t="shared" ref="E57:G57" si="11">_xlfn.XLOOKUP(E56,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="E57:G57" si="12">_xlfn.XLOOKUP(E56,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
       <c r="F57" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>categorical</v>
       </c>
       <c r="G57" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>categorical</v>
       </c>
       <c r="H57" s="3" t="str">
-        <f t="shared" ref="H57" si="12">_xlfn.XLOOKUP(H56,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="H57" si="13">_xlfn.XLOOKUP(H56,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
       <c r="I57" s="3" t="str">
-        <f t="shared" ref="I57" si="13">_xlfn.XLOOKUP(I56,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="I57" si="14">_xlfn.XLOOKUP(I56,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
       <c r="J57" s="3" t="str">
-        <f t="shared" ref="J57" si="14">_xlfn.XLOOKUP(J56,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="J57" si="15">_xlfn.XLOOKUP(J56,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
       <c r="K57" s="3" t="str">
-        <f t="shared" ref="K57" si="15">_xlfn.XLOOKUP(K56,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="K57" si="16">_xlfn.XLOOKUP(K56,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
       <c r="L57" s="3" t="str">
-        <f t="shared" ref="L57" si="16">_xlfn.XLOOKUP(L56,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="L57" si="17">_xlfn.XLOOKUP(L56,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
       <c r="M57" s="3"/>
@@ -4942,35 +4941,35 @@
         <v>None</v>
       </c>
       <c r="E58" s="3" t="str">
-        <f t="shared" ref="E58:G58" si="17">_xlfn.XLOOKUP(E56,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <f t="shared" ref="E58:G58" si="18">_xlfn.XLOOKUP(E56,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>None</v>
       </c>
       <c r="F58" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v>None</v>
-      </c>
-      <c r="G58" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v>None</v>
-      </c>
-      <c r="H58" s="3" t="str">
-        <f t="shared" ref="H58:L58" si="18">_xlfn.XLOOKUP(H56,$B$26:$XFD$26,$B$28:$XFD$28)</f>
-        <v>None</v>
-      </c>
-      <c r="I58" s="3" t="str">
         <f t="shared" si="18"/>
         <v>None</v>
       </c>
-      <c r="J58" s="3" t="str">
+      <c r="G58" s="3" t="str">
         <f t="shared" si="18"/>
         <v>None</v>
       </c>
+      <c r="H58" s="3" t="str">
+        <f t="shared" ref="H58:L58" si="19">_xlfn.XLOOKUP(H56,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <v>None</v>
+      </c>
+      <c r="I58" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v>None</v>
+      </c>
+      <c r="J58" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v>None</v>
+      </c>
       <c r="K58" s="3" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>None</v>
       </c>
       <c r="L58" s="3" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>None</v>
       </c>
       <c r="M58" s="3"/>
@@ -4995,35 +4994,35 @@
         <v>region in which the market is</v>
       </c>
       <c r="E59" t="str">
-        <f t="shared" ref="E59:G59" si="19">_xlfn.XLOOKUP(E56,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <f t="shared" ref="E59:G59" si="20">_xlfn.XLOOKUP(E56,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>type of market</v>
       </c>
       <c r="F59" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>name of the market</v>
       </c>
       <c r="G59" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>type of energy (electr., heat, etc.)</v>
       </c>
       <c r="H59" t="str">
-        <f t="shared" ref="H59:L59" si="20">_xlfn.XLOOKUP(H56,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <f t="shared" ref="H59:L59" si="21">_xlfn.XLOOKUP(H56,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>action to be undertaken for market</v>
       </c>
       <c r="I59" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>clearing type (ex-ante, ex-post)</v>
       </c>
       <c r="J59" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>clearing method (pda, etc.)</v>
       </c>
       <c r="K59" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>pricing method (uniform, etc.)</v>
       </c>
       <c r="L59" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>coupling method (above, below)</v>
       </c>
     </row>
@@ -5085,35 +5084,35 @@
         <v>0</v>
       </c>
       <c r="B65" s="9" t="str">
-        <f>B26</f>
+        <f t="shared" ref="B65:I65" si="22">B26</f>
         <v>timestamp</v>
       </c>
       <c r="C65" s="9" t="str">
-        <f>C26</f>
+        <f t="shared" si="22"/>
         <v>timestep</v>
       </c>
       <c r="D65" s="9" t="str">
-        <f>D26</f>
+        <f t="shared" si="22"/>
         <v>region</v>
       </c>
       <c r="E65" s="9" t="str">
-        <f>E26</f>
+        <f t="shared" si="22"/>
         <v>market</v>
       </c>
       <c r="F65" s="9" t="str">
-        <f>F26</f>
+        <f t="shared" si="22"/>
         <v>name</v>
       </c>
       <c r="G65" s="9" t="str">
-        <f>G26</f>
+        <f t="shared" si="22"/>
         <v>energy_type</v>
       </c>
       <c r="H65" s="9" t="str">
-        <f>H26</f>
+        <f t="shared" si="22"/>
         <v>type_transaction</v>
       </c>
       <c r="I65" s="9" t="str">
-        <f>I26</f>
+        <f t="shared" si="22"/>
         <v>id_agent</v>
       </c>
       <c r="J65" s="9" t="str">
@@ -5155,23 +5154,23 @@
         <v>datetime</v>
       </c>
       <c r="C66" s="3" t="str">
-        <f t="shared" ref="C66:F66" si="21">_xlfn.XLOOKUP(C65,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="C66:F66" si="23">_xlfn.XLOOKUP(C65,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>datetime</v>
       </c>
       <c r="D66" s="3" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>categorical</v>
       </c>
       <c r="E66" s="3" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>categorical</v>
       </c>
       <c r="F66" s="3" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>categorical</v>
       </c>
       <c r="G66" s="3" t="str">
-        <f t="shared" ref="G66" si="22">_xlfn.XLOOKUP(G65,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="G66" si="24">_xlfn.XLOOKUP(G65,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
       <c r="H66" s="3" t="str">
@@ -5183,31 +5182,31 @@
         <v>categorical</v>
       </c>
       <c r="J66" s="3" t="str">
-        <f t="shared" ref="J66:P66" si="23">_xlfn.XLOOKUP(J65,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="J66:P66" si="25">_xlfn.XLOOKUP(J65,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>uint64</v>
       </c>
       <c r="K66" s="3" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>uint64</v>
       </c>
       <c r="L66" s="3" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>int32</v>
       </c>
       <c r="M66" s="3" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>int32</v>
       </c>
       <c r="N66" s="3" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>int64</v>
       </c>
       <c r="O66" s="3" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>int64</v>
       </c>
       <c r="P66" s="3" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>int8</v>
       </c>
     </row>
@@ -5221,27 +5220,27 @@
         <v>s</v>
       </c>
       <c r="C67" s="3" t="str">
-        <f t="shared" ref="C67:F67" si="24">_xlfn.XLOOKUP(C65,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <f t="shared" ref="C67:F67" si="26">_xlfn.XLOOKUP(C65,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>s</v>
       </c>
       <c r="D67" s="3" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>None</v>
       </c>
       <c r="E67" s="3" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>None</v>
       </c>
       <c r="F67" s="3" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>None</v>
       </c>
       <c r="G67" s="3" t="str">
-        <f t="shared" ref="G67" si="25">_xlfn.XLOOKUP(G65,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <f t="shared" ref="G67" si="27">_xlfn.XLOOKUP(G65,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>None</v>
       </c>
       <c r="H67" s="3" t="str">
-        <f t="shared" ref="H67" si="26">_xlfn.XLOOKUP(H65,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <f t="shared" ref="H67" si="28">_xlfn.XLOOKUP(H65,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>None</v>
       </c>
       <c r="I67" s="3" t="str">
@@ -5249,31 +5248,31 @@
         <v>None</v>
       </c>
       <c r="J67" s="3" t="str">
-        <f t="shared" ref="J67:P67" si="27">_xlfn.XLOOKUP(J65,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <f t="shared" ref="J67:P67" si="29">_xlfn.XLOOKUP(J65,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>Wh</v>
       </c>
       <c r="K67" s="3" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>Wh</v>
       </c>
       <c r="L67" s="3" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>€e7/Wh</v>
       </c>
       <c r="M67" s="3" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>€e7/Wh</v>
       </c>
       <c r="N67" s="3" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>€e7</v>
       </c>
       <c r="O67" s="3" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>€e7</v>
       </c>
       <c r="P67" s="3" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0-100</v>
       </c>
     </row>
@@ -5287,27 +5286,27 @@
         <v>current timestamp</v>
       </c>
       <c r="C68" t="str">
-        <f t="shared" ref="C68:F68" si="28">_xlfn.XLOOKUP(C65,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <f t="shared" ref="C68:F68" si="30">_xlfn.XLOOKUP(C65,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>timestep (can be in future)</v>
       </c>
       <c r="D68" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>region in which the market is</v>
       </c>
       <c r="E68" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>type of market</v>
       </c>
       <c r="F68" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>name of the market</v>
       </c>
       <c r="G68" t="str">
-        <f t="shared" ref="G68" si="29">_xlfn.XLOOKUP(G65,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <f t="shared" ref="G68" si="31">_xlfn.XLOOKUP(G65,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>type of energy (electr., heat, etc.)</v>
       </c>
       <c r="H68" t="str">
-        <f t="shared" ref="H68" si="30">_xlfn.XLOOKUP(H65,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <f t="shared" ref="H68" si="32">_xlfn.XLOOKUP(H65,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>source of the costs/profits (e.g. Market, levies, balancing)</v>
       </c>
       <c r="I68" t="str">
@@ -5315,31 +5314,31 @@
         <v>agent id (also serves as main meter)</v>
       </c>
       <c r="J68" t="str">
-        <f t="shared" ref="J68:P68" si="31">_xlfn.XLOOKUP(J65,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <f t="shared" ref="J68:P68" si="33">_xlfn.XLOOKUP(J65,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>energy going into the meter</v>
       </c>
       <c r="K68" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>energy going out of the meter</v>
       </c>
       <c r="L68" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>spec. price for incoming energy</v>
       </c>
       <c r="M68" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>spec. price for outflowing energy</v>
       </c>
       <c r="N68" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>total price for incoming energy</v>
       </c>
       <c r="O68" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>total price for outflowing energy</v>
       </c>
       <c r="P68" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>quality share of energy (one column per type)</v>
       </c>
     </row>
@@ -5440,31 +5439,31 @@
         <v>datetime</v>
       </c>
       <c r="C75" s="3" t="str">
-        <f t="shared" ref="C75:E75" si="32">_xlfn.XLOOKUP(C74,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="C75:E75" si="34">_xlfn.XLOOKUP(C74,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
       <c r="D75" s="3" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>categorical</v>
       </c>
       <c r="E75" s="3" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>categorical</v>
       </c>
       <c r="F75" s="3" t="str">
-        <f t="shared" ref="F75:I75" si="33">_xlfn.XLOOKUP(F74,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="F75:I75" si="35">_xlfn.XLOOKUP(F74,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
       <c r="G75" s="3" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>str</v>
       </c>
       <c r="H75" s="3" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>uint64</v>
       </c>
       <c r="I75" s="3" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>uint64</v>
       </c>
     </row>
@@ -5478,31 +5477,31 @@
         <v>s</v>
       </c>
       <c r="C76" s="3" t="str">
-        <f t="shared" ref="C76:E76" si="34">_xlfn.XLOOKUP(C74,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <f t="shared" ref="C76:E76" si="36">_xlfn.XLOOKUP(C74,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>None</v>
       </c>
       <c r="D76" s="3" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>None</v>
       </c>
       <c r="E76" s="3" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>None</v>
       </c>
       <c r="F76" s="3" t="str">
-        <f t="shared" ref="F76:I76" si="35">_xlfn.XLOOKUP(F74,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <f t="shared" ref="F76:I76" si="37">_xlfn.XLOOKUP(F74,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>None</v>
       </c>
       <c r="G76" s="3" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>None</v>
       </c>
       <c r="H76" s="3" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>Wh</v>
       </c>
       <c r="I76" s="3" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>Wh</v>
       </c>
     </row>
@@ -5516,31 +5515,31 @@
         <v>current timestamp</v>
       </c>
       <c r="C77" t="str">
-        <f t="shared" ref="C77:E77" si="36">_xlfn.XLOOKUP(C74,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <f t="shared" ref="C77:E77" si="38">_xlfn.XLOOKUP(C74,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>region in which the market is</v>
       </c>
       <c r="D77" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>type of market</v>
       </c>
       <c r="E77" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>name of the market</v>
       </c>
       <c r="F77" t="str">
-        <f t="shared" ref="F77:I77" si="37">_xlfn.XLOOKUP(F74,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <f t="shared" ref="F77:I77" si="39">_xlfn.XLOOKUP(F74,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>agent id (also serves as main meter)</v>
       </c>
       <c r="G77" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>id of the (sub-)meter</v>
       </c>
       <c r="H77" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>energy going into the meter</v>
       </c>
       <c r="I77" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>energy going out of the meter</v>
       </c>
     </row>
@@ -5641,31 +5640,31 @@
         <v>datetime</v>
       </c>
       <c r="C84" s="3" t="str">
-        <f t="shared" ref="C84:I84" si="38">_xlfn.XLOOKUP(C83,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="C84:I84" si="40">_xlfn.XLOOKUP(C83,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
       <c r="D84" s="3" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>categorical</v>
       </c>
       <c r="E84" s="3" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>categorical</v>
       </c>
       <c r="F84" s="3" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>categorical</v>
       </c>
       <c r="G84" s="3" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>str</v>
       </c>
       <c r="H84" s="3" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>uint64</v>
       </c>
       <c r="I84" s="3" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>uint64</v>
       </c>
     </row>
@@ -5679,31 +5678,31 @@
         <v>s</v>
       </c>
       <c r="C85" s="3" t="str">
-        <f t="shared" ref="C85:I85" si="39">_xlfn.XLOOKUP(C83,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <f t="shared" ref="C85:I85" si="41">_xlfn.XLOOKUP(C83,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>None</v>
       </c>
       <c r="D85" s="3" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>None</v>
       </c>
       <c r="E85" s="3" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>None</v>
       </c>
       <c r="F85" s="3" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>None</v>
       </c>
       <c r="G85" s="3" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>None</v>
       </c>
       <c r="H85" s="3" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>Wh</v>
       </c>
       <c r="I85" s="3" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>Wh</v>
       </c>
     </row>
@@ -5717,31 +5716,31 @@
         <v>current timestamp</v>
       </c>
       <c r="C86" t="str">
-        <f t="shared" ref="C86:I86" si="40">_xlfn.XLOOKUP(C83,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <f t="shared" ref="C86:I86" si="42">_xlfn.XLOOKUP(C83,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>region in which the market is</v>
       </c>
       <c r="D86" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>type of market</v>
       </c>
       <c r="E86" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>name of the market</v>
       </c>
       <c r="F86" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>agent id (also serves as main meter)</v>
       </c>
       <c r="G86" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>id of the (sub-)meter</v>
       </c>
       <c r="H86" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>energy going into the meter</v>
       </c>
       <c r="I86" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>energy going out of the meter</v>
       </c>
     </row>
@@ -5857,47 +5856,47 @@
         <v>datetime</v>
       </c>
       <c r="C93" s="3" t="str">
-        <f t="shared" ref="C93" si="41">_xlfn.XLOOKUP(C92,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="C93" si="43">_xlfn.XLOOKUP(C92,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>datetime</v>
       </c>
       <c r="D93" s="3" t="str">
-        <f t="shared" ref="D93" si="42">_xlfn.XLOOKUP(D92,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="D93" si="44">_xlfn.XLOOKUP(D92,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
       <c r="E93" s="3" t="str">
-        <f t="shared" ref="E93" si="43">_xlfn.XLOOKUP(E92,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="E93" si="45">_xlfn.XLOOKUP(E92,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
       <c r="F93" s="3" t="str">
-        <f t="shared" ref="F93" si="44">_xlfn.XLOOKUP(F92,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="F93" si="46">_xlfn.XLOOKUP(F92,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
       <c r="G93" s="3" t="str">
-        <f t="shared" ref="G93" si="45">_xlfn.XLOOKUP(G92,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="G93" si="47">_xlfn.XLOOKUP(G92,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
       <c r="H93" s="3" t="str">
-        <f t="shared" ref="H93" si="46">_xlfn.XLOOKUP(H92,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="H93" si="48">_xlfn.XLOOKUP(H92,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>uint64</v>
       </c>
       <c r="I93" s="3" t="str">
-        <f t="shared" ref="I93" si="47">_xlfn.XLOOKUP(I92,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="I93" si="49">_xlfn.XLOOKUP(I92,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>uint64</v>
       </c>
       <c r="J93" s="3" t="str">
-        <f t="shared" ref="J93" si="48">_xlfn.XLOOKUP(J92,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="J93" si="50">_xlfn.XLOOKUP(J92,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>int32</v>
       </c>
       <c r="K93" s="3" t="str">
-        <f t="shared" ref="K93" si="49">_xlfn.XLOOKUP(K92,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="K93" si="51">_xlfn.XLOOKUP(K92,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>int32</v>
       </c>
       <c r="L93" s="3" t="str">
-        <f t="shared" ref="L93" si="50">_xlfn.XLOOKUP(L92,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="L93" si="52">_xlfn.XLOOKUP(L92,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>int64</v>
       </c>
       <c r="M93" s="3" t="str">
-        <f t="shared" ref="M93" si="51">_xlfn.XLOOKUP(M92,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="M93" si="53">_xlfn.XLOOKUP(M92,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>int64</v>
       </c>
     </row>
@@ -5911,47 +5910,47 @@
         <v>s</v>
       </c>
       <c r="C94" s="3" t="str">
-        <f t="shared" ref="C94:I94" si="52">_xlfn.XLOOKUP(C92,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <f t="shared" ref="C94:I94" si="54">_xlfn.XLOOKUP(C92,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>s</v>
       </c>
       <c r="D94" s="3" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>None</v>
       </c>
       <c r="E94" s="3" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>None</v>
       </c>
       <c r="F94" s="3" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>None</v>
       </c>
       <c r="G94" s="3" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>None</v>
       </c>
       <c r="H94" s="3" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>Wh</v>
       </c>
       <c r="I94" s="3" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>Wh</v>
       </c>
       <c r="J94" s="3" t="str">
-        <f t="shared" ref="J94:M94" si="53">_xlfn.XLOOKUP(J92,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <f t="shared" ref="J94:M94" si="55">_xlfn.XLOOKUP(J92,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>€e7/Wh</v>
       </c>
       <c r="K94" s="3" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>€e7/Wh</v>
       </c>
       <c r="L94" s="3" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>€e7</v>
       </c>
       <c r="M94" s="3" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>€e7</v>
       </c>
     </row>
@@ -5965,47 +5964,47 @@
         <v>current timestamp</v>
       </c>
       <c r="C95" t="str">
-        <f t="shared" ref="C95:I95" si="54">_xlfn.XLOOKUP(C92,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <f t="shared" ref="C95:I95" si="56">_xlfn.XLOOKUP(C92,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>timestep (can be in future)</v>
       </c>
       <c r="D95" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>region in which the market is</v>
       </c>
       <c r="E95" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>type of market</v>
       </c>
       <c r="F95" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>name of the market</v>
       </c>
       <c r="G95" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>source of the costs/profits (e.g. Market, levies, balancing)</v>
       </c>
       <c r="H95" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>energy going into the meter</v>
       </c>
       <c r="I95" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>energy going out of the meter</v>
       </c>
       <c r="J95" t="str">
-        <f t="shared" ref="J95:M95" si="55">_xlfn.XLOOKUP(J92,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <f t="shared" ref="J95:M95" si="57">_xlfn.XLOOKUP(J92,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>spec. price for incoming energy</v>
       </c>
       <c r="K95" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>spec. price for outflowing energy</v>
       </c>
       <c r="L95" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>total price for incoming energy</v>
       </c>
       <c r="M95" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>total price for outflowing energy</v>
       </c>
     </row>
@@ -6125,51 +6124,51 @@
         <v>datetime</v>
       </c>
       <c r="C102" s="3" t="str">
-        <f t="shared" ref="C102" si="56">_xlfn.XLOOKUP(C101,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="C102" si="58">_xlfn.XLOOKUP(C101,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
       <c r="D102" s="3" t="str">
-        <f t="shared" ref="D102" si="57">_xlfn.XLOOKUP(D101,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="D102" si="59">_xlfn.XLOOKUP(D101,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
       <c r="E102" s="3" t="str">
-        <f t="shared" ref="E102" si="58">_xlfn.XLOOKUP(E101,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="E102" si="60">_xlfn.XLOOKUP(E101,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
       <c r="F102" s="3" t="str">
-        <f t="shared" ref="F102" si="59">_xlfn.XLOOKUP(F101,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="F102" si="61">_xlfn.XLOOKUP(F101,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
       <c r="G102" s="3" t="str">
-        <f t="shared" ref="G102" si="60">_xlfn.XLOOKUP(G101,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="G102" si="62">_xlfn.XLOOKUP(G101,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
       <c r="H102" s="3" t="str">
-        <f t="shared" ref="H102" si="61">_xlfn.XLOOKUP(H101,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="H102" si="63">_xlfn.XLOOKUP(H101,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>uint64</v>
       </c>
       <c r="I102" s="3" t="str">
-        <f t="shared" ref="I102" si="62">_xlfn.XLOOKUP(I101,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="I102" si="64">_xlfn.XLOOKUP(I101,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>uint64</v>
       </c>
       <c r="J102" s="3" t="str">
-        <f t="shared" ref="J102" si="63">_xlfn.XLOOKUP(J101,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="J102" si="65">_xlfn.XLOOKUP(J101,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>int32</v>
       </c>
       <c r="K102" s="3" t="str">
-        <f t="shared" ref="K102" si="64">_xlfn.XLOOKUP(K101,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="K102" si="66">_xlfn.XLOOKUP(K101,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>int32</v>
       </c>
       <c r="L102" s="3" t="str">
-        <f t="shared" ref="L102" si="65">_xlfn.XLOOKUP(L101,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="L102" si="67">_xlfn.XLOOKUP(L101,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>int64</v>
       </c>
       <c r="M102" s="3" t="str">
-        <f t="shared" ref="M102:N102" si="66">_xlfn.XLOOKUP(M101,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="M102:N102" si="68">_xlfn.XLOOKUP(M101,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>int64</v>
       </c>
       <c r="N102" s="3" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>int8</v>
       </c>
     </row>
@@ -6183,51 +6182,51 @@
         <v>s</v>
       </c>
       <c r="C103" s="3" t="str">
-        <f t="shared" ref="C103:E103" si="67">_xlfn.XLOOKUP(C101,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <f t="shared" ref="C103:E103" si="69">_xlfn.XLOOKUP(C101,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>None</v>
       </c>
       <c r="D103" s="3" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>None</v>
       </c>
       <c r="E103" s="3" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>None</v>
       </c>
       <c r="F103" s="3" t="str">
-        <f t="shared" ref="F103:M103" si="68">_xlfn.XLOOKUP(F101,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <f t="shared" ref="F103:M103" si="70">_xlfn.XLOOKUP(F101,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>None</v>
       </c>
       <c r="G103" s="3" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>None</v>
       </c>
       <c r="H103" s="3" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>Wh</v>
       </c>
       <c r="I103" s="3" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>Wh</v>
       </c>
       <c r="J103" s="3" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>€e7/Wh</v>
       </c>
       <c r="K103" s="3" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>€e7/Wh</v>
       </c>
       <c r="L103" s="3" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>€e7</v>
       </c>
       <c r="M103" s="3" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>€e7</v>
       </c>
       <c r="N103" s="3" t="str">
-        <f t="shared" ref="N103" si="69">_xlfn.XLOOKUP(N101,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <f t="shared" ref="N103" si="71">_xlfn.XLOOKUP(N101,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>0-100</v>
       </c>
     </row>
@@ -6241,51 +6240,51 @@
         <v>current timestamp</v>
       </c>
       <c r="C104" t="str">
-        <f t="shared" ref="C104:E104" si="70">_xlfn.XLOOKUP(C101,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <f t="shared" ref="C104:E104" si="72">_xlfn.XLOOKUP(C101,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>region in which the market is</v>
       </c>
       <c r="D104" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>type of market</v>
       </c>
       <c r="E104" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>name of the market</v>
       </c>
       <c r="F104" t="str">
-        <f t="shared" ref="F104:M104" si="71">_xlfn.XLOOKUP(F101,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <f t="shared" ref="F104:M104" si="73">_xlfn.XLOOKUP(F101,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>source of the costs/profits (e.g. Market, levies, balancing)</v>
       </c>
       <c r="G104" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>agent id (also serves as main meter)</v>
       </c>
       <c r="H104" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>energy going into the meter</v>
       </c>
       <c r="I104" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>energy going out of the meter</v>
       </c>
       <c r="J104" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>spec. price for incoming energy</v>
       </c>
       <c r="K104" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>spec. price for outflowing energy</v>
       </c>
       <c r="L104" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>total price for incoming energy</v>
       </c>
       <c r="M104" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>total price for outflowing energy</v>
       </c>
       <c r="N104" t="str">
-        <f t="shared" ref="N104" si="72">_xlfn.XLOOKUP(N101,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <f t="shared" ref="N104" si="74">_xlfn.XLOOKUP(N101,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>quality share of energy (one column per type)</v>
       </c>
     </row>
@@ -6401,23 +6400,23 @@
         <v>categorical</v>
       </c>
       <c r="C111" s="3" t="str">
-        <f t="shared" ref="C111" si="73">_xlfn.XLOOKUP(C110,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="C111" si="75">_xlfn.XLOOKUP(C110,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
       <c r="D111" s="3" t="str">
-        <f t="shared" ref="D111" si="74">_xlfn.XLOOKUP(D110,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="D111" si="76">_xlfn.XLOOKUP(D110,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
       <c r="E111" s="3" t="str">
-        <f t="shared" ref="E111" si="75">_xlfn.XLOOKUP(E110,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="E111" si="77">_xlfn.XLOOKUP(E110,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
       <c r="F111" s="3" t="str">
-        <f t="shared" ref="F111" si="76">_xlfn.XLOOKUP(F110,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="F111" si="78">_xlfn.XLOOKUP(F110,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>uint64</v>
       </c>
       <c r="G111" s="3" t="str">
-        <f t="shared" ref="G111" si="77">_xlfn.XLOOKUP(G110,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="G111" si="79">_xlfn.XLOOKUP(G110,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>uint64</v>
       </c>
       <c r="H111" s="3" t="str">
@@ -6425,23 +6424,23 @@
         <v>uint64</v>
       </c>
       <c r="I111" s="3" t="str">
-        <f t="shared" ref="I111" si="78">_xlfn.XLOOKUP(I110,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="I111" si="80">_xlfn.XLOOKUP(I110,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>int64</v>
       </c>
       <c r="J111" s="3" t="str">
-        <f t="shared" ref="J111" si="79">_xlfn.XLOOKUP(J110,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="J111" si="81">_xlfn.XLOOKUP(J110,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>int64</v>
       </c>
       <c r="K111" s="3" t="str">
-        <f t="shared" ref="K111" si="80">_xlfn.XLOOKUP(K110,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="K111" si="82">_xlfn.XLOOKUP(K110,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>int64</v>
       </c>
       <c r="L111" s="3" t="str">
-        <f t="shared" ref="L111:M111" si="81">_xlfn.XLOOKUP(L110,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="L111:M111" si="83">_xlfn.XLOOKUP(L110,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>int8</v>
       </c>
       <c r="M111" s="3" t="str">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>categorical</v>
       </c>
     </row>
@@ -6455,23 +6454,23 @@
         <v>None</v>
       </c>
       <c r="C112" s="3" t="str">
-        <f t="shared" ref="C112:L112" si="82">_xlfn.XLOOKUP(C110,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <f t="shared" ref="C112:L112" si="84">_xlfn.XLOOKUP(C110,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>None</v>
       </c>
       <c r="D112" s="3" t="str">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>None</v>
       </c>
       <c r="E112" s="3" t="str">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>None</v>
       </c>
       <c r="F112" s="3" t="str">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>Wh</v>
       </c>
       <c r="G112" s="3" t="str">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>Wh</v>
       </c>
       <c r="H112" s="3" t="str">
@@ -6479,23 +6478,23 @@
         <v>Wh</v>
       </c>
       <c r="I112" s="3" t="str">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>€e7</v>
       </c>
       <c r="J112" s="3" t="str">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>€e7</v>
       </c>
       <c r="K112" s="3" t="str">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>€e7</v>
       </c>
       <c r="L112" s="3" t="str">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>0-100</v>
       </c>
       <c r="M112" s="3" t="str">
-        <f t="shared" ref="M112" si="83">_xlfn.XLOOKUP(M110,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <f t="shared" ref="M112" si="85">_xlfn.XLOOKUP(M110,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>None</v>
       </c>
     </row>
@@ -6509,23 +6508,23 @@
         <v>region in which the market is</v>
       </c>
       <c r="C113" t="str">
-        <f t="shared" ref="C113:L113" si="84">_xlfn.XLOOKUP(C110,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <f t="shared" ref="C113:L113" si="86">_xlfn.XLOOKUP(C110,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>type of market</v>
       </c>
       <c r="D113" t="str">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>name of the market</v>
       </c>
       <c r="E113" t="str">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>agent id (also serves as main meter)</v>
       </c>
       <c r="F113" t="str">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>energy going into the meter</v>
       </c>
       <c r="G113" t="str">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>energy going out of the meter</v>
       </c>
       <c r="H113" t="str">
@@ -6533,23 +6532,23 @@
         <v>used energy over all timesteps</v>
       </c>
       <c r="I113" t="str">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>total price for incoming energy</v>
       </c>
       <c r="J113" t="str">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>total price for outflowing energy</v>
       </c>
       <c r="K113" t="str">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>balance of bank account</v>
       </c>
       <c r="L113" t="str">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>quality share of energy (one column per type)</v>
       </c>
       <c r="M113" t="str">
-        <f t="shared" ref="M113" si="85">_xlfn.XLOOKUP(M110,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <f t="shared" ref="M113" si="87">_xlfn.XLOOKUP(M110,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>types of plants (per agent)</v>
       </c>
     </row>
@@ -6645,27 +6644,27 @@
         <v>categorical</v>
       </c>
       <c r="C120" s="3" t="str">
-        <f t="shared" ref="C120" si="86">_xlfn.XLOOKUP(C119,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="C120" si="88">_xlfn.XLOOKUP(C119,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
       <c r="D120" s="3" t="str">
-        <f t="shared" ref="D120" si="87">_xlfn.XLOOKUP(D119,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="D120" si="89">_xlfn.XLOOKUP(D119,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
       <c r="E120" s="3" t="str">
-        <f t="shared" ref="E120" si="88">_xlfn.XLOOKUP(E119,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="E120" si="90">_xlfn.XLOOKUP(E119,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
       <c r="F120" s="3" t="str">
-        <f t="shared" ref="F120" si="89">_xlfn.XLOOKUP(F119,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="F120" si="91">_xlfn.XLOOKUP(F119,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>str</v>
       </c>
       <c r="G120" s="3" t="str">
-        <f t="shared" ref="G120" si="90">_xlfn.XLOOKUP(G119,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="G120" si="92">_xlfn.XLOOKUP(G119,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
       <c r="H120" s="3" t="str">
-        <f t="shared" ref="H120" si="91">_xlfn.XLOOKUP(H119,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="H120" si="93">_xlfn.XLOOKUP(H119,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
       <c r="I120" s="3"/>
@@ -6685,27 +6684,27 @@
         <v>None</v>
       </c>
       <c r="C121" s="3" t="str">
-        <f t="shared" ref="C121:H121" si="92">_xlfn.XLOOKUP(C119,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <f t="shared" ref="C121:H121" si="94">_xlfn.XLOOKUP(C119,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>None</v>
       </c>
       <c r="D121" s="3" t="str">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>None</v>
       </c>
       <c r="E121" s="3" t="str">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>None</v>
       </c>
       <c r="F121" s="3" t="str">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>None</v>
       </c>
       <c r="G121" s="3" t="str">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>None</v>
       </c>
       <c r="H121" s="3" t="str">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>None</v>
       </c>
       <c r="I121" s="3"/>
@@ -6725,27 +6724,27 @@
         <v>region in which the market is</v>
       </c>
       <c r="C122" t="str">
-        <f t="shared" ref="C122:H122" si="93">_xlfn.XLOOKUP(C119,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <f t="shared" ref="C122:H122" si="95">_xlfn.XLOOKUP(C119,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>type of market</v>
       </c>
       <c r="D122" t="str">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>name of the market</v>
       </c>
       <c r="E122" t="str">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>agent id (also serves as main meter)</v>
       </c>
       <c r="F122" t="str">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>id of the (sub-)meter</v>
       </c>
       <c r="G122" t="str">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>type of meter</v>
       </c>
       <c r="H122" t="str">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>quality of energy</v>
       </c>
     </row>
@@ -6826,9 +6825,9 @@
         <f>H26</f>
         <v>type_transaction</v>
       </c>
-      <c r="H128" t="str">
-        <f>I26</f>
-        <v>id_agent</v>
+      <c r="H128" s="9" t="str">
+        <f>J26</f>
+        <v>id_agent_in</v>
       </c>
       <c r="I128" s="9" t="str">
         <f>N26</f>
@@ -6855,19 +6854,19 @@
         <v>datetime</v>
       </c>
       <c r="C129" s="3" t="str">
-        <f t="shared" ref="C129:F129" si="94">_xlfn.XLOOKUP(C128,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="C129:F129" si="96">_xlfn.XLOOKUP(C128,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>datetime</v>
       </c>
       <c r="D129" s="3" t="str">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>categorical</v>
       </c>
       <c r="E129" s="3" t="str">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>categorical</v>
       </c>
       <c r="F129" s="3" t="str">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>categorical</v>
       </c>
       <c r="G129" s="3" t="str">
@@ -6903,19 +6902,19 @@
         <v>s</v>
       </c>
       <c r="C130" s="3" t="str">
-        <f t="shared" ref="C130:F130" si="95">_xlfn.XLOOKUP(C128,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <f t="shared" ref="C130:F130" si="97">_xlfn.XLOOKUP(C128,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>s</v>
       </c>
       <c r="D130" s="3" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>None</v>
       </c>
       <c r="E130" s="3" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>None</v>
       </c>
       <c r="F130" s="3" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>None</v>
       </c>
       <c r="G130" s="3" t="str">
@@ -6951,19 +6950,19 @@
         <v>current timestamp</v>
       </c>
       <c r="C131" t="str">
-        <f t="shared" ref="C131:F131" si="96">_xlfn.XLOOKUP(C128,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <f t="shared" ref="C131:F131" si="98">_xlfn.XLOOKUP(C128,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>timestep (can be in future)</v>
       </c>
       <c r="D131" t="str">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>region in which the market is</v>
       </c>
       <c r="E131" t="str">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>type of market</v>
       </c>
       <c r="F131" t="str">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>name of the market</v>
       </c>
       <c r="G131" t="str">
@@ -6972,7 +6971,7 @@
       </c>
       <c r="H131" t="str">
         <f>_xlfn.XLOOKUP(H128,$B$26:$XFD$26,$B$29:$XFD$29)</f>
-        <v>agent id (also serves as main meter)</v>
+        <v>agent id of incoming energy</v>
       </c>
       <c r="I131" t="str">
         <f>_xlfn.XLOOKUP(I128,$B$26:$XFD$26,$B$29:$XFD$29)</f>
@@ -7045,28 +7044,28 @@
         <v>timestamp</v>
       </c>
       <c r="C137" t="str">
-        <f t="shared" ref="C137:H137" si="97">C128</f>
+        <f t="shared" ref="C137:H137" si="99">C128</f>
         <v>timestep</v>
       </c>
       <c r="D137" t="str">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>region</v>
       </c>
       <c r="E137" t="str">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>market</v>
       </c>
       <c r="F137" t="str">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>name</v>
       </c>
       <c r="G137" t="str">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>type_transaction</v>
       </c>
       <c r="H137" t="str">
-        <f t="shared" si="97"/>
-        <v>id_agent</v>
+        <f t="shared" si="99"/>
+        <v>id_agent_in</v>
       </c>
       <c r="I137" t="str">
         <f>I128</f>
@@ -7091,31 +7090,31 @@
         <v>datetime</v>
       </c>
       <c r="C138" s="3" t="str">
-        <f t="shared" ref="C138:I138" si="98">_xlfn.XLOOKUP(C137,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="C138:I138" si="100">_xlfn.XLOOKUP(C137,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>datetime</v>
       </c>
       <c r="D138" s="3" t="str">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>categorical</v>
       </c>
       <c r="E138" s="3" t="str">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>categorical</v>
       </c>
       <c r="F138" s="3" t="str">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>categorical</v>
       </c>
       <c r="G138" s="3" t="str">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>categorical</v>
       </c>
       <c r="H138" s="3" t="str">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>categorical</v>
       </c>
       <c r="I138" s="3" t="str">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>uint64</v>
       </c>
       <c r="J138" s="3" t="str">
@@ -7140,31 +7139,31 @@
         <v>s</v>
       </c>
       <c r="C139" s="3" t="str">
-        <f t="shared" ref="C139:I139" si="99">_xlfn.XLOOKUP(C137,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <f t="shared" ref="C139:I139" si="101">_xlfn.XLOOKUP(C137,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>s</v>
       </c>
       <c r="D139" s="3" t="str">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>None</v>
       </c>
       <c r="E139" s="3" t="str">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>None</v>
       </c>
       <c r="F139" s="3" t="str">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>None</v>
       </c>
       <c r="G139" s="3" t="str">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>None</v>
       </c>
       <c r="H139" s="3" t="str">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>None</v>
       </c>
       <c r="I139" s="3" t="str">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>Wh</v>
       </c>
       <c r="J139" s="3" t="str">
@@ -7189,31 +7188,31 @@
         <v>current timestamp</v>
       </c>
       <c r="C140" t="str">
-        <f t="shared" ref="C140:I140" si="100">_xlfn.XLOOKUP(C137,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <f t="shared" ref="C140:I140" si="102">_xlfn.XLOOKUP(C137,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>timestep (can be in future)</v>
       </c>
       <c r="D140" t="str">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>region in which the market is</v>
       </c>
       <c r="E140" t="str">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>type of market</v>
       </c>
       <c r="F140" t="str">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>name of the market</v>
       </c>
       <c r="G140" t="str">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>source of the costs/profits (e.g. Market, levies, balancing)</v>
       </c>
       <c r="H140" t="str">
-        <f t="shared" si="100"/>
-        <v>agent id (also serves as main meter)</v>
+        <f t="shared" si="102"/>
+        <v>agent id of incoming energy</v>
       </c>
       <c r="I140" t="str">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>energy going into the meter</v>
       </c>
       <c r="J140" t="str">
@@ -7303,8 +7302,8 @@
         <v>type_transaction</v>
       </c>
       <c r="H146" s="9" t="str">
-        <f>I26</f>
-        <v>id_agent</v>
+        <f>K26</f>
+        <v>id_agent_out</v>
       </c>
       <c r="I146" s="9" t="str">
         <f>O26</f>
@@ -7333,43 +7332,43 @@
         <v>datetime</v>
       </c>
       <c r="C147" s="3" t="str">
-        <f t="shared" ref="C147:F147" si="101">_xlfn.XLOOKUP(C146,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="C147:F147" si="103">_xlfn.XLOOKUP(C146,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>datetime</v>
       </c>
       <c r="D147" s="3" t="str">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>categorical</v>
       </c>
       <c r="E147" s="3" t="str">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>categorical</v>
       </c>
       <c r="F147" s="3" t="str">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>categorical</v>
       </c>
       <c r="G147" s="3" t="str">
-        <f t="shared" ref="G147:L147" si="102">_xlfn.XLOOKUP(G146,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="G147:L147" si="104">_xlfn.XLOOKUP(G146,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
       <c r="H147" s="3" t="str">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>categorical</v>
       </c>
       <c r="I147" s="3" t="str">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>uint64</v>
       </c>
       <c r="J147" s="3" t="str">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>int32</v>
       </c>
       <c r="K147" s="3" t="str">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>int64</v>
       </c>
       <c r="L147" s="3" t="str">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>categorical</v>
       </c>
       <c r="N147" s="3"/>
@@ -7385,43 +7384,43 @@
         <v>s</v>
       </c>
       <c r="C148" s="3" t="str">
-        <f t="shared" ref="C148:F148" si="103">_xlfn.XLOOKUP(C146,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <f t="shared" ref="C148:F148" si="105">_xlfn.XLOOKUP(C146,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>s</v>
       </c>
       <c r="D148" s="3" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>None</v>
       </c>
       <c r="E148" s="3" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>None</v>
       </c>
       <c r="F148" s="3" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>None</v>
       </c>
       <c r="G148" s="3" t="str">
-        <f t="shared" ref="G148:L148" si="104">_xlfn.XLOOKUP(G146,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <f t="shared" ref="G148:L148" si="106">_xlfn.XLOOKUP(G146,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>None</v>
       </c>
       <c r="H148" s="3" t="str">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>None</v>
       </c>
       <c r="I148" s="3" t="str">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>Wh</v>
       </c>
       <c r="J148" s="3" t="str">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>€e7/Wh</v>
       </c>
       <c r="K148" s="3" t="str">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>€e7</v>
       </c>
       <c r="L148" s="3" t="str">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>None</v>
       </c>
       <c r="N148" s="3"/>
@@ -7437,43 +7436,43 @@
         <v>current timestamp</v>
       </c>
       <c r="C149" t="str">
-        <f t="shared" ref="C149:F149" si="105">_xlfn.XLOOKUP(C146,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <f t="shared" ref="C149:F149" si="107">_xlfn.XLOOKUP(C146,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>timestep (can be in future)</v>
       </c>
       <c r="D149" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>region in which the market is</v>
       </c>
       <c r="E149" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>type of market</v>
       </c>
       <c r="F149" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>name of the market</v>
       </c>
       <c r="G149" t="str">
-        <f t="shared" ref="G149:L149" si="106">_xlfn.XLOOKUP(G146,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <f t="shared" ref="G149:L149" si="108">_xlfn.XLOOKUP(G146,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>source of the costs/profits (e.g. Market, levies, balancing)</v>
       </c>
       <c r="H149" t="str">
-        <f t="shared" si="106"/>
-        <v>agent id (also serves as main meter)</v>
+        <f t="shared" si="108"/>
+        <v>agent id of outgoing energy</v>
       </c>
       <c r="I149" t="str">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>energy going out of the meter</v>
       </c>
       <c r="J149" t="str">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>spec. price for outflowing energy</v>
       </c>
       <c r="K149" t="str">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>total price for outflowing energy</v>
       </c>
       <c r="L149" t="str">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>quality of energy</v>
       </c>
     </row>
@@ -7535,28 +7534,28 @@
         <v>timestamp</v>
       </c>
       <c r="C155" t="str">
-        <f t="shared" ref="C155:H155" si="107">C146</f>
+        <f t="shared" ref="C155:H155" si="109">C146</f>
         <v>timestep</v>
       </c>
       <c r="D155" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>region</v>
       </c>
       <c r="E155" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>market</v>
       </c>
       <c r="F155" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>name</v>
       </c>
       <c r="G155" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>type_transaction</v>
       </c>
       <c r="H155" t="str">
-        <f t="shared" si="107"/>
-        <v>id_agent</v>
+        <f t="shared" si="109"/>
+        <v>id_agent_out</v>
       </c>
       <c r="I155" t="str">
         <f>I146</f>
@@ -7585,43 +7584,43 @@
         <v>datetime</v>
       </c>
       <c r="C156" s="3" t="str">
-        <f t="shared" ref="C156:L156" si="108">_xlfn.XLOOKUP(C155,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="C156:L156" si="110">_xlfn.XLOOKUP(C155,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>datetime</v>
       </c>
       <c r="D156" s="3" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>categorical</v>
       </c>
       <c r="E156" s="3" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>categorical</v>
       </c>
       <c r="F156" s="3" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>categorical</v>
       </c>
       <c r="G156" s="3" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>categorical</v>
       </c>
       <c r="H156" s="3" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>categorical</v>
       </c>
       <c r="I156" s="3" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>uint64</v>
       </c>
       <c r="J156" s="3" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>int32</v>
       </c>
       <c r="K156" s="3" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>int64</v>
       </c>
       <c r="L156" s="3" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>categorical</v>
       </c>
       <c r="M156" s="3"/>
@@ -7638,43 +7637,43 @@
         <v>s</v>
       </c>
       <c r="C157" s="3" t="str">
-        <f t="shared" ref="C157:L157" si="109">_xlfn.XLOOKUP(C155,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <f t="shared" ref="C157:L157" si="111">_xlfn.XLOOKUP(C155,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>s</v>
       </c>
       <c r="D157" s="3" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>None</v>
       </c>
       <c r="E157" s="3" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>None</v>
       </c>
       <c r="F157" s="3" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>None</v>
       </c>
       <c r="G157" s="3" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>None</v>
       </c>
       <c r="H157" s="3" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>None</v>
       </c>
       <c r="I157" s="3" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>Wh</v>
       </c>
       <c r="J157" s="3" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>€e7/Wh</v>
       </c>
       <c r="K157" s="3" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>€e7</v>
       </c>
       <c r="L157" s="3" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>None</v>
       </c>
       <c r="M157" s="3"/>
@@ -7691,43 +7690,43 @@
         <v>current timestamp</v>
       </c>
       <c r="C158" t="str">
-        <f t="shared" ref="C158:L158" si="110">_xlfn.XLOOKUP(C155,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <f t="shared" ref="C158:L158" si="112">_xlfn.XLOOKUP(C155,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>timestep (can be in future)</v>
       </c>
       <c r="D158" t="str">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>region in which the market is</v>
       </c>
       <c r="E158" t="str">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>type of market</v>
       </c>
       <c r="F158" t="str">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>name of the market</v>
       </c>
       <c r="G158" t="str">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>source of the costs/profits (e.g. Market, levies, balancing)</v>
       </c>
       <c r="H158" t="str">
-        <f t="shared" si="110"/>
-        <v>agent id (also serves as main meter)</v>
+        <f t="shared" si="112"/>
+        <v>agent id of outgoing energy</v>
       </c>
       <c r="I158" t="str">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>energy going out of the meter</v>
       </c>
       <c r="J158" t="str">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>spec. price for outflowing energy</v>
       </c>
       <c r="K158" t="str">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>total price for outflowing energy</v>
       </c>
       <c r="L158" t="str">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>quality of energy</v>
       </c>
     </row>
@@ -7843,47 +7842,47 @@
         <v>datetime</v>
       </c>
       <c r="C165" s="3" t="str">
-        <f t="shared" ref="C165:H165" si="111">_xlfn.XLOOKUP(C164,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="C165:H165" si="113">_xlfn.XLOOKUP(C164,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>datetime</v>
       </c>
       <c r="D165" s="3" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>categorical</v>
       </c>
       <c r="E165" s="3" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>categorical</v>
       </c>
       <c r="F165" s="3" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>categorical</v>
       </c>
       <c r="G165" s="3" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>categorical</v>
       </c>
       <c r="H165" s="3" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>categorical</v>
       </c>
       <c r="I165" s="3" t="str">
-        <f t="shared" ref="I165:M165" si="112">_xlfn.XLOOKUP(I164,$B$26:$XFD$26,$B$27:$XFD$27)</f>
+        <f t="shared" ref="I165:M165" si="114">_xlfn.XLOOKUP(I164,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>categorical</v>
       </c>
       <c r="J165" s="3" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>int64</v>
       </c>
       <c r="K165" s="3" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>int32</v>
       </c>
       <c r="L165" s="3" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>int64</v>
       </c>
       <c r="M165" s="3" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>categorical</v>
       </c>
       <c r="N165" s="3"/>
@@ -7899,47 +7898,47 @@
         <v>s</v>
       </c>
       <c r="C166" s="3" t="str">
-        <f t="shared" ref="C166:H166" si="113">_xlfn.XLOOKUP(C164,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <f t="shared" ref="C166:H166" si="115">_xlfn.XLOOKUP(C164,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>s</v>
       </c>
       <c r="D166" s="3" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>None</v>
       </c>
       <c r="E166" s="3" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>None</v>
       </c>
       <c r="F166" s="3" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>None</v>
       </c>
       <c r="G166" s="3" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>None</v>
       </c>
       <c r="H166" s="3" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>None</v>
       </c>
       <c r="I166" s="3" t="str">
-        <f t="shared" ref="I166:M166" si="114">_xlfn.XLOOKUP(I164,$B$26:$XFD$26,$B$28:$XFD$28)</f>
+        <f t="shared" ref="I166:M166" si="116">_xlfn.XLOOKUP(I164,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>None</v>
       </c>
       <c r="J166" s="3" t="str">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>Wh</v>
       </c>
       <c r="K166" s="3" t="str">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>€e7/Wh</v>
       </c>
       <c r="L166" s="3" t="str">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>€e7</v>
       </c>
       <c r="M166" s="3" t="str">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>None</v>
       </c>
       <c r="N166" s="3"/>
@@ -7955,47 +7954,47 @@
         <v>current timestamp</v>
       </c>
       <c r="C167" t="str">
-        <f t="shared" ref="C167:H167" si="115">_xlfn.XLOOKUP(C164,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <f t="shared" ref="C167:H167" si="117">_xlfn.XLOOKUP(C164,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>timestep (can be in future)</v>
       </c>
       <c r="D167" t="str">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>region in which the market is</v>
       </c>
       <c r="E167" t="str">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>type of market</v>
       </c>
       <c r="F167" t="str">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>name of the market</v>
       </c>
       <c r="G167" t="str">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>source of the costs/profits (e.g. Market, levies, balancing)</v>
       </c>
       <c r="H167" t="str">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>agent id of incoming energy</v>
       </c>
       <c r="I167" t="str">
-        <f t="shared" ref="I167:M167" si="116">_xlfn.XLOOKUP(I164,$B$26:$XFD$26,$B$29:$XFD$29)</f>
+        <f t="shared" ref="I167:M167" si="118">_xlfn.XLOOKUP(I164,$B$26:$XFD$26,$B$29:$XFD$29)</f>
         <v>agent id of outgoing energy</v>
       </c>
       <c r="J167" t="str">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>undirectional energy</v>
       </c>
       <c r="K167" t="str">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>spec. price for energy</v>
       </c>
       <c r="L167" t="str">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>total price for energy</v>
       </c>
       <c r="M167" t="str">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>quality of energy</v>
       </c>
     </row>

--- a/hamlet/tables.xlsx
+++ b/hamlet/tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ge23nur\Documents\Python Scripts\HAMLET\hamlet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91527C64-33C2-4BF7-B4B9-B04F38276B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{350FCF08-5E86-486B-AE3B-1990C9DC4B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" autoFilterDateGrouping="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" autoFilterDateGrouping="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Explanation" sheetId="13" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="301">
   <si>
     <t>column</t>
   </si>
@@ -935,6 +935,12 @@
   </si>
   <si>
     <t>coupling method (above, below)</t>
+  </si>
+  <si>
+    <t>any integer (flexible size)</t>
+  </si>
+  <si>
+    <t>unit depends on plant</t>
   </si>
 </sst>
 </file>
@@ -4120,6 +4126,9 @@
       <c r="AE27" s="9" t="s">
         <v>126</v>
       </c>
+      <c r="AF27" s="9" t="s">
+        <v>184</v>
+      </c>
       <c r="AG27" s="9" t="s">
         <v>98</v>
       </c>
@@ -4230,6 +4239,9 @@
       <c r="AE28" s="9" t="s">
         <v>248</v>
       </c>
+      <c r="AF28" s="9" t="s">
+        <v>300</v>
+      </c>
       <c r="AG28" s="9" t="s">
         <v>155</v>
       </c>
@@ -4367,7 +4379,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="33" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>169</v>
       </c>
@@ -4416,8 +4428,11 @@
       <c r="P33" s="9" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="34" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="Q33" s="9" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>123</v>
       </c>
@@ -4454,8 +4469,11 @@
       <c r="O34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="Q34" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>124</v>
       </c>
@@ -4492,8 +4510,11 @@
       <c r="O35">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="Q35" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>129</v>
       </c>
@@ -4501,7 +4522,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="37" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>130</v>
       </c>
@@ -4509,19 +4530,19 @@
         <v>164</v>
       </c>
     </row>
-    <row r="38" spans="1:16" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="8"/>
       <c r="B38" s="13"/>
     </row>
-    <row r="41" spans="1:16" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B42" s="5"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="15" t="str">
         <f>$A$3</f>
         <v>Table</v>
@@ -4543,7 +4564,7 @@
         <v>Saved</v>
       </c>
     </row>
-    <row r="44" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A44" s="16" t="str">
         <f>A4</f>
         <v>balancing_energy</v>
@@ -4565,10 +4586,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A45"/>
     </row>
-    <row r="46" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>0</v>
       </c>
@@ -4617,7 +4638,7 @@
         <v>price_out</v>
       </c>
     </row>
-    <row r="47" spans="1:16" s="10" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" s="10" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="str">
         <f>$A$27</f>
         <v>dtype</v>
@@ -4667,7 +4688,7 @@
         <v>int64</v>
       </c>
     </row>
-    <row r="48" spans="1:16" s="10" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" s="10" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="str">
         <f>$A$28</f>
         <v>unit</v>
@@ -8324,9 +8345,9 @@
         <f>_xlfn.XLOOKUP(B191,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>datetime</v>
       </c>
-      <c r="C192" s="3">
+      <c r="C192" s="3" t="str">
         <f>_xlfn.XLOOKUP(C191,$B$26:$XFD$26,$B$27:$XFD$27)</f>
-        <v>0</v>
+        <v>int</v>
       </c>
       <c r="D192" s="3"/>
       <c r="E192" s="3"/>
@@ -8350,9 +8371,9 @@
         <f>_xlfn.XLOOKUP(B191,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>s</v>
       </c>
-      <c r="C193" s="3">
+      <c r="C193" s="3" t="str">
         <f>_xlfn.XLOOKUP(C191,$B$26:$XFD$26,$B$28:$XFD$28)</f>
-        <v>0</v>
+        <v>unit depends on plant</v>
       </c>
       <c r="D193" s="3"/>
       <c r="E193" s="3"/>
@@ -8616,9 +8637,9 @@
         <f>_xlfn.XLOOKUP(C210,$B$26:$XFD$26,$B$27:$XFD$27)</f>
         <v>datetime</v>
       </c>
-      <c r="D211" s="3">
+      <c r="D211" s="3" t="str">
         <f>_xlfn.XLOOKUP(D210,$B$26:$XFD$26,$B$27:$XFD$27)</f>
-        <v>0</v>
+        <v>int</v>
       </c>
       <c r="E211" s="3"/>
       <c r="F211" s="3"/>
@@ -8645,9 +8666,9 @@
         <f>_xlfn.XLOOKUP(C210,$B$26:$XFD$26,$B$28:$XFD$28)</f>
         <v>s</v>
       </c>
-      <c r="D212" s="3">
+      <c r="D212" s="3" t="str">
         <f>_xlfn.XLOOKUP(D210,$B$26:$XFD$26,$B$28:$XFD$28)</f>
-        <v>0</v>
+        <v>unit depends on plant</v>
       </c>
       <c r="E212" s="3"/>
       <c r="F212" s="3"/>
